--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,31 +44,31 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.45229434967041</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5783224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73796367645264</t>
+    <t xml:space="preserve">9.57832336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033271789551</t>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028308868408</t>
+    <t xml:space="preserve">9.53631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.56992340087891</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832685470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,37 +128,37 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320329666138</t>
+    <t xml:space="preserve">10.0320320129395</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488367080688</t>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.89760112762451</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.98162078857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
@@ -179,43 +179,43 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.72955989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
+    <t xml:space="preserve">9.1162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623561859131</t>
+    <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85724830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94324016571045</t>
+    <t xml:space="preserve">8.8572473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07222938537598</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -305,73 +305,73 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">8.03171920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3093786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859970092773</t>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06860017776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74182748794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.7418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
+    <t xml:space="preserve">6.77622509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89661455154419</t>
+    <t xml:space="preserve">6.69023180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89661407470703</t>
   </si>
   <si>
     <t xml:space="preserve">7.01700353622437</t>
@@ -431,28 +431,28 @@
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377670288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233909606934</t>
+    <t xml:space="preserve">7.78233814239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315134048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.33315086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
+    <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651096343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77763414382935</t>
+    <t xml:space="preserve">6.26651048660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7776346206665</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
+    <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -57367,7 +57367,7 @@
     </row>
     <row r="2093">
       <c r="A2093" s="1" t="n">
-        <v>45945.6448148148</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2093" t="n">
         <v>15326</v>
@@ -57388,6 +57388,32 @@
         <v>650</v>
       </c>
       <c r="H2093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="1" t="n">
+        <v>45946.6436921296</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>5523</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2094" t="s">
+        <v>650</v>
+      </c>
+      <c r="H2094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.45229244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.737961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.52791213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
@@ -113,70 +113,70 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832685470581</t>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002456665039</t>
+    <t xml:space="preserve">10.0320329666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656404495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9984245300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873554229736</t>
+    <t xml:space="preserve">9.93961048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89759922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873458862305</t>
   </si>
   <si>
     <t xml:space="preserve">9.72955989837646</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -239,46 +239,46 @@
     <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02923393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327610015869</t>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529956817627</t>
+    <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -296,85 +296,85 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23810005187988</t>
+    <t xml:space="preserve">8.2381010055542</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7049446105957</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537191390991</t>
+    <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898868560791</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41257047653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06860017776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299682617188</t>
+    <t xml:space="preserve">7.10299634933472</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -410,49 +410,49 @@
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77622509002686</t>
+    <t xml:space="preserve">6.77622413635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">6.89661455154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696807861328</t>
+    <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377670288086</t>
+    <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233814239502</t>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233957290649</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206783294678</t>
+    <t xml:space="preserve">6.22206735610962</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7776346206665</t>
+    <t xml:space="preserve">6.26651096343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652040481567</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990081787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324036598206</t>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
+    <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
@@ -57393,7 +57393,7 @@
     </row>
     <row r="2094">
       <c r="A2094" s="1" t="n">
-        <v>45946.6436921296</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2094" t="n">
         <v>5523</v>
@@ -57414,6 +57414,32 @@
         <v>650</v>
       </c>
       <c r="H2094" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="1" t="n">
+        <v>45947.6415393519</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>20028</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>1.92999994754791</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>2.00999999046326</v>
+      </c>
+      <c r="G2095" t="s">
+        <v>733</v>
+      </c>
+      <c r="H2095" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
+    <t xml:space="preserve">9.70435523986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553928375244</t>
+    <t xml:space="preserve">9.61193084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553833007812</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992340087891</t>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -110,19 +110,19 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157020568848</t>
+    <t xml:space="preserve">9.77156925201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002265930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -161,40 +161,40 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89759922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
+    <t xml:space="preserve">9.8976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600395202637</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
+    <t xml:space="preserve">9.98162269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224090576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41619968414307</t>
+    <t xml:space="preserve">8.99017906188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41619873046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923393249512</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327705383301</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53047561645508</t>
+    <t xml:space="preserve">8.23810005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490962982178</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735754013062</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256999969482</t>
+    <t xml:space="preserve">7.41257047653198</t>
   </si>
   <si>
     <t xml:space="preserve">7.53296041488647</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -386,46 +386,46 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299634933472</t>
+    <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">6.74182748794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863611221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
+    <t xml:space="preserve">7.61895132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.31095457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
+    <t xml:space="preserve">5.95540761947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -57419,7 +57419,7 @@
     </row>
     <row r="2095">
       <c r="A2095" s="1" t="n">
-        <v>45947.6415393519</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2095" t="n">
         <v>20028</v>
@@ -57440,6 +57440,32 @@
         <v>733</v>
       </c>
       <c r="H2095" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2096">
+      <c r="A2096" s="1" t="n">
+        <v>45950.6277314815</v>
+      </c>
+      <c r="B2096" t="n">
+        <v>8908</v>
+      </c>
+      <c r="C2096" t="n">
+        <v>2.07999992370605</v>
+      </c>
+      <c r="D2096" t="n">
+        <v>1.95500004291534</v>
+      </c>
+      <c r="E2096" t="n">
+        <v>2.0699999332428</v>
+      </c>
+      <c r="F2096" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="G2096" t="s">
+        <v>872</v>
+      </c>
+      <c r="H2096" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868495941162</t>
+    <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553833007812</t>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77156925201416</t>
+    <t xml:space="preserve">9.77157115936279</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002265930176</t>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
@@ -152,28 +152,28 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -185,16 +185,16 @@
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224090576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99017906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619873046875</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
+    <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07222938537598</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327705383301</t>
+    <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090244293213</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32409381866455</t>
+    <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494508743286</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537239074707</t>
+    <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097431182861</t>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618772506714</t>
+    <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
     <t xml:space="preserve">7.73934316635132</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.41257047653198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739442825317</t>
+    <t xml:space="preserve">7.13739347457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">7.06860017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -392,58 +392,58 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74182748794556</t>
+    <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140066146851</t>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260641098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
+    <t xml:space="preserve">6.77622509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89661455154419</t>
+    <t xml:space="preserve">6.69023180007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89661407470703</t>
   </si>
   <si>
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
+    <t xml:space="preserve">7.44696807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377670288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634628295898</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233909606934</t>
+    <t xml:space="preserve">7.78233814239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536699295044</t>
+    <t xml:space="preserve">7.066490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536794662476</t>
   </si>
   <si>
     <t xml:space="preserve">7.46648073196411</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">7.022047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,49 +527,49 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.71094465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
+    <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651096343994</t>
+    <t xml:space="preserve">6.26651048660278</t>
   </si>
   <si>
     <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77763414382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73319101333618</t>
+    <t xml:space="preserve">5.7776346206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
+    <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -614,52 +614,52 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
+    <t xml:space="preserve">4.24878358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990081787109</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8576819896698</t>
+    <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
     <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75101804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879747390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.75101757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879723548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80435013771057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546292304993</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -57445,7 +57445,7 @@
     </row>
     <row r="2096">
       <c r="A2096" s="1" t="n">
-        <v>45950.6277314815</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2096" t="n">
         <v>8908</v>
@@ -57466,6 +57466,32 @@
         <v>872</v>
       </c>
       <c r="H2096" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2097">
+      <c r="A2097" s="1" t="n">
+        <v>45951.6457523148</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>2301</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>1.96000003814697</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2097" t="s">
+        <v>650</v>
+      </c>
+      <c r="H2097" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -53,19 +53,19 @@
     <t xml:space="preserve">9.45229244232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
+    <t xml:space="preserve">9.66234397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553928375244</t>
+    <t xml:space="preserve">9.64553833007812</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,22 +92,22 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636363983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198333740234</t>
+    <t xml:space="preserve">9.56151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
@@ -119,37 +119,37 @@
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8555908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85558986663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002456665039</t>
+    <t xml:space="preserve">10.0320339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.93960952758789</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
+    <t xml:space="preserve">10.0488367080688</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -173,106 +173,106 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72955894470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.24224090576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1582202911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0742015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41619968414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11522483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8572473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024375915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41619968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11522579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8572473526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15822219848633</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
+    <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5673565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3093786239624</t>
+    <t xml:space="preserve">7.56735754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618724822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334987640381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136377334595</t>
+    <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214412689209</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.53295946121216</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820928573608</t>
@@ -386,40 +386,40 @@
     <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70742988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10299634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87941551208496</t>
+    <t xml:space="preserve">6.70743036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10299682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8794150352478</t>
   </si>
   <si>
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77622413635254</t>
+    <t xml:space="preserve">6.75902557373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -428,25 +428,25 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416568756104</t>
+    <t xml:space="preserve">7.01700353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058485031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895322799683</t>
+    <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.61035442352295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233957290649</t>
+    <t xml:space="preserve">7.78233861923218</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0442943572998</t>
+    <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651096343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77763414382935</t>
+    <t xml:space="preserve">6.26651048660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7776346206665</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
+    <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652040481567</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
+    <t xml:space="preserve">3.99990081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -656,22 +656,22 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
+    <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
@@ -57500,7 +57500,7 @@
     </row>
     <row r="2098">
       <c r="A2098" s="1" t="n">
-        <v>45952.6495949074</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2098" t="n">
         <v>5387</v>
@@ -57521,6 +57521,32 @@
         <v>651</v>
       </c>
       <c r="H2098" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2099">
+      <c r="A2099" s="1" t="n">
+        <v>45953.6494212963</v>
+      </c>
+      <c r="B2099" t="n">
+        <v>4092</v>
+      </c>
+      <c r="C2099" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="D2099" t="n">
+        <v>1.97000002861023</v>
+      </c>
+      <c r="E2099" t="n">
+        <v>2.04999995231628</v>
+      </c>
+      <c r="F2099" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="G2099" t="s">
+        <v>733</v>
+      </c>
+      <c r="H2099" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="876">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.45229148864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151866912842</t>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430274963379</t>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992244720459</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404348373413</t>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656423568726</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.90600204467773</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -182,31 +182,31 @@
     <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
+    <t xml:space="preserve">9.78837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15822124481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1162109375</t>
+    <t xml:space="preserve">9.15822219848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
@@ -263,19 +263,19 @@
     <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
+    <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090148925781</t>
+    <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -287,28 +287,28 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4100866317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23810005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.2381010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693023681641</t>
+    <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
     <t xml:space="preserve">7.82533502578735</t>
@@ -317,49 +317,49 @@
     <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56735706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">7.5673565864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3093786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -368,49 +368,49 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859922409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820976257324</t>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820928573608</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70743036270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10299682617188</t>
+    <t xml:space="preserve">6.70742988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10299634933472</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342269897461</t>
+    <t xml:space="preserve">6.74182748794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622413635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501838684082</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377670288086</t>
+    <t xml:space="preserve">7.24058532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416568756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895322799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976856231689</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.61035442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233957290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
+    <t xml:space="preserve">7.066490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">7.022047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.71094465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
+    <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
+    <t xml:space="preserve">5.73319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">4.24878358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.80435013771057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546292304993</t>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -2637,6 +2637,9 @@
   </si>
   <si>
     <t xml:space="preserve">1.99000000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44000005722046</t>
   </si>
 </sst>
 </file>
@@ -57549,7 +57552,7 @@
     </row>
     <row r="2100">
       <c r="A2100" s="1" t="n">
-        <v>45954.6495138889</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2100" t="n">
         <v>19418</v>
@@ -57570,6 +57573,32 @@
         <v>651</v>
       </c>
       <c r="H2100" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2101">
+      <c r="A2101" s="1" t="n">
+        <v>45957.6912847222</v>
+      </c>
+      <c r="B2101" t="n">
+        <v>251177</v>
+      </c>
+      <c r="C2101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2101" t="n">
+        <v>2.02999997138977</v>
+      </c>
+      <c r="E2101" t="n">
+        <v>2.05999994277954</v>
+      </c>
+      <c r="F2101" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="G2101" t="s">
+        <v>875</v>
+      </c>
+      <c r="H2101" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229148864746</t>
+    <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.56151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
+    <t xml:space="preserve">9.76316738128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">9.91440391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -143,28 +143,28 @@
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656423568726</t>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600204467773</t>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15822219848633</t>
+    <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
     <t xml:space="preserve">9.11621189117432</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02923202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
@@ -263,19 +263,19 @@
     <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969573974609</t>
+    <t xml:space="preserve">8.28969669342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090244293213</t>
+    <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -287,28 +287,28 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.4100866317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490962982178</t>
+    <t xml:space="preserve">8.23810005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693071365356</t>
+    <t xml:space="preserve">7.87693023681641</t>
   </si>
   <si>
     <t xml:space="preserve">7.82533502578735</t>
@@ -317,49 +317,49 @@
     <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5673565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3093786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657766342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.73934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -368,49 +368,49 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820928573608</t>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859922409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70742988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10299634933472</t>
+    <t xml:space="preserve">6.70743036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74182748794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342317581177</t>
+    <t xml:space="preserve">6.7418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863611221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342269897461</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77622413635254</t>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501838684082</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895322799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
+    <t xml:space="preserve">7.24058485031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377670288086</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976856231689</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.31095457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
+    <t xml:space="preserve">5.95540761947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -57578,7 +57578,7 @@
     </row>
     <row r="2101">
       <c r="A2101" s="1" t="n">
-        <v>45957.6912847222</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2101" t="n">
         <v>251177</v>
@@ -57599,6 +57599,32 @@
         <v>875</v>
       </c>
       <c r="H2101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2102">
+      <c r="A2102" s="1" t="n">
+        <v>45958.6915162037</v>
+      </c>
+      <c r="B2102" t="n">
+        <v>166898</v>
+      </c>
+      <c r="C2102" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="D2102" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="E2102" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="F2102" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="G2102" t="s">
+        <v>644</v>
+      </c>
+      <c r="H2102" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="876">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="877">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73796272277832</t>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074680328369</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -92,46 +92,46 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51951026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636554718018</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157020568848</t>
+    <t xml:space="preserve">9.77156925201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404357910156</t>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404367446899</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -173,28 +173,28 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
+    <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721141815186</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
+    <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07223033905029</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
+    <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">9.02923202514648</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607753753662</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">8.28969669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
+    <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4100866317749</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.16930675506592</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490772247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">7.30937814712524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898868560791</t>
+    <t xml:space="preserve">7.36097431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -341,10 +341,10 @@
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934268951416</t>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.91381311416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">6.79342269897461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902652740479</t>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023132324219</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416616439819</t>
@@ -440,22 +440,22 @@
     <t xml:space="preserve">7.61895179748535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.43836688995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -2640,6 +2640,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.44000005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66000008583069</t>
   </si>
 </sst>
 </file>
@@ -57604,7 +57607,7 @@
     </row>
     <row r="2102">
       <c r="A2102" s="1" t="n">
-        <v>45958.6915162037</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2102" t="n">
         <v>166898</v>
@@ -57625,6 +57628,32 @@
         <v>644</v>
       </c>
       <c r="H2102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="1" t="n">
+        <v>45959.6912037037</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>156997</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>2.47000002861023</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="G2103" t="s">
+        <v>876</v>
+      </c>
+      <c r="H2103" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="877">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="878">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
+    <t xml:space="preserve">9.44389152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033462524414</t>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
+    <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553928375244</t>
+    <t xml:space="preserve">9.64553833007812</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636554718018</t>
@@ -110,40 +110,40 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77156925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316738128662</t>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316928863525</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997303009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8555908203125</t>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997207641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
     <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404367446899</t>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002265930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239456176758</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.97321796417236</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">8.98623561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926891326904</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
+    <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.3412914276123</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090339660645</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529956817627</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35848999023438</t>
+    <t xml:space="preserve">8.35848903656006</t>
   </si>
   <si>
     <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490772247314</t>
+    <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494604110718</t>
+    <t xml:space="preserve">7.87692975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097431182861</t>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898868560791</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -341,28 +341,28 @@
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218006134033</t>
+    <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739395141602</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859922409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342269897461</t>
+    <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -419,25 +419,25 @@
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895179748535</t>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
@@ -449,25 +449,25 @@
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035394668579</t>
+    <t xml:space="preserve">7.61035442352295</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836688995361</t>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15537786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.1553783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
+    <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
     <t xml:space="preserve">6.88871812820435</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
+    <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
     <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
+    <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990105628967</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324060440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
     <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80434989929199</t>
+    <t xml:space="preserve">3.68879723548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
     <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71546292304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212139129639</t>
+    <t xml:space="preserve">3.71546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212091445923</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
@@ -2643,6 +2643,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.66000008583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59999990463257</t>
   </si>
 </sst>
 </file>
@@ -57633,7 +57636,7 @@
     </row>
     <row r="2103">
       <c r="A2103" s="1" t="n">
-        <v>45959.6912037037</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2103" t="n">
         <v>156997</v>
@@ -57654,6 +57657,32 @@
         <v>876</v>
       </c>
       <c r="H2103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="1" t="n">
+        <v>45960.6910300926</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>86260</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G2104" t="s">
+        <v>877</v>
+      </c>
+      <c r="H2104" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229244232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.57832431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796367645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -74,19 +74,19 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -98,37 +98,37 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198238372803</t>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198143005371</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88920021057129</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057240486145</t>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -161,43 +161,43 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873554229736</t>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837299346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.78837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15822124481201</t>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15822219848633</t>
   </si>
   <si>
     <t xml:space="preserve">9.11621189117432</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
+    <t xml:space="preserve">8.94817161560059</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">8.98623561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.72825908660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -257,37 +257,37 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.59926986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090339660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35848903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -302,73 +302,73 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87692975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3093786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
+    <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.48136377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381311416626</t>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">6.98260688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416664123535</t>
+    <t xml:space="preserve">7.46416568756104</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
+    <t xml:space="preserve">7.61895322799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035442352295</t>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.33315134048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1553783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.11093473434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15537786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428443908691</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
+    <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.64435386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323862075806</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
     <t xml:space="preserve">4.06212091445923</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -57662,7 +57662,7 @@
     </row>
     <row r="2104">
       <c r="A2104" s="1" t="n">
-        <v>45960.6910300926</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2104" t="n">
         <v>86260</v>
@@ -57683,6 +57683,32 @@
         <v>877</v>
       </c>
       <c r="H2104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="1" t="n">
+        <v>45961.6910300926</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>57781</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G2105" t="s">
+        <v>646</v>
+      </c>
+      <c r="H2105" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -50,19 +50,19 @@
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796367645264</t>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -71,22 +71,22 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
+    <t xml:space="preserve">9.70435523986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.52791213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
+    <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157020568848</t>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77156925201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85558986663818</t>
+    <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.95641613006592</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88920021057129</t>
+    <t xml:space="preserve">9.99002265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -161,22 +161,22 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
+    <t xml:space="preserve">9.8976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600395202637</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.98162269592285</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873649597168</t>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72956085205078</t>
@@ -185,34 +185,34 @@
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
+    <t xml:space="preserve">9.24224090576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15822219848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11621189117432</t>
+    <t xml:space="preserve">9.15822124481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219032287598</t>
+    <t xml:space="preserve">8.94816970825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99017906188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619968414307</t>
+    <t xml:space="preserve">9.41619873046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825908660889</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923202514648</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -257,31 +257,31 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.28969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
+    <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3093786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
@@ -344,31 +344,31 @@
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41257047653198</t>
   </si>
   <si>
     <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">6.63863611221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023132324219</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416568756104</t>
+    <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895322799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
+    <t xml:space="preserve">7.61895132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035394668579</t>
+    <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33315134048462</t>
+    <t xml:space="preserve">7.6442551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
     <t xml:space="preserve">7.37759494781494</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
+    <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
@@ -521,31 +521,31 @@
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
+    <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
   </si>
   <si>
     <t xml:space="preserve">3.78657269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
+    <t xml:space="preserve">3.99990057945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80435013771057</t>
+    <t xml:space="preserve">3.80434989929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
+    <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
     <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212512016296</t>
+    <t xml:space="preserve">3.90212535858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434743881226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212091445923</t>
+    <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767532348633</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -57688,7 +57688,7 @@
     </row>
     <row r="2105">
       <c r="A2105" s="1" t="n">
-        <v>45961.6910300926</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2105" t="n">
         <v>57781</v>
@@ -57709,6 +57709,32 @@
         <v>646</v>
       </c>
       <c r="H2105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="1" t="n">
+        <v>45964.6910416667</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>98434</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2106" t="s">
+        <v>641</v>
+      </c>
+      <c r="H2106" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="878" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="879">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435523986816</t>
+    <t xml:space="preserve">9.73796367645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553833007812</t>
+    <t xml:space="preserve">9.61192989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
+    <t xml:space="preserve">9.56151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77156925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.82198143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832685470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -137,40 +137,40 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
+    <t xml:space="preserve">9.99002456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88920021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600395202637</t>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162269592285</t>
+    <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
@@ -179,19 +179,19 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224090576172</t>
+    <t xml:space="preserve">9.72955989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -200,19 +200,19 @@
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94816970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99017906188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">9.11621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619873046875</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
+    <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">8.59926986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409381866455</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -299,73 +299,73 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097431182861</t>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
+    <t xml:space="preserve">7.73934364318848</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41257047653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739442825317</t>
+    <t xml:space="preserve">7.13739347457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.91381216049194</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260593414307</t>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140066146851</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,25 +428,25 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377670288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15537786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.1553783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
+    <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
     <t xml:space="preserve">6.88871812820435</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
+    <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
     <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
+    <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990105628967</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324060440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
     <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80434989929199</t>
+    <t xml:space="preserve">3.68879723548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
     <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71546292304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212139129639</t>
+    <t xml:space="preserve">3.71546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212091445923</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
@@ -2646,6 +2646,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.59999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74000000953674</t>
   </si>
 </sst>
 </file>
@@ -57714,7 +57717,7 @@
     </row>
     <row r="2106">
       <c r="A2106" s="1" t="n">
-        <v>45964.6910416667</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2106" t="n">
         <v>98434</v>
@@ -57735,6 +57738,32 @@
         <v>641</v>
       </c>
       <c r="H2106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="1" t="n">
+        <v>45965.6942592593</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>39787</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="G2107" t="s">
+        <v>878</v>
+      </c>
+      <c r="H2107" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40187931060791</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4186840057373</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73796367645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033462524414</t>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61192989349365</t>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -89,37 +89,37 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51951026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992340087891</t>
+    <t xml:space="preserve">9.41028213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198143005371</t>
+    <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832685470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -137,28 +137,28 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88920021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.98162078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
+    <t xml:space="preserve">9.72955894470215</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837490081787</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.1162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94817066192627</t>
@@ -212,40 +212,40 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">9.11522483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07223033905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77125549316406</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024375915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32409381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35848999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.32409286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35849094390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -308,22 +308,22 @@
     <t xml:space="preserve">8.03171825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
+    <t xml:space="preserve">7.30937957763672</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934364318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739347457886</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820976257324</t>
+    <t xml:space="preserve">6.94820928573608</t>
   </si>
   <si>
     <t xml:space="preserve">6.91381216049194</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70743036270142</t>
+    <t xml:space="preserve">6.70743083953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941551208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74182748794556</t>
+    <t xml:space="preserve">6.8794150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233909606934</t>
+    <t xml:space="preserve">7.78233861923218</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1553783416748</t>
+    <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28870725631714</t>
+    <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536794662476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428443908691</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
+    <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26651096343994</t>
+    <t xml:space="preserve">6.17762422561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26651048660278</t>
   </si>
   <si>
     <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77763414382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.7776346206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990105628967</t>
+    <t xml:space="preserve">3.99990081787109</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879723548889</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
+    <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
     <t xml:space="preserve">3.98212313652039</t>
@@ -683,25 +683,25 @@
     <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212488174438</t>
+    <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101558685303</t>
+    <t xml:space="preserve">3.83101606369019</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">3.81323838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -57743,7 +57743,7 @@
     </row>
     <row r="2107">
       <c r="A2107" s="1" t="n">
-        <v>45965.6942592593</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2107" t="n">
         <v>39787</v>
@@ -57764,6 +57764,32 @@
         <v>878</v>
       </c>
       <c r="H2107" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="1" t="n">
+        <v>45966.6911921296</v>
+      </c>
+      <c r="B2108" t="n">
+        <v>121807</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="G2108" t="s">
+        <v>636</v>
+      </c>
+      <c r="H2108" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="880">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4186840057373</t>
+    <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234493255615</t>
+    <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
+    <t xml:space="preserve">9.70435523986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028213500977</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8555908203125</t>
+    <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
     <t xml:space="preserve">9.95641613006592</t>
@@ -143,46 +143,46 @@
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842643737793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600204467773</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
+    <t xml:space="preserve">9.98162269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827278137207</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.94817161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9901819229126</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020687103271</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">9.11522579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825908660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90024375915527</t>
+    <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125453948975</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.28969669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090148925781</t>
+    <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35849094390869</t>
+    <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
     <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87692975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221742630005</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214317321777</t>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
+    <t xml:space="preserve">6.96540832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743083953857</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -404,37 +404,37 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.84501838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.01700353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696760177612</t>
+    <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233861923218</t>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.33315134048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7776346206665</t>
+    <t xml:space="preserve">6.26651096343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990081787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
+    <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767627716064</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -2649,6 +2649,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.74000000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84999990463257</t>
   </si>
 </sst>
 </file>
@@ -57769,25 +57772,25 @@
     </row>
     <row r="2108">
       <c r="A2108" s="1" t="n">
-        <v>45966.6911921296</v>
+        <v>45967.6912384259</v>
       </c>
       <c r="B2108" t="n">
-        <v>121807</v>
+        <v>96981</v>
       </c>
       <c r="C2108" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="E2108" t="n">
         <v>2.88000011444092</v>
       </c>
-      <c r="D2108" t="n">
-        <v>2.74000000953674</v>
-      </c>
-      <c r="E2108" t="n">
-        <v>2.74000000953674</v>
-      </c>
       <c r="F2108" t="n">
-        <v>2.88000011444092</v>
+        <v>2.84999990463257</v>
       </c>
       <c r="G2108" t="s">
-        <v>636</v>
+        <v>879</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="881">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,88 +38,88 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4186840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.70435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.56151866912842</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992053985596</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
+    <t xml:space="preserve">9.82198143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316738128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -161,58 +161,58 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.8976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600395202637</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.98162269592285</t>
   </si>
   <si>
     <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.62873554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
+    <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9901819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">8.94817066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -236,46 +236,46 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024566650391</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
+    <t xml:space="preserve">9.02923202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
+    <t xml:space="preserve">8.28969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -302,82 +302,82 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">7.87692975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3093786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65335035324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
+    <t xml:space="preserve">7.73934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218053817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820976257324</t>
+    <t xml:space="preserve">6.96540832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9482102394104</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,19 +389,19 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941598892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.8794150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74182748794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260593414307</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.24058532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976951599121</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.78234004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836832046509</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -2648,7 +2648,13 @@
     <t xml:space="preserve">2.74000000953674</t>
   </si>
   <si>
+    <t xml:space="preserve">2.84999990463257</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.70000004768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69000005722046</t>
   </si>
 </sst>
 </file>
@@ -57769,27 +57775,105 @@
     </row>
     <row r="2108">
       <c r="A2108" s="1" t="n">
-        <v>45968.691087963</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2108" t="n">
+        <v>121807</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="G2108" t="s">
+        <v>635</v>
+      </c>
+      <c r="H2108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>96981</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>2.84999990463257</v>
+      </c>
+      <c r="G2109" t="s">
+        <v>878</v>
+      </c>
+      <c r="H2109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2110" t="n">
         <v>64036</v>
       </c>
-      <c r="C2108" t="n">
+      <c r="C2110" t="n">
         <v>2.79999995231628</v>
       </c>
-      <c r="D2108" t="n">
+      <c r="D2110" t="n">
         <v>2.63000011444092</v>
       </c>
-      <c r="E2108" t="n">
+      <c r="E2110" t="n">
         <v>2.79999995231628</v>
       </c>
-      <c r="F2108" t="n">
+      <c r="F2110" t="n">
         <v>2.70000004768372</v>
       </c>
-      <c r="G2108" t="s">
-        <v>878</v>
-      </c>
-      <c r="H2108" t="s">
+      <c r="G2110" t="s">
+        <v>879</v>
+      </c>
+      <c r="H2110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="1" t="n">
+        <v>45971.6909722222</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>65566</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="G2111" t="s">
+        <v>880</v>
+      </c>
+      <c r="H2111" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.45229434967041</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033462524414</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -92,40 +92,40 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992053985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.56151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636363983154</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77156925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440677642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997303009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85558986663818</t>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997207641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.95641613006592</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002265930176</t>
+    <t xml:space="preserve">10.0320339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88920021057129</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057240486145</t>
+    <t xml:space="preserve">9.87239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">10.0488367080688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600395202637</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224090576172</t>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">8.94817161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219223022461</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721141815186</t>
@@ -230,10 +230,10 @@
     <t xml:space="preserve">8.98623561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825717926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8572473526001</t>
+    <t xml:space="preserve">8.72825813293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85724830627441</t>
   </si>
   <si>
     <t xml:space="preserve">8.94324016571045</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -278,16 +278,16 @@
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090339660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35848903656006</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
     <t xml:space="preserve">8.41008567810059</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
+    <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490867614746</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87692975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
+    <t xml:space="preserve">7.3093786239624</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097478866577</t>
@@ -335,55 +335,55 @@
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">7.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381311416626</t>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -431,28 +431,28 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416664123535</t>
+    <t xml:space="preserve">7.24058485031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416568756104</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
+    <t xml:space="preserve">7.61895275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.33315134048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,28 +479,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1553783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.11093473434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15537786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -509,22 +509,22 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428443908691</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
+    <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
@@ -554,37 +554,37 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.64435386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323862075806</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
     <t xml:space="preserve">4.06212091445923</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -734,16 +734,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -893,25 +893,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -983,16 +983,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -57885,7 +57885,7 @@
     </row>
     <row r="2112">
       <c r="A2112" s="1" t="n">
-        <v>45972.6910300926</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2112" t="n">
         <v>31939</v>
@@ -57906,6 +57906,32 @@
         <v>644</v>
       </c>
       <c r="H2112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="1" t="n">
+        <v>45973.6912615741</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>17861</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2113" t="s">
+        <v>642</v>
+      </c>
+      <c r="H2113" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
+    <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234397888184</t>
+    <t xml:space="preserve">9.57832336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234302520752</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553833007812</t>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430274963379</t>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636363983154</t>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198333740234</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832695007324</t>
+    <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320329666138</t>
+    <t xml:space="preserve">10.0320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002456665039</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">10.0656423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99842548370361</t>
+    <t xml:space="preserve">9.9984245300293</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488367080688</t>
@@ -197,73 +197,73 @@
     <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
+    <t xml:space="preserve">9.1582202911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41620063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11522579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8572473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41619968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11522579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8572473526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15822219848633</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
+    <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171730041504</t>
+    <t xml:space="preserve">8.03171825408936</t>
   </si>
   <si>
     <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533502578735</t>
+    <t xml:space="preserve">7.82533597946167</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494556427002</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">7.5673565864563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3093786239624</t>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937814712524</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
+    <t xml:space="preserve">7.65334892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214412689209</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.53296089172363</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">7.06860017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820928573608</t>
@@ -386,19 +386,19 @@
     <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70742988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10299634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87941551208496</t>
+    <t xml:space="preserve">6.70743036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10299682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8794150352478</t>
   </si>
   <si>
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.77622413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
+    <t xml:space="preserve">6.84501791000366</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101119995117</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416568756104</t>
+    <t xml:space="preserve">7.24058485031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416616439819</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895322799683</t>
+    <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.34377574920654</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035442352295</t>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233957290649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -57963,7 +57963,7 @@
     </row>
     <row r="2115">
       <c r="A2115" s="1" t="n">
-        <v>45975.672962963</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2115" t="n">
         <v>12449</v>
@@ -57984,6 +57984,32 @@
         <v>643</v>
       </c>
       <c r="H2115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="1" t="n">
+        <v>45978.6911111111</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>14792</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2116" t="s">
+        <v>646</v>
+      </c>
+      <c r="H2116" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.45229244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.737961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -74,34 +74,34 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151866912842</t>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -110,19 +110,19 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404348373413</t>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -161,10 +161,10 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.89759922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600204467773</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873554229736</t>
+    <t xml:space="preserve">9.62873458862305</t>
   </si>
   <si>
     <t xml:space="preserve">9.72955989837646</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425312042236</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02923393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
+    <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.34129047393799</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4100866317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23810005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.2381010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
@@ -311,25 +311,25 @@
     <t xml:space="preserve">7.87693023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937814712524</t>
+    <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32657766342163</t>
+    <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898868560791</t>
@@ -344,37 +344,37 @@
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859922409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299682617188</t>
+    <t xml:space="preserve">7.10299634933472</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
+    <t xml:space="preserve">6.63863563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260641098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622413635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501838684082</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377670288086</t>
+    <t xml:space="preserve">7.24058532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976856231689</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.61035442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233957290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
+    <t xml:space="preserve">7.066490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">7.022047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.71094465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
+    <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
+    <t xml:space="preserve">5.73319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">4.24878358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.80435013771057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546292304993</t>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -58012,7 +58012,7 @@
     </row>
     <row r="2117">
       <c r="A2117" s="1" t="n">
-        <v>45979.6772222222</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2117" t="n">
         <v>1985</v>
@@ -58033,6 +58033,32 @@
         <v>695</v>
       </c>
       <c r="H2117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="1" t="n">
+        <v>45980.614837963</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>13305</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="G2118" t="s">
+        <v>694</v>
+      </c>
+      <c r="H2118" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5783224105835</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992340087891</t>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992053985596</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -119,22 +119,22 @@
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8555908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320329666138</t>
+    <t xml:space="preserve">9.91440677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85558986663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.0572395324707</t>
@@ -161,22 +161,22 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89759922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873458862305</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.72955989837646</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
@@ -194,34 +194,34 @@
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
+    <t xml:space="preserve">9.11621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41619968414307</t>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41619873046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923393249512</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327705383301</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -296,10 +296,10 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53047561645508</t>
+    <t xml:space="preserve">8.23810005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490962982178</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735754013062</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256999969482</t>
+    <t xml:space="preserve">7.41257047653198</t>
   </si>
   <si>
     <t xml:space="preserve">7.53296041488647</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -386,46 +386,46 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299634933472</t>
+    <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">6.74182748794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863611221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
+    <t xml:space="preserve">7.61895132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.31095457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
+    <t xml:space="preserve">5.95540761947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -58038,7 +58038,7 @@
     </row>
     <row r="2118">
       <c r="A2118" s="1" t="n">
-        <v>45980.614837963</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2118" t="n">
         <v>13305</v>
@@ -58059,6 +58059,32 @@
         <v>694</v>
       </c>
       <c r="H2118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="1" t="n">
+        <v>45981.6910648148</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>3163</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>2.58999991416931</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>695</v>
+      </c>
+      <c r="H2119" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.4186840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229434967041</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5783224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234397888184</t>
+    <t xml:space="preserve">9.57832336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234302520752</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51951026916504</t>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.49430274963379</t>
@@ -107,52 +107,52 @@
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
+    <t xml:space="preserve">9.82198333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404348373413</t>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404367446899</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656394958496</t>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -161,46 +161,46 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
+    <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
+    <t xml:space="preserve">9.83038425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425407409668</t>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
+    <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.07420063018799</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -245,40 +245,40 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969669342041</t>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4100866317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930484771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
   </si>
   <si>
     <t xml:space="preserve">7.87693023681641</t>
@@ -314,52 +314,52 @@
     <t xml:space="preserve">7.82533502578735</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937814712524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898868560791</t>
+    <t xml:space="preserve">7.36097526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934268951416</t>
+    <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136425018311</t>
+    <t xml:space="preserve">7.48136377334595</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859922409058</t>
+    <t xml:space="preserve">7.06860017776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.91381311416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342269897461</t>
+    <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902652740479</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -419,34 +419,34 @@
     <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377670288086</t>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634580612183</t>
+    <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
+    <t xml:space="preserve">7.066490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">7.022047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.71094465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
+    <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
+    <t xml:space="preserve">5.73319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">4.24878358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.80435013771057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546292304993</t>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -58177,7 +58177,7 @@
     </row>
     <row r="2123">
       <c r="A2123" s="1" t="n">
-        <v>45987.6777430556</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2123" t="n">
         <v>10560</v>
@@ -58198,6 +58198,32 @@
         <v>884</v>
       </c>
       <c r="H2123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="1" t="n">
+        <v>45988.4041898148</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>5501</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2124" t="s">
+        <v>645</v>
+      </c>
+      <c r="H2124" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.57832431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.70435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028308868408</t>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5363130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
+    <t xml:space="preserve">9.76316928863525</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239456176758</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842643737793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
+    <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600204467773</t>
@@ -170,22 +170,22 @@
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
+    <t xml:space="preserve">9.98162269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626342773438</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420253753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94817066192627</t>
+    <t xml:space="preserve">9.0742015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817161560059</t>
   </si>
   <si>
     <t xml:space="preserve">8.9901819229126</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020687103271</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">9.11522579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825908660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90024375915527</t>
+    <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125453948975</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.28969669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,34 +299,34 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87692975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537191390991</t>
+    <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
@@ -341,61 +341,61 @@
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53295946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820928573608</t>
+    <t xml:space="preserve">6.96540832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70743036270142</t>
+    <t xml:space="preserve">6.70743083953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74182748794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.87941551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233861923218</t>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.33315134048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7776346206665</t>
+    <t xml:space="preserve">6.26651096343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990081787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
+    <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767627716064</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -58310,7 +58310,7 @@
     </row>
     <row r="2128">
       <c r="A2128" s="1" t="n">
-        <v>45994.6912152778</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2128" t="n">
         <v>15164</v>
@@ -58331,6 +58331,32 @@
         <v>692</v>
       </c>
       <c r="H2128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="1" t="n">
+        <v>45995.6912384259</v>
+      </c>
+      <c r="B2129" t="n">
+        <v>43112</v>
+      </c>
+      <c r="C2129" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2129" t="s">
+        <v>643</v>
+      </c>
+      <c r="H2129" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
@@ -53,19 +53,19 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5783224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553833007812</t>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4102840423584</t>
+    <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992149353027</t>
+    <t xml:space="preserve">9.56992053985596</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316738128662</t>
+    <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.91440677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320329666138</t>
+    <t xml:space="preserve">10.0404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93960952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057240486145</t>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162078857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72955989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
@@ -194,43 +194,43 @@
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
+    <t xml:space="preserve">9.11621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41619968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11522483825684</t>
+    <t xml:space="preserve">8.99018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41619873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
     <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,13 +239,13 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77125453948975</t>
+    <t xml:space="preserve">9.07222938537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327610015869</t>
+    <t xml:space="preserve">8.42728328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,34 +299,34 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537191390991</t>
+    <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618724822998</t>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
     <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334987640381</t>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">7.72214412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295946121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739442825317</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820928573608</t>
+    <t xml:space="preserve">6.96540832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.74182748794556</t>
@@ -398,28 +398,28 @@
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">6.79342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
+    <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
+    <t xml:space="preserve">7.61895132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233861923218</t>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
     <t xml:space="preserve">7.46648073196411</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,49 +527,49 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
+    <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
     <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7776346206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.77763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -614,52 +614,52 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990081787109</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85768222808838</t>
+    <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -58388,7 +58388,7 @@
     </row>
     <row r="2131">
       <c r="A2131" s="1" t="n">
-        <v>45999.6913310185</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2131" t="n">
         <v>34499</v>
@@ -58409,6 +58409,32 @@
         <v>880</v>
       </c>
       <c r="H2131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="1" t="n">
+        <v>46000.6825462963</v>
+      </c>
+      <c r="B2132" t="n">
+        <v>25903</v>
+      </c>
+      <c r="C2132" t="n">
+        <v>2.82999992370605</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2132" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="G2132" t="s">
+        <v>641</v>
+      </c>
+      <c r="H2132" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5783224105835</t>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -74,37 +74,37 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
   </si>
   <si>
     <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992053985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
+    <t xml:space="preserve">9.56992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636554718018</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832714080811</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440677642822</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85558986663818</t>
+    <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404367446899</t>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320339202881</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600395202637</t>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162078857422</t>
+    <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.62873554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
+    <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -203,25 +203,25 @@
     <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619873046875</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -245,22 +245,22 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
+    <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
+    <t xml:space="preserve">8.42728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090244293213</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -302,46 +302,46 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
   </si>
   <si>
     <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533550262451</t>
+    <t xml:space="preserve">7.82533645629883</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097431182861</t>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
     <t xml:space="preserve">7.73934316635132</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41257047653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296089172363</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739442825317</t>
+    <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74182748794556</t>
+    <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260593414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260641098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140018463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895132064819</t>
+    <t xml:space="preserve">7.44696807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15537786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.1553783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
+    <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
     <t xml:space="preserve">6.88871812820435</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
+    <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
     <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
+    <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990105628967</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324060440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
     <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80434989929199</t>
+    <t xml:space="preserve">3.68879723548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
     <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71546292304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212139129639</t>
+    <t xml:space="preserve">3.71546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212091445923</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
@@ -58414,7 +58414,7 @@
     </row>
     <row r="2132">
       <c r="A2132" s="1" t="n">
-        <v>46000.6825462963</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2132" t="n">
         <v>25903</v>
@@ -58435,6 +58435,32 @@
         <v>641</v>
       </c>
       <c r="H2132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="1" t="n">
+        <v>46001.6720486111</v>
+      </c>
+      <c r="B2133" t="n">
+        <v>9118</v>
+      </c>
+      <c r="C2133" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2133" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="F2133" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2133" t="s">
+        <v>645</v>
+      </c>
+      <c r="H2133" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -71,16 +71,16 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.70435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950836181641</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">9.76316928863525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832714080811</t>
+    <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440677642822</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320339202881</t>
+    <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919925689697</t>
+    <t xml:space="preserve">9.88920021057129</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
+    <t xml:space="preserve">10.0656423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.98162078857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837299346924</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">9.03219223022461</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721141815186</t>
@@ -58440,7 +58440,7 @@
     </row>
     <row r="2133">
       <c r="A2133" s="1" t="n">
-        <v>46001.6720486111</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2133" t="n">
         <v>9118</v>
@@ -58461,6 +58461,32 @@
         <v>645</v>
       </c>
       <c r="H2133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="1" t="n">
+        <v>46002.6911689815</v>
+      </c>
+      <c r="B2134" t="n">
+        <v>35785</v>
+      </c>
+      <c r="C2134" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D2134" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="E2134" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F2134" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="G2134" t="s">
+        <v>644</v>
+      </c>
+      <c r="H2134" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.44388961791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -62,31 +62,31 @@
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.737961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6371374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64554023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992053985596</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440677642822</t>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8555908203125</t>
+    <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
     <t xml:space="preserve">9.9564151763916</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88920021057129</t>
+    <t xml:space="preserve">9.99002265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
@@ -152,10 +152,10 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656423568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9984245300293</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488386154175</t>
@@ -164,25 +164,25 @@
     <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.90600395202637</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837299346924</t>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
+    <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">9.03219223022461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619968414307</t>
+    <t xml:space="preserve">9.41619873046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
+    <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
+    <t xml:space="preserve">8.42728328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32409381866455</t>
+    <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -305,40 +305,40 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171825408936</t>
+    <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657814025879</t>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657766342163</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.2061882019043</t>
@@ -359,10 +359,10 @@
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739395141602</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">7.06859922409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342317581177</t>
+    <t xml:space="preserve">6.79342269897461</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895132064819</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836688995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1553783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.15537786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
+    <t xml:space="preserve">7.02204751968384</t>
   </si>
   <si>
     <t xml:space="preserve">6.88871812820435</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
+    <t xml:space="preserve">6.71094417572021</t>
   </si>
   <si>
     <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990105628967</t>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324060440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
   </si>
   <si>
     <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80435013771057</t>
+    <t xml:space="preserve">3.68879747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80434989929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
   </si>
   <si>
     <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71546316146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212091445923</t>
+    <t xml:space="preserve">3.71546292304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
@@ -58466,7 +58466,7 @@
     </row>
     <row r="2134">
       <c r="A2134" s="1" t="n">
-        <v>46002.6911689815</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2134" t="n">
         <v>35785</v>
@@ -58487,6 +58487,32 @@
         <v>644</v>
       </c>
       <c r="H2134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="1" t="n">
+        <v>46003.6912152778</v>
+      </c>
+      <c r="B2135" t="n">
+        <v>6761</v>
+      </c>
+      <c r="C2135" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D2135" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="E2135" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="F2135" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="G2135" t="s">
+        <v>666</v>
+      </c>
+      <c r="H2135" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234397888184</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5783224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234302520752</t>
   </si>
   <si>
     <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435333251953</t>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033367156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
     <t xml:space="preserve">9.6371374130249</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631496429443</t>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992053985596</t>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.77157115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -161,40 +161,40 @@
     <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600395202637</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.98162078857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219223022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619873046875</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.2012186050415</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607849121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969573974609</t>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607753753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969669342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327705383301</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490772247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32657766342163</t>
+    <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898916244507</t>
@@ -338,28 +338,28 @@
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221694946289</t>
+    <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
+    <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136472702026</t>
+    <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.91381311416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501886367798</t>
+    <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895132064819</t>
+    <t xml:space="preserve">7.61895179748535</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035346984863</t>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
@@ -58492,7 +58492,7 @@
     </row>
     <row r="2135">
       <c r="A2135" s="1" t="n">
-        <v>46003.6912152778</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2135" t="n">
         <v>6761</v>
@@ -58513,6 +58513,32 @@
         <v>666</v>
       </c>
       <c r="H2135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="1" t="n">
+        <v>46006.6683333333</v>
+      </c>
+      <c r="B2136" t="n">
+        <v>10350</v>
+      </c>
+      <c r="C2136" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="E2136" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F2136" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2136" t="s">
+        <v>645</v>
+      </c>
+      <c r="H2136" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5783224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
+    <t xml:space="preserve">9.57832336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -95,40 +95,40 @@
     <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.74636554718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77156925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85558986663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.8555908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95641422271729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
+    <t xml:space="preserve">9.83038520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626342773438</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923202514648</t>
+    <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">9.2012186050415</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
+    <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.3412914276123</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
+    <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490772247314</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693071365356</t>
+    <t xml:space="preserve">7.87693119049072</t>
   </si>
   <si>
     <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70494604110718</t>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097431182861</t>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898963928223</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859922409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381311416626</t>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342269897461</t>
+    <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
@@ -407,37 +407,37 @@
     <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
+    <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
+    <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895179748535</t>
+    <t xml:space="preserve">7.61895275115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836688995361</t>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15537786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.1553783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
+    <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
     <t xml:space="preserve">6.88871812820435</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
+    <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
     <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
+    <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990105628967</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324060440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
     <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80434989929199</t>
+    <t xml:space="preserve">3.68879723548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
     <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71546292304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212139129639</t>
+    <t xml:space="preserve">3.71546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212091445923</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
@@ -58518,7 +58518,7 @@
     </row>
     <row r="2136">
       <c r="A2136" s="1" t="n">
-        <v>46006.6683333333</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2136" t="n">
         <v>10350</v>
@@ -58539,6 +58539,32 @@
         <v>645</v>
       </c>
       <c r="H2136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="1" t="n">
+        <v>46007.6396527778</v>
+      </c>
+      <c r="B2137" t="n">
+        <v>10531</v>
+      </c>
+      <c r="C2137" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2137" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2137" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G2137" t="s">
+        <v>877</v>
+      </c>
+      <c r="H2137" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.45229148864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033462524414</t>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -95,31 +95,31 @@
     <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77156925201416</t>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641422271729</t>
+    <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656414031982</t>
+    <t xml:space="preserve">9.87239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656423568726</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.90600204467773</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15822124481201</t>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15822219848633</t>
   </si>
   <si>
     <t xml:space="preserve">9.11621189117432</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607753753662</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -296,79 +296,79 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23810005187988</t>
+    <t xml:space="preserve">8.2381010055542</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490772247314</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537143707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3093786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820976257324</t>
+    <t xml:space="preserve">6.94820928573608</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70743036270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10299682617188</t>
+    <t xml:space="preserve">6.70742988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10299634933472</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">6.98260688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -425,37 +425,37 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.46416568756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895322799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233957290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1553783416748</t>
+    <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.39984083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -581,52 +581,52 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.64435386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101558685303</t>
+    <t xml:space="preserve">3.83101606369019</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">3.81323838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -58544,7 +58544,7 @@
     </row>
     <row r="2137">
       <c r="A2137" s="1" t="n">
-        <v>46007.6396527778</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2137" t="n">
         <v>10531</v>
@@ -58565,6 +58565,32 @@
         <v>877</v>
       </c>
       <c r="H2137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="1" t="n">
+        <v>46008.691087963</v>
+      </c>
+      <c r="B2138" t="n">
+        <v>25480</v>
+      </c>
+      <c r="C2138" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="E2138" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2138" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="G2138" t="s">
+        <v>666</v>
+      </c>
+      <c r="H2138" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229148864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553928375244</t>
+    <t xml:space="preserve">9.64554023742676</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.56151866912842</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
@@ -110,25 +110,25 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">9.77157115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656423568726</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">10.0488367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
+    <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
@@ -188,16 +188,16 @@
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626342773438</t>
+    <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15822219848633</t>
+    <t xml:space="preserve">9.28425216674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
     <t xml:space="preserve">9.11621189117432</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
+    <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721141815186</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623657226562</t>
+    <t xml:space="preserve">8.98623561859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8572473526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94323921203613</t>
+    <t xml:space="preserve">8.85724830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07222938537598</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
+    <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
+    <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
@@ -311,28 +311,28 @@
     <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533502578735</t>
+    <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5673565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537143707275</t>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.3093786239624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898963928223</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980592727661</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.65334892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820928573608</t>
+    <t xml:space="preserve">6.96540880203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70742988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10299634933472</t>
+    <t xml:space="preserve">6.70743036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">6.77622413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">7.01700353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416568756104</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895322799683</t>
+    <t xml:space="preserve">7.61895275115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
+    <t xml:space="preserve">7.33315134048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.37759494781494</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
+    <t xml:space="preserve">7.5553674697876</t>
   </si>
   <si>
     <t xml:space="preserve">7.46648025512695</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
+    <t xml:space="preserve">5.95540761947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -578,31 +578,31 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
+    <t xml:space="preserve">3.78657269477844</t>
   </si>
   <si>
     <t xml:space="preserve">3.99990034103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89323687553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73324012756348</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212361335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -686,31 +686,31 @@
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767627716064</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -58570,7 +58570,7 @@
     </row>
     <row r="2138">
       <c r="A2138" s="1" t="n">
-        <v>46008.691087963</v>
+        <v>46008.3333333333</v>
       </c>
       <c r="B2138" t="n">
         <v>25480</v>
@@ -58591,6 +58591,32 @@
         <v>666</v>
       </c>
       <c r="H2138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="1" t="n">
+        <v>46009.6910300926</v>
+      </c>
+      <c r="B2139" t="n">
+        <v>7913</v>
+      </c>
+      <c r="C2139" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E2139" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G2139" t="s">
+        <v>646</v>
+      </c>
+      <c r="H2139" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.737961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64554023742676</t>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,28 +92,28 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316928863525</t>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636554718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77156925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832714080811</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.95641422271729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002456665039</t>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488367080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
+    <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623561859131</t>
+    <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85724830627441</t>
+    <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,46 +248,46 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490772247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693071365356</t>
+    <t xml:space="preserve">7.87693119049072</t>
   </si>
   <si>
     <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70494556427002</t>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3093786239624</t>
+    <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097478866577</t>
@@ -335,46 +335,46 @@
     <t xml:space="preserve">7.18898963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77622413635254</t>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501886367798</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
+    <t xml:space="preserve">7.24058532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377574920654</t>
+    <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315134048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.33315086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15537786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.11093425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1553783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.066490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984083175659</t>
+    <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428443908691</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.73319101333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
+    <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324060440063</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">3.98212313652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323838233948</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323862075806</t>
   </si>
   <si>
     <t xml:space="preserve">4.06212091445923</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767532348633</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -58596,7 +58596,7 @@
     </row>
     <row r="2139">
       <c r="A2139" s="1" t="n">
-        <v>46009.6910300926</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2139" t="n">
         <v>7913</v>
@@ -58617,6 +58617,32 @@
         <v>646</v>
       </c>
       <c r="H2139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="1" t="n">
+        <v>46010.6912384259</v>
+      </c>
+      <c r="B2140" t="n">
+        <v>3386</v>
+      </c>
+      <c r="C2140" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="D2140" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="E2140" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="F2140" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="G2140" t="s">
+        <v>644</v>
+      </c>
+      <c r="H2140" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796367645264</t>
+    <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074680328369</t>
@@ -74,52 +74,52 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791023254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.6371374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950836181641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430274963379</t>
+    <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.74636554718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77156925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404367446899</t>
+    <t xml:space="preserve">9.95641422271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002456665039</t>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873649597168</t>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72956085205078</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018001556396</t>
+    <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -251,37 +251,37 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -302,82 +302,82 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
+    <t xml:space="preserve">8.13490772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
+    <t xml:space="preserve">7.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06860017776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820928573608</t>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.74182748794556</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">6.98260641098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501791000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -425,34 +425,34 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058485031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
+    <t xml:space="preserve">7.01700353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233957290649</t>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836736679077</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15537786483765</t>
+    <t xml:space="preserve">7.1553783416748</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.31095457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.73319101333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -581,52 +581,52 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
+    <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.73324060440063</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101606369019</t>
+    <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">3.81323862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -58674,7 +58674,7 @@
     </row>
     <row r="2142">
       <c r="A2142" s="1" t="n">
-        <v>46014.6442939815</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2142" t="n">
         <v>12108</v>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.45229244232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435428619385</t>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033367156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435523986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
+    <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193180084229</t>
@@ -89,37 +89,37 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028308868408</t>
+    <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77156925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641422271729</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
+    <t xml:space="preserve">9.88919830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
@@ -155,22 +155,22 @@
     <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99842548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">9.99842643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.90600204467773</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.98162269592285</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
@@ -194,31 +194,31 @@
     <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
+    <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.94817066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9901819229126</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">9.02923393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607753753662</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23810005187988</t>
+    <t xml:space="preserve">8.2381010055542</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490772247314</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898963928223</t>
+    <t xml:space="preserve">7.18898868560791</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -341,34 +341,34 @@
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299682617188</t>
+    <t xml:space="preserve">7.10299634933472</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74182748794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.7418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233957290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1553783416748</t>
+    <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.39984083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -581,52 +581,52 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.64435386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101558685303</t>
+    <t xml:space="preserve">3.83101606369019</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">3.81323838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435523986816</t>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435333251953</t>
   </si>
   <si>
     <t xml:space="preserve">9.6371374130249</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
+    <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
     <t xml:space="preserve">9.56152057647705</t>
@@ -101,22 +101,22 @@
     <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -140,55 +140,55 @@
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919830322266</t>
+    <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
+    <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224281311035</t>
@@ -206,19 +206,19 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9901819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
+    <t xml:space="preserve">8.94816970825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -239,46 +239,46 @@
     <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -296,85 +296,85 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
+    <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537239074707</t>
+    <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06860017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299634933472</t>
+    <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -410,49 +410,49 @@
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77622413635254</t>
+    <t xml:space="preserve">6.77622509002686</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">6.89661407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
+    <t xml:space="preserve">7.44696807861328</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377574920654</t>
+    <t xml:space="preserve">7.34377670288086</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233814239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0442943572998</t>
+    <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651096343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77763414382935</t>
+    <t xml:space="preserve">6.26651048660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7776346206665</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
+    <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652040481567</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
+    <t xml:space="preserve">3.99990081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
+    <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868591308594</t>
+    <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
@@ -65,52 +65,52 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033462524414</t>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435333251953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64554023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5363130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
+    <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636459350586</t>
+    <t xml:space="preserve">9.74636363983154</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157115936279</t>
+    <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -149,22 +149,22 @@
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.90600395202637</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -212,40 +212,40 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">9.11522483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77125549316406</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024375915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
@@ -269,28 +269,28 @@
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35848999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.35849094390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -305,25 +305,25 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
+    <t xml:space="preserve">7.30937957763672</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2061882019043</t>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
     <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334939956665</t>
+    <t xml:space="preserve">7.65334987640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41257047653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739347457886</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06860017776489</t>
+    <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9138126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743036270142</t>
+    <t xml:space="preserve">6.94820928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381216049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743083953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941551208496</t>
+    <t xml:space="preserve">6.8794150352478</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77622509002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">6.89661455154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696807861328</t>
+    <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233814239502</t>
+    <t xml:space="preserve">7.78233861923218</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -58698,6 +58698,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2143">
+      <c r="A2143" s="1" t="n">
+        <v>46020.6915393519</v>
+      </c>
+      <c r="B2143" t="n">
+        <v>80545</v>
+      </c>
+      <c r="C2143" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="D2143" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E2143" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2143" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2143" t="s">
+        <v>645</v>
+      </c>
+      <c r="H2143" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.41868591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229434967041</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435333251953</t>
+    <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
@@ -83,28 +83,28 @@
     <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.56151866912842</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636363983154</t>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832685470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -134,10 +134,10 @@
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">10.0320320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
@@ -149,34 +149,34 @@
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488376617432</t>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038330078125</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873649597168</t>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72955989837646</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0742015838623</t>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
@@ -212,40 +212,40 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">9.11522579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77125453948975</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
@@ -269,28 +269,28 @@
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35849094390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.35848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -305,25 +305,25 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
+    <t xml:space="preserve">8.03171920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937957763672</t>
+    <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
     <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334987640381</t>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739347457886</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
+    <t xml:space="preserve">7.06860017776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743083953857</t>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9138126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">6.89661407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696760177612</t>
+    <t xml:space="preserve">7.44696807861328</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
+    <t xml:space="preserve">7.34377670288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233861923218</t>
+    <t xml:space="preserve">7.78233814239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -58700,7 +58700,7 @@
     </row>
     <row r="2143">
       <c r="A2143" s="1" t="n">
-        <v>46020.6915393519</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2143" t="n">
         <v>80545</v>
@@ -58709,7 +58709,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="D2143" t="n">
-        <v>2.65000009536743</v>
+        <v>2.63000011444092</v>
       </c>
       <c r="E2143" t="n">
         <v>2.6800000667572</v>
@@ -58721,6 +58721,32 @@
         <v>645</v>
       </c>
       <c r="H2143" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="1" t="n">
+        <v>46021.6920717593</v>
+      </c>
+      <c r="B2144" t="n">
+        <v>19429</v>
+      </c>
+      <c r="C2144" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2144" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2144" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2144" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G2144" t="s">
+        <v>692</v>
+      </c>
+      <c r="H2144" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229434967041</t>
+    <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074584960938</t>
+    <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
+    <t xml:space="preserve">9.70435333251953</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151866912842</t>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992340087891</t>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992053985596</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832685470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8555908203125</t>
+    <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
     <t xml:space="preserve">9.95641613006592</t>
@@ -134,64 +134,64 @@
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002456665039</t>
+    <t xml:space="preserve">10.0320339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656404495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9984245300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">10.0572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488367080688</t>
   </si>
   <si>
     <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600299835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873554229736</t>
+    <t xml:space="preserve">9.90600395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.78837490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -203,61 +203,61 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522579193115</t>
+    <t xml:space="preserve">9.11522483825684</t>
   </si>
   <si>
     <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77125549316406</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024375915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529956817627</t>
+    <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171920776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735754013062</t>
@@ -332,52 +332,52 @@
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898868560791</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2061882019043</t>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618724822998</t>
   </si>
   <si>
     <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334939956665</t>
+    <t xml:space="preserve">7.65334987640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41257047653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295946121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06860017776489</t>
+    <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820976257324</t>
+    <t xml:space="preserve">6.94820928573608</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941551208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.8794150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77622509002686</t>
+    <t xml:space="preserve">6.75902557373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501838684082</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661407470703</t>
+    <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
     <t xml:space="preserve">7.01700353622437</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696807861328</t>
+    <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233814239502</t>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233861923218</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -58726,7 +58726,7 @@
     </row>
     <row r="2144">
       <c r="A2144" s="1" t="n">
-        <v>46021.6920717593</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B2144" t="n">
         <v>19429</v>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868591308594</t>
+    <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435333251953</t>
+    <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
+    <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193084716797</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992053985596</t>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -113,37 +113,37 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85558986663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.8555908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320339202881</t>
+    <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.88920021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
@@ -152,19 +152,19 @@
     <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488367080688</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600395202637</t>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873649597168</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
+    <t xml:space="preserve">9.78837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,46 +203,46 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94816970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
+    <t xml:space="preserve">9.07420063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9901819229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522483825684</t>
+    <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
     <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024375915527</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125453948975</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
+    <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930484771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -305,61 +305,61 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56735754013062</t>
+    <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
+    <t xml:space="preserve">7.3093786239624</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32657814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.32657766342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53295946121216</t>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
+    <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,25 +389,25 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941598892212</t>
   </si>
   <si>
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260641098022</t>
+    <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836832046509</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.33315134048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7776346206665</t>
+    <t xml:space="preserve">6.26651096343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990081787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
+    <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767627716064</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40187931060791</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234302520752</t>
+    <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -74,43 +74,43 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.6371374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.5363130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -134,55 +134,55 @@
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656404495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9984245300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488367080688</t>
+    <t xml:space="preserve">10.0320339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93960952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">9.90600204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873458862305</t>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837490081787</t>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,46 +203,46 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">8.9901819229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">9.11522483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024471282959</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024375915527</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125453948975</t>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090244293213</t>
+    <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35848999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930484771729</t>
+    <t xml:space="preserve">8.35849094390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -305,52 +305,52 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">7.5673565864563</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3093786239624</t>
+    <t xml:space="preserve">7.30937957763672</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32657766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898963928223</t>
+    <t xml:space="preserve">7.32657814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980592727661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221694946289</t>
+    <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53295993804932</t>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -377,43 +377,43 @@
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9138126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743036270142</t>
+    <t xml:space="preserve">6.94820928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381216049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743083953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941598892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74182748794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.8794150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.98260641098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
+    <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
+    <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696760177612</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836832046509</t>
+    <t xml:space="preserve">7.78233861923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315134048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.33315086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
+    <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651096343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77763414382935</t>
+    <t xml:space="preserve">6.26651048660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7776346206665</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
+    <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -58836,7 +58836,7 @@
     </row>
     <row r="2148">
       <c r="A2148" s="1" t="n">
-        <v>46029.691099537</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2148" t="n">
         <v>11038</v>
@@ -58857,6 +58857,32 @@
         <v>887</v>
       </c>
       <c r="H2148" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2149">
+      <c r="A2149" s="1" t="n">
+        <v>46030.6912037037</v>
+      </c>
+      <c r="B2149" t="n">
+        <v>30894</v>
+      </c>
+      <c r="C2149" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D2149" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E2149" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="F2149" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="G2149" t="s">
+        <v>688</v>
+      </c>
+      <c r="H2149" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.41868591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -74,34 +74,34 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
+    <t xml:space="preserve">9.53631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832685470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,34 +128,34 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93960952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">10.0320320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488386154175</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162078857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
@@ -203,49 +203,49 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0742015838623</t>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9901819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">9.11522579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77125453948975</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
@@ -269,28 +269,28 @@
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35849094390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.35848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -305,25 +305,25 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
+    <t xml:space="preserve">8.03171920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937957763672</t>
+    <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
     <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334987640381</t>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739347457886</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
+    <t xml:space="preserve">7.06860017776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743083953857</t>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9138126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">6.89661407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696760177612</t>
+    <t xml:space="preserve">7.44696807861328</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
+    <t xml:space="preserve">7.34377670288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233861923218</t>
+    <t xml:space="preserve">7.78233814239502</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -58862,7 +58862,7 @@
     </row>
     <row r="2149">
       <c r="A2149" s="1" t="n">
-        <v>46030.6912037037</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2149" t="n">
         <v>30894</v>
@@ -58883,6 +58883,32 @@
         <v>688</v>
       </c>
       <c r="H2149" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" s="1" t="n">
+        <v>46031.6912268518</v>
+      </c>
+      <c r="B2150" t="n">
+        <v>30059</v>
+      </c>
+      <c r="C2150" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D2150" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E2150" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="F2150" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G2150" t="s">
+        <v>637</v>
+      </c>
+      <c r="H2150" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229434967041</t>
+    <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.65394115447998</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234397888184</t>
+    <t xml:space="preserve">9.66234302520752</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435523986816</t>
+    <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
+    <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193084716797</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151866912842</t>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
@@ -101,37 +101,37 @@
     <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198143005371</t>
+    <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
+    <t xml:space="preserve">9.76316738128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8555908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404348373413</t>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997398376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85558986663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95641613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320320129395</t>
@@ -155,46 +155,46 @@
     <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9984245300293</t>
+    <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89759922027588</t>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.83038425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425121307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
+    <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
+    <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07223033905029</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
+    <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607753753662</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
+    <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409381866455</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
+    <t xml:space="preserve">8.13490772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">7.87693119049072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533502578735</t>
+    <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494508743286</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">7.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934364318848</t>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381216049194</t>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
@@ -440,22 +440,22 @@
     <t xml:space="preserve">7.61895275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -58940,7 +58940,7 @@
     </row>
     <row r="2152">
       <c r="A2152" s="1" t="n">
-        <v>46035.691087963</v>
+        <v>46035.3333333333</v>
       </c>
       <c r="B2152" t="n">
         <v>6519</v>
@@ -58961,6 +58961,32 @@
         <v>686</v>
       </c>
       <c r="H2152" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" s="1" t="n">
+        <v>46036.6910069444</v>
+      </c>
+      <c r="B2153" t="n">
+        <v>22722</v>
+      </c>
+      <c r="C2153" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="D2153" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="E2153" t="n">
+        <v>2.9300000667572</v>
+      </c>
+      <c r="F2153" t="n">
+        <v>2.89000010490417</v>
+      </c>
+      <c r="G2153" t="s">
+        <v>887</v>
+      </c>
+      <c r="H2153" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">9.66234302520752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
+    <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.6371374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
+    <t xml:space="preserve">9.82198333740234</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.76316738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997398376465</t>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.85558986663818</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">10.0320320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88920021057129</t>
+    <t xml:space="preserve">9.99002265930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837394714355</t>
+    <t xml:space="preserve">9.78837299346924</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425121307373</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.2012186050415</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969573974609</t>
+    <t xml:space="preserve">8.28969669342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.3412914276123</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
+    <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490772247314</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693119049072</t>
+    <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
     <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70494508743286</t>
+    <t xml:space="preserve">7.70494604110718</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898963928223</t>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
+    <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">7.06859922409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.91381311416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74182748794556</t>
+    <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342317581177</t>
+    <t xml:space="preserve">6.79342269897461</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
@@ -407,37 +407,37 @@
     <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501886367798</t>
+    <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416664123535</t>
+    <t xml:space="preserve">7.46416616439819</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895275115967</t>
+    <t xml:space="preserve">7.61895179748535</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.43836688995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1553783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.15537786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
+    <t xml:space="preserve">7.02204751968384</t>
   </si>
   <si>
     <t xml:space="preserve">6.88871812820435</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
+    <t xml:space="preserve">6.71094417572021</t>
   </si>
   <si>
     <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990105628967</t>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324060440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
   </si>
   <si>
     <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80435013771057</t>
+    <t xml:space="preserve">3.68879747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80434989929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
   </si>
   <si>
     <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71546316146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212091445923</t>
+    <t xml:space="preserve">3.71546292304993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
@@ -58966,7 +58966,7 @@
     </row>
     <row r="2153">
       <c r="A2153" s="1" t="n">
-        <v>46036.6910069444</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2153" t="n">
         <v>22722</v>
@@ -58987,6 +58987,32 @@
         <v>887</v>
       </c>
       <c r="H2153" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" s="1" t="n">
+        <v>46037.6912152778</v>
+      </c>
+      <c r="B2154" t="n">
+        <v>12992</v>
+      </c>
+      <c r="C2154" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="D2154" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="E2154" t="n">
+        <v>2.86999988555908</v>
+      </c>
+      <c r="F2154" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G2154" t="s">
+        <v>637</v>
+      </c>
+      <c r="H2154" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="889">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,91 +53,91 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234493255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033462524414</t>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791118621826</t>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.64553833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316738128662</t>
+    <t xml:space="preserve">9.56151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636554718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77156925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85558986663818</t>
+    <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002265930176</t>
+    <t xml:space="preserve">10.0404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320329666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">10.0488376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89759922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
@@ -176,37 +176,37 @@
     <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72956085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837299346924</t>
+    <t xml:space="preserve">9.62873458862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72955989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837585449219</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626342773438</t>
+    <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
+    <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">9.02923393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.28969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -275,64 +275,64 @@
     <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23810005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490772247314</t>
+    <t xml:space="preserve">8.2381010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097431182861</t>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898868560791</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -341,52 +341,52 @@
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
+    <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
     <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334939956665</t>
+    <t xml:space="preserve">7.65334987640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859922409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381311416626</t>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299682617188</t>
+    <t xml:space="preserve">7.10299634933472</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
@@ -395,31 +395,31 @@
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342269897461</t>
+    <t xml:space="preserve">6.63863563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
+    <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7762246131897</t>
+    <t xml:space="preserve">6.77622413635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -431,37 +431,37 @@
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836688995361</t>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233957290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
+    <t xml:space="preserve">7.066490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">7.022047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.71094465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
+    <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
+    <t xml:space="preserve">5.73319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">4.24878358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.80435013771057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546292304993</t>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -2676,6 +2676,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.89000010490417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79999995231628</t>
   </si>
 </sst>
 </file>
@@ -58992,7 +58995,7 @@
     </row>
     <row r="2154">
       <c r="A2154" s="1" t="n">
-        <v>46037.6912152778</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B2154" t="n">
         <v>12992</v>
@@ -59013,6 +59016,32 @@
         <v>637</v>
       </c>
       <c r="H2154" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" s="1" t="n">
+        <v>46038.6911689815</v>
+      </c>
+      <c r="B2155" t="n">
+        <v>13369</v>
+      </c>
+      <c r="C2155" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D2155" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="E2155" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F2155" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G2155" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2155" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40187931060791</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -50,16 +50,16 @@
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234493255615</t>
+    <t xml:space="preserve">9.45229244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631496429443</t>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950836181641</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.56992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77156925201416</t>
+    <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
@@ -128,25 +128,25 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404367446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320329666138</t>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
+    <t xml:space="preserve">9.88919830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93960952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89759922027588</t>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600204467773</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873458862305</t>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837585449219</t>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.94816970825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9901819229126</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
@@ -224,58 +224,58 @@
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">9.11522483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
+    <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90024471282959</t>
+    <t xml:space="preserve">8.90024375915527</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -284,58 +284,58 @@
     <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35848999023438</t>
+    <t xml:space="preserve">8.35849094390869</t>
   </si>
   <si>
     <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
+    <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693023681641</t>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
     <t xml:space="preserve">7.82533597946167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221742630005</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334987640381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
@@ -362,40 +362,40 @@
     <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9138126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743036270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10299634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87941551208496</t>
+    <t xml:space="preserve">6.96540880203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381216049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743083953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10299682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8794150352478</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -428,13 +428,13 @@
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
+    <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233861923218</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0442943572998</t>
+    <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651096343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77763414382935</t>
+    <t xml:space="preserve">6.26651048660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7776346206665</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
+    <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652040481567</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
+    <t xml:space="preserve">3.99990081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
+    <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
@@ -59157,7 +59157,7 @@
     </row>
     <row r="2160">
       <c r="A2160" s="1" t="n">
-        <v>46045.6909953704</v>
+        <v>46045.3333333333</v>
       </c>
       <c r="B2160" t="n">
         <v>1654</v>
@@ -59178,6 +59178,32 @@
         <v>890</v>
       </c>
       <c r="H2160" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" s="1" t="n">
+        <v>46048.6909953704</v>
+      </c>
+      <c r="B2161" t="n">
+        <v>12402</v>
+      </c>
+      <c r="C2161" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D2161" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="E2161" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="F2161" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="G2161" t="s">
+        <v>645</v>
+      </c>
+      <c r="H2161" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -50,37 +50,37 @@
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.45229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028308868408</t>
+    <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.56152057647705</t>
@@ -98,31 +98,31 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
+    <t xml:space="preserve">9.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -131,43 +131,43 @@
     <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">10.0404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
+    <t xml:space="preserve">9.72955989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425312042236</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420253753662</t>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
@@ -221,43 +221,43 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728328704834</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930484771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
+    <t xml:space="preserve">7.30937814712524</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -335,40 +335,40 @@
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06860017776489</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381311416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.87941551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260641098022</t>
+    <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,25 +416,25 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">6.89661455154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206783294678</t>
+    <t xml:space="preserve">6.22206735610962</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7776346206665</t>
+    <t xml:space="preserve">6.26651096343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652040481567</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990081787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324036598206</t>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
+    <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
@@ -59365,7 +59365,7 @@
     </row>
     <row r="2168">
       <c r="A2168" s="1" t="n">
-        <v>46057.6008449074</v>
+        <v>46057.3333333333</v>
       </c>
       <c r="B2168" t="n">
         <v>15166</v>
@@ -59386,6 +59386,32 @@
         <v>883</v>
       </c>
       <c r="H2168" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="1" t="n">
+        <v>46058.601412037</v>
+      </c>
+      <c r="B2169" t="n">
+        <v>1812</v>
+      </c>
+      <c r="C2169" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D2169" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="E2169" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F2169" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G2169" t="s">
+        <v>646</v>
+      </c>
+      <c r="H2169" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033462524414</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
+    <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193084716797</t>
@@ -89,61 +89,61 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992340087891</t>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198333740234</t>
+    <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
+    <t xml:space="preserve">9.76316738128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8555908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404367446899</t>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997398376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85558986663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95641613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88920021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9984245300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">10.0656414031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
@@ -179,37 +179,37 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425121307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.11621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018001556396</t>
+    <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
+    <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07223033905029</t>
@@ -251,46 +251,46 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930484771729</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,85 +302,85 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
+    <t xml:space="preserve">8.13490772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898963928223</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136377334595</t>
+    <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41257047653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06860017776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381311416626</t>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">6.98260641098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902557373047</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895275115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035346984863</t>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15537786483765</t>
+    <t xml:space="preserve">7.1553783416748</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.31095457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.73319101333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -581,52 +581,52 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
+    <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.73324060440063</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101606369019</t>
+    <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">3.81323862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -59391,7 +59391,7 @@
     </row>
     <row r="2169">
       <c r="A2169" s="1" t="n">
-        <v>46058.601412037</v>
+        <v>46058.3333333333</v>
       </c>
       <c r="B2169" t="n">
         <v>1812</v>
@@ -59412,6 +59412,32 @@
         <v>646</v>
       </c>
       <c r="H2169" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="1" t="n">
+        <v>46059.6910648148</v>
+      </c>
+      <c r="B2170" t="n">
+        <v>4953</v>
+      </c>
+      <c r="C2170" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="D2170" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="E2170" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="F2170" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="G2170" t="s">
+        <v>646</v>
+      </c>
+      <c r="H2170" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234302520752</t>
+    <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
@@ -68,43 +68,43 @@
     <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033462524414</t>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636459350586</t>
+    <t xml:space="preserve">9.74636554718018</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -113,34 +113,34 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997398376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85558986663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8555908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320320129395</t>
+    <t xml:space="preserve">10.0320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88920021057129</t>
+    <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
+    <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837394714355</t>
+    <t xml:space="preserve">9.78837299346924</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425121307373</t>
+    <t xml:space="preserve">9.32626247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607753753662</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529956817627</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490772247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533645629883</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494508743286</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
+    <t xml:space="preserve">7.30937957763672</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097478866577</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898963928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221742630005</t>
@@ -350,22 +350,22 @@
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136425018311</t>
+    <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296089172363</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739347457886</t>
+    <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74182748794556</t>
+    <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
+    <t xml:space="preserve">7.05140018463135</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902557373047</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895275115967</t>
+    <t xml:space="preserve">7.44696807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035394668579</t>
+    <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -59417,7 +59417,7 @@
     </row>
     <row r="2170">
       <c r="A2170" s="1" t="n">
-        <v>46059.6910648148</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2170" t="n">
         <v>4953</v>
@@ -59438,6 +59438,32 @@
         <v>646</v>
       </c>
       <c r="H2170" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="1" t="n">
+        <v>46062.69125</v>
+      </c>
+      <c r="B2171" t="n">
+        <v>59792</v>
+      </c>
+      <c r="C2171" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="D2171" t="n">
+        <v>2.3199999332428</v>
+      </c>
+      <c r="E2171" t="n">
+        <v>2.51999998092651</v>
+      </c>
+      <c r="F2171" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="G2171" t="s">
+        <v>665</v>
+      </c>
+      <c r="H2171" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="892">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074584960938</t>
+    <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6371374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.70435333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950836181641</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440677642822</t>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,13 +128,13 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320339202881</t>
+    <t xml:space="preserve">9.95641613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
@@ -143,13 +143,13 @@
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057240486145</t>
+    <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">10.0488376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837299346924</t>
+    <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
+    <t xml:space="preserve">9.32626152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
+    <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">8.99018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -230,16 +230,16 @@
     <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
+    <t xml:space="preserve">9.02923393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
+    <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23810005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937957763672</t>
+    <t xml:space="preserve">8.2381010055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097478866577</t>
@@ -332,34 +332,34 @@
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296089172363</t>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299682617188</t>
+    <t xml:space="preserve">7.10299634933472</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696807861328</t>
+    <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233957290649</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1553783416748</t>
+    <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.39984083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -581,52 +581,52 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.64435386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101558685303</t>
+    <t xml:space="preserve">3.83101606369019</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">3.81323838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -2685,6 +2685,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.76999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48000001907349</t>
   </si>
 </sst>
 </file>
@@ -59443,7 +59446,7 @@
     </row>
     <row r="2171">
       <c r="A2171" s="1" t="n">
-        <v>46062.69125</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B2171" t="n">
         <v>59792</v>
@@ -59464,6 +59467,32 @@
         <v>665</v>
       </c>
       <c r="H2171" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="1" t="n">
+        <v>46063.6910069444</v>
+      </c>
+      <c r="B2172" t="n">
+        <v>14520</v>
+      </c>
+      <c r="C2172" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="D2172" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E2172" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="F2172" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="G2172" t="s">
+        <v>891</v>
+      </c>
+      <c r="H2172" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="892">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="893">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,34 +44,34 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.45229244232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.5783224105835</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.737961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435333251953</t>
+    <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950836181641</t>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51951026916504</t>
   </si>
   <si>
     <t xml:space="preserve">9.49430465698242</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832704544067</t>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440582275391</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404367446899</t>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837490081787</t>
+    <t xml:space="preserve">9.78837299346924</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626152038574</t>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41619968414307</t>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41619873046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -236,49 +236,49 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -296,64 +296,64 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490962982178</t>
+    <t xml:space="preserve">8.23810005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898868560791</t>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657766342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
@@ -362,19 +362,19 @@
     <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29217958450317</t>
+    <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859922409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299634933472</t>
+    <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
@@ -395,31 +395,31 @@
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342317581177</t>
+    <t xml:space="preserve">6.63863611221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342269897461</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -431,37 +431,37 @@
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836688995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.31095457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
+    <t xml:space="preserve">5.95540761947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -2688,6 +2688,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.48000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5</t>
   </si>
 </sst>
 </file>
@@ -59472,7 +59475,7 @@
     </row>
     <row r="2172">
       <c r="A2172" s="1" t="n">
-        <v>46063.6910069444</v>
+        <v>46063.3333333333</v>
       </c>
       <c r="B2172" t="n">
         <v>14520</v>
@@ -59493,6 +59496,32 @@
         <v>891</v>
       </c>
       <c r="H2172" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="1" t="n">
+        <v>46064.6911689815</v>
+      </c>
+      <c r="B2173" t="n">
+        <v>30223</v>
+      </c>
+      <c r="C2173" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D2173" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2173" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2173" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2173" t="s">
+        <v>892</v>
+      </c>
+      <c r="H2173" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="894">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,34 +44,34 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229244232178</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4186840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5783224105835</t>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.73796367645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435428619385</t>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435523986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
@@ -89,37 +89,37 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51951026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198238372803</t>
+    <t xml:space="preserve">9.41028213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636554718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198333740234</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
+    <t xml:space="preserve">10.0404367446899</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837299346924</t>
+    <t xml:space="preserve">9.72955989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
+    <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018001556396</t>
+    <t xml:space="preserve">8.94817066192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619873046875</t>
+    <t xml:space="preserve">9.41620063781738</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">8.98623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
+    <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -299,67 +299,67 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
   </si>
   <si>
     <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937814712524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
+    <t xml:space="preserve">7.36097526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980545043945</t>
+    <t xml:space="preserve">6.99980592727661</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.53296089172363</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859922409058</t>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06860017776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820976257324</t>
+    <t xml:space="preserve">6.94820928573608</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,37 +389,37 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941551208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.8794150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501791000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,40 +428,40 @@
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416616439819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836688995361</t>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233957290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
+    <t xml:space="preserve">7.066490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">7.022047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.71094465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
+    <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
+    <t xml:space="preserve">5.73319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">4.24878358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.80435013771057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546292304993</t>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -2691,6 +2691,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49000000953674</t>
   </si>
 </sst>
 </file>
@@ -59501,7 +59504,7 @@
     </row>
     <row r="2173">
       <c r="A2173" s="1" t="n">
-        <v>46064.6911689815</v>
+        <v>46064.3333333333</v>
       </c>
       <c r="B2173" t="n">
         <v>30223</v>
@@ -59522,6 +59525,32 @@
         <v>892</v>
       </c>
       <c r="H2173" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="1" t="n">
+        <v>46065.6910416667</v>
+      </c>
+      <c r="B2174" t="n">
+        <v>3048</v>
+      </c>
+      <c r="C2174" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="D2174" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="E2174" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F2174" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="G2174" t="s">
+        <v>893</v>
+      </c>
+      <c r="H2174" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4186840057373</t>
+    <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
@@ -56,25 +56,25 @@
     <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796367645264</t>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.62033367156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
@@ -83,46 +83,46 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553928375244</t>
+    <t xml:space="preserve">9.64554023742676</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430274963379</t>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157020568848</t>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157115936279</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316928863525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">10.1832714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404367446899</t>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057240486145</t>
+    <t xml:space="preserve">9.87239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,16 +158,16 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
+    <t xml:space="preserve">10.0488367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626342773438</t>
+    <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -215,25 +215,25 @@
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8572473526001</t>
+    <t xml:space="preserve">8.98623561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85724830627441</t>
   </si>
   <si>
     <t xml:space="preserve">8.94324016571045</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533597946167</t>
+    <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5673565864563</t>
+    <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.3093786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898963928223</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980592727661</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296089172363</t>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06860017776489</t>
+    <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
+    <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,73 +389,73 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.77622413635254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501791000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
+    <t xml:space="preserve">7.46416568756104</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
+    <t xml:space="preserve">7.61895275115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
+    <t xml:space="preserve">7.33315134048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.37759494781494</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
+    <t xml:space="preserve">7.5553674697876</t>
   </si>
   <si>
     <t xml:space="preserve">7.46648025512695</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
+    <t xml:space="preserve">5.95540761947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -578,31 +578,31 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
+    <t xml:space="preserve">3.78657269477844</t>
   </si>
   <si>
     <t xml:space="preserve">3.99990034103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89323687553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73324012756348</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212361335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -686,31 +686,31 @@
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767627716064</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -59530,7 +59530,7 @@
     </row>
     <row r="2174">
       <c r="A2174" s="1" t="n">
-        <v>46065.6910416667</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B2174" t="n">
         <v>3048</v>
@@ -59551,6 +59551,32 @@
         <v>893</v>
       </c>
       <c r="H2174" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="1" t="n">
+        <v>46066.6913078704</v>
+      </c>
+      <c r="B2175" t="n">
+        <v>18565</v>
+      </c>
+      <c r="C2175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D2175" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="E2175" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="F2175" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="G2175" t="s">
+        <v>893</v>
+      </c>
+      <c r="H2175" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033271789551</t>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
+    <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193084716797</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -101,28 +101,28 @@
     <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832714080811</t>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636554718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77156925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">9.77997398376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
+    <t xml:space="preserve">10.0404367446899</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -140,40 +140,40 @@
     <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919925689697</t>
+    <t xml:space="preserve">9.88920021057129</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">9.87239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488367080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.97321796417236</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425121307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
+    <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -254,43 +254,43 @@
     <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930484771729</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490772247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">7.87693119049072</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
@@ -323,58 +323,58 @@
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3093786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898963928223</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136377334595</t>
+    <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256999969482</t>
+    <t xml:space="preserve">7.41256952285767</t>
   </si>
   <si>
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -389,31 +389,31 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941598892212</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.98260641098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
+    <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416616439819</t>
+    <t xml:space="preserve">7.24058532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
+    <t xml:space="preserve">7.61895275115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035346984863</t>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836832046509</t>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315134048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.33315086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15537786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.11093425750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1553783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.066490650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984083175659</t>
+    <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428443908691</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.73319101333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
+    <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324060440063</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">3.98212313652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323838233948</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323862075806</t>
   </si>
   <si>
     <t xml:space="preserve">4.06212091445923</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767532348633</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -59634,7 +59634,7 @@
     </row>
     <row r="2178">
       <c r="A2178" s="1" t="n">
-        <v>46071.6822106481</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B2178" t="n">
         <v>9404</v>
@@ -59655,6 +59655,32 @@
         <v>891</v>
       </c>
       <c r="H2178" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="1" t="n">
+        <v>46072.6870138889</v>
+      </c>
+      <c r="B2179" t="n">
+        <v>31604</v>
+      </c>
+      <c r="C2179" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="D2179" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="E2179" t="n">
+        <v>2.49000000953674</v>
+      </c>
+      <c r="F2179" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G2179" t="s">
+        <v>877</v>
+      </c>
+      <c r="H2179" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.45229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791213989258</t>
+    <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193084716797</t>
@@ -89,40 +89,40 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028308868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.41028213500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77156925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316738128662</t>
+    <t xml:space="preserve">9.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997398376465</t>
+    <t xml:space="preserve">9.91440391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -134,82 +134,82 @@
     <t xml:space="preserve">10.0404367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320329666138</t>
+    <t xml:space="preserve">10.0320320129395</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88920021057129</t>
+    <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321796417236</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
+    <t xml:space="preserve">9.72955989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626342773438</t>
+    <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425121307373</t>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
+    <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.94816970825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
+    <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07223033905029</t>
@@ -251,46 +251,46 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32409381866455</t>
+    <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930484771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,85 +302,85 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490772247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898963928223</t>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136425018311</t>
+    <t xml:space="preserve">7.48136377334595</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">7.06860017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.91381311416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140066146851</t>
+    <t xml:space="preserve">6.98260688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902557373047</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">6.84501838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895275115967</t>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976903915405</t>
+    <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035394668579</t>
+    <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1553783416748</t>
+    <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.39984083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206783294678</t>
+    <t xml:space="preserve">6.31095409393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206735610962</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -581,52 +581,52 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.64435386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101558685303</t>
+    <t xml:space="preserve">3.83101606369019</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">3.81323838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -59660,7 +59660,7 @@
     </row>
     <row r="2179">
       <c r="A2179" s="1" t="n">
-        <v>46072.6870138889</v>
+        <v>46072.3333333333</v>
       </c>
       <c r="B2179" t="n">
         <v>31604</v>
@@ -59681,6 +59681,32 @@
         <v>877</v>
       </c>
       <c r="H2179" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="1" t="n">
+        <v>46073.6737847222</v>
+      </c>
+      <c r="B2180" t="n">
+        <v>24365</v>
+      </c>
+      <c r="C2180" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="D2180" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="E2180" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F2180" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G2180" t="s">
+        <v>880</v>
+      </c>
+      <c r="H2180" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -50,40 +50,40 @@
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5783224105835</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553928375244</t>
+    <t xml:space="preserve">9.70435428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6371374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64554023742676</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.56151962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -116,49 +116,49 @@
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832704544067</t>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320339202881</t>
+    <t xml:space="preserve">9.95641613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404348373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919830322266</t>
+    <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656414031982</t>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656394958496</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -170,22 +170,22 @@
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.98162078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873458862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425407409668</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,43 +203,43 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420253753662</t>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">8.99018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,34 +248,34 @@
     <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923393249512</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45919704437256</t>
+    <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49607849121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.49607753753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090244293213</t>
+    <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.4100866317749</t>
   </si>
   <si>
     <t xml:space="preserve">8.16930675506592</t>
@@ -299,88 +299,88 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
+    <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657814025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657766342163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
   </si>
   <si>
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06860017776489</t>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859922409058</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.79342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902652740479</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89661407470703</t>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
     <t xml:space="preserve">7.01700401306152</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
+    <t xml:space="preserve">7.61895179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377670288086</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976856231689</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233861923218</t>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836736679077</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
     <t xml:space="preserve">7.46648073196411</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,49 +527,49 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
+    <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
     <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7776346206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.77763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -614,52 +614,52 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990081787109</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85768222808838</t>
+    <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -59738,7 +59738,7 @@
     </row>
     <row r="2182">
       <c r="A2182" s="1" t="n">
-        <v>46077.4320601852</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B2182" t="n">
         <v>1270</v>
@@ -59759,6 +59759,32 @@
         <v>643</v>
       </c>
       <c r="H2182" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="1" t="n">
+        <v>46078.6911458333</v>
+      </c>
+      <c r="B2183" t="n">
+        <v>13082</v>
+      </c>
+      <c r="C2183" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D2183" t="n">
+        <v>2.57999992370605</v>
+      </c>
+      <c r="E2183" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="F2183" t="n">
+        <v>2.74000000953674</v>
+      </c>
+      <c r="G2183" t="s">
+        <v>878</v>
+      </c>
+      <c r="H2183" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40187931060791</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229244232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.65394115447998</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234302520752</t>
+    <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.737961769104</t>
@@ -71,34 +71,34 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.70435333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713645935059</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553833007812</t>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4102840423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151962280273</t>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56152057647705</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157020568848</t>
+    <t xml:space="preserve">9.77157115936279</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85558986663818</t>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.9564151763916</t>
@@ -134,19 +134,19 @@
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
+    <t xml:space="preserve">10.0320339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919830322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239551544189</t>
+    <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038425445557</t>
+    <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837299346924</t>
+    <t xml:space="preserve">9.62873554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
+    <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425312042236</t>
@@ -200,34 +200,34 @@
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
+    <t xml:space="preserve">9.1162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420253753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018001556396</t>
+    <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619968414307</t>
+    <t xml:space="preserve">9.41620063781738</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623561859131</t>
+    <t xml:space="preserve">8.98623752593994</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825717926025</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02923393249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
@@ -269,28 +269,28 @@
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090339660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35848903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,25 +299,25 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
+    <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87692975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
@@ -326,28 +326,28 @@
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20618772506714</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
     <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334939956665</t>
+    <t xml:space="preserve">7.65334892272949</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
@@ -365,22 +365,22 @@
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381311416626</t>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06860017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381216049194</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941551208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74182748794556</t>
+    <t xml:space="preserve">6.8794150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
+    <t xml:space="preserve">6.89661407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058485031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233861923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1553783416748</t>
+    <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28870725631714</t>
+    <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536794662476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650104522705</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650056838989</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428443908691</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
+    <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1776237487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26651096343994</t>
+    <t xml:space="preserve">6.17762422561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26651048660278</t>
   </si>
   <si>
     <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77763414382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.7776346206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990105628967</t>
+    <t xml:space="preserve">3.99990081787109</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879723548889</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
+    <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
     <t xml:space="preserve">3.98212313652039</t>
@@ -683,25 +683,25 @@
     <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212488174438</t>
+    <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101558685303</t>
+    <t xml:space="preserve">3.83101606369019</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
+    <t xml:space="preserve">3.81323838233948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -59868,7 +59868,7 @@
     </row>
     <row r="2187">
       <c r="A2187" s="1" t="n">
-        <v>46084.6474652778</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B2187" t="n">
         <v>25457</v>
@@ -59889,6 +59889,32 @@
         <v>884</v>
       </c>
       <c r="H2187" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="1" t="n">
+        <v>46085.687025463</v>
+      </c>
+      <c r="B2188" t="n">
+        <v>7212</v>
+      </c>
+      <c r="C2188" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="D2188" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="E2188" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="F2188" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="G2188" t="s">
+        <v>884</v>
+      </c>
+      <c r="H2188" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -47,46 +47,46 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.4186840057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435333251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713645935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.70435428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
+    <t xml:space="preserve">9.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316928863525</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832704544067</t>
@@ -131,52 +131,52 @@
     <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">10.0404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320329666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
+    <t xml:space="preserve">10.0488376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873554229736</t>
+    <t xml:space="preserve">9.97321796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.72956085205078</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425312042236</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420253753662</t>
+    <t xml:space="preserve">9.11621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
@@ -221,43 +221,43 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728328704834</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930484771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
+    <t xml:space="preserve">7.30937814712524</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -335,40 +335,40 @@
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41257047653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06860017776489</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381311416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.87941551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
@@ -401,13 +401,13 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260641098022</t>
+    <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,25 +416,25 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">6.89661455154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206783294678</t>
+    <t xml:space="preserve">6.22206735610962</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7776346206665</t>
+    <t xml:space="preserve">6.26651096343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652040481567</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990081787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324036598206</t>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
+    <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
@@ -59894,7 +59894,7 @@
     </row>
     <row r="2188">
       <c r="A2188" s="1" t="n">
-        <v>46085.687025463</v>
+        <v>46085.3333333333</v>
       </c>
       <c r="B2188" t="n">
         <v>7212</v>
@@ -59915,6 +59915,32 @@
         <v>884</v>
       </c>
       <c r="H2188" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="1" t="n">
+        <v>46086.6829282407</v>
+      </c>
+      <c r="B2189" t="n">
+        <v>12612</v>
+      </c>
+      <c r="C2189" t="n">
+        <v>2.69000005722046</v>
+      </c>
+      <c r="D2189" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="E2189" t="n">
+        <v>2.54999995231628</v>
+      </c>
+      <c r="F2189" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="G2189" t="s">
+        <v>877</v>
+      </c>
+      <c r="H2189" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -47,25 +47,25 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4186840057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
+    <t xml:space="preserve">9.41868495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -74,40 +74,40 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.6371374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64554023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.56151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198333740234</t>
+    <t xml:space="preserve">9.82198143005371</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404367446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320329666138</t>
+    <t xml:space="preserve">9.95641613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320339202881</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">9.88920021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572385787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">9.89760112762451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.90600204467773</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321796417236</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873649597168</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837394714355</t>
+    <t xml:space="preserve">9.78837299346924</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,19 +203,19 @@
     <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94816970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018001556396</t>
+    <t xml:space="preserve">9.0742015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9901819229126</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -227,19 +227,19 @@
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623657226562</t>
+    <t xml:space="preserve">8.98623561859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8572473526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">8.85724830627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529956817627</t>
+    <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16930484771729</t>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,40 +302,40 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.3093786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
+    <t xml:space="preserve">7.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41257047653198</t>
+    <t xml:space="preserve">7.65334892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
     <t xml:space="preserve">7.53296041488647</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06860017776489</t>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381311416626</t>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -395,31 +395,31 @@
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75902557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77622413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -431,22 +431,22 @@
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416664123535</t>
+    <t xml:space="preserve">7.46416568756104</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
+    <t xml:space="preserve">7.61895275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
+    <t xml:space="preserve">7.33315134048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.37759494781494</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
+    <t xml:space="preserve">7.5553674697876</t>
   </si>
   <si>
     <t xml:space="preserve">7.46648025512695</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
+    <t xml:space="preserve">5.95540761947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -578,31 +578,31 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
+    <t xml:space="preserve">3.78657269477844</t>
   </si>
   <si>
     <t xml:space="preserve">3.99990034103394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89323687553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73324012756348</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212361335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -686,31 +686,31 @@
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767627716064</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -59920,7 +59920,7 @@
     </row>
     <row r="2189">
       <c r="A2189" s="1" t="n">
-        <v>46086.6829282407</v>
+        <v>46086.3333333333</v>
       </c>
       <c r="B2189" t="n">
         <v>12612</v>
@@ -59941,6 +59941,32 @@
         <v>877</v>
       </c>
       <c r="H2189" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="1" t="n">
+        <v>46087.6750578704</v>
+      </c>
+      <c r="B2190" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2190" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="D2190" t="n">
+        <v>2.52999997138977</v>
+      </c>
+      <c r="E2190" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="F2190" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="G2190" t="s">
+        <v>692</v>
+      </c>
+      <c r="H2190" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40187931060791</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -62,31 +62,31 @@
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
+    <t xml:space="preserve">9.6371374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.64554023742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">9.49430274963379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
+    <t xml:space="preserve">9.82198143005371</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157115936279</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832704544067</t>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
+    <t xml:space="preserve">10.040433883667</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
@@ -173,40 +173,40 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.97322082519531</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873649597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
+    <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.9901819229126</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024566650391</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
+    <t xml:space="preserve">8.28969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090148925781</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
+    <t xml:space="preserve">7.87692975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
@@ -323,34 +323,34 @@
     <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3093786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65335035324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
+    <t xml:space="preserve">7.73934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218053817749</t>
+    <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859970092773</t>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859922409058</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
@@ -389,19 +389,19 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941598892212</t>
+    <t xml:space="preserve">6.8794150352478</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.63863563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.01700401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416568756104</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.61895179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976951599121</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.78234004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -59969,7 +59969,7 @@
     </row>
     <row r="2191">
       <c r="A2191" s="1" t="n">
-        <v>46090.5555555556</v>
+        <v>46090.3333333333</v>
       </c>
       <c r="B2191" t="n">
         <v>5276</v>
@@ -59990,6 +59990,32 @@
         <v>884</v>
       </c>
       <c r="H2191" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="1" t="n">
+        <v>46091.6910532407</v>
+      </c>
+      <c r="B2192" t="n">
+        <v>54392</v>
+      </c>
+      <c r="C2192" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D2192" t="n">
+        <v>2.55999994277954</v>
+      </c>
+      <c r="E2192" t="n">
+        <v>2.63000011444092</v>
+      </c>
+      <c r="F2192" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2192" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2192" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44389152526855</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
+    <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033462524414</t>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">9.64554023742676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631496429443</t>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430274963379</t>
+    <t xml:space="preserve">9.51951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">9.77157115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
+    <t xml:space="preserve">9.76316738128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -131,34 +131,34 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.040433883667</t>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057240486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656414031982</t>
+    <t xml:space="preserve">10.0572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -173,28 +173,28 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97322082519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873649597168</t>
+    <t xml:space="preserve">9.973219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.78837299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9901819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -59995,7 +59995,7 @@
     </row>
     <row r="2192">
       <c r="A2192" s="1" t="n">
-        <v>46091.6910532407</v>
+        <v>46091.3333333333</v>
       </c>
       <c r="B2192" t="n">
         <v>54392</v>
@@ -60016,6 +60016,32 @@
         <v>888</v>
       </c>
       <c r="H2192" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="1" t="n">
+        <v>46092.6836458333</v>
+      </c>
+      <c r="B2193" t="n">
+        <v>7306</v>
+      </c>
+      <c r="C2193" t="n">
+        <v>2.82999992370605</v>
+      </c>
+      <c r="D2193" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="E2193" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="F2193" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2193" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2193" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="894">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="895">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229244232178</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796367645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -71,25 +71,25 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.70435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028308868408</t>
+    <t xml:space="preserve">9.53631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157020568848</t>
+    <t xml:space="preserve">9.77157115936279</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316928863525</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997398376465</t>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
+    <t xml:space="preserve">10.0404348373413</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239456176758</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
+    <t xml:space="preserve">10.0488367080688</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -170,13 +170,13 @@
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873649597168</t>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72956085205078</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626342773438</t>
@@ -200,40 +200,40 @@
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">9.11621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619873046875</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623657226562</t>
+    <t xml:space="preserve">8.98623561859131</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8572473526001</t>
+    <t xml:space="preserve">8.85724830627441</t>
   </si>
   <si>
     <t xml:space="preserve">8.94324016571045</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02923202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
+    <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490867614746</t>
@@ -314,46 +314,46 @@
     <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70494604110718</t>
+    <t xml:space="preserve">7.70494556427002</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097431182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3093786239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859922409058</t>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
@@ -392,25 +392,25 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342269897461</t>
+    <t xml:space="preserve">6.74182748794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
+    <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7762246131897</t>
+    <t xml:space="preserve">6.77622413635254</t>
   </si>
   <si>
     <t xml:space="preserve">6.84501886367798</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
+    <t xml:space="preserve">7.01700353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058485031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416568756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634628295898</t>
+    <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836688995361</t>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33315086364746</t>
+    <t xml:space="preserve">7.64425468444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33315134048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.37759494781494</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
+    <t xml:space="preserve">7.022047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
@@ -521,31 +521,31 @@
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.71094465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
+    <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
+    <t xml:space="preserve">5.73319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221275806427</t>
+    <t xml:space="preserve">4.24878358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
     <t xml:space="preserve">3.78657269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990057945251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
   </si>
   <si>
     <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">3.73324012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80434989929199</t>
+    <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
+    <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
     <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212535858154</t>
+    <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434743881226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546292304993</t>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
+    <t xml:space="preserve">4.06212091445923</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -2694,6 +2694,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.49000000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
 </sst>
 </file>
@@ -60050,7 +60053,7 @@
     </row>
     <row r="2194">
       <c r="A2194" s="1" t="n">
-        <v>46093.68125</v>
+        <v>46093.3333333333</v>
       </c>
       <c r="B2194" t="n">
         <v>14316</v>
@@ -60071,6 +60074,56 @@
         <v>640</v>
       </c>
       <c r="H2194" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="1" t="n">
+        <v>46094.3333333333</v>
+      </c>
+      <c r="B2195" t="n">
+        <v>13124</v>
+      </c>
+      <c r="C2195" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2195" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2195" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2195"/>
+      <c r="G2195" t="s">
+        <v>894</v>
+      </c>
+      <c r="H2195" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="1" t="n">
+        <v>46094.6910300926</v>
+      </c>
+      <c r="B2196" t="n">
+        <v>13124</v>
+      </c>
+      <c r="C2196" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2196" t="n">
+        <v>2.66000008583069</v>
+      </c>
+      <c r="E2196" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F2196" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="G2196" t="s">
+        <v>886</v>
+      </c>
+      <c r="H2196" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -56,25 +56,25 @@
     <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73796367645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
+    <t xml:space="preserve">9.5783224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.70435428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
+    <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
+    <t xml:space="preserve">9.51951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430274963379</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992244720459</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
+    <t xml:space="preserve">9.82198333740234</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157115936279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316928863525</t>
+    <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997207641602</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404348373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002456665039</t>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
@@ -146,76 +146,76 @@
     <t xml:space="preserve">9.93961143493652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488367080688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
+    <t xml:space="preserve">9.72955989837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626342773438</t>
+    <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420253753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94817066192627</t>
+    <t xml:space="preserve">9.1162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623561859131</t>
+    <t xml:space="preserve">8.98623657226562</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85724830627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94324016571045</t>
+    <t xml:space="preserve">8.8572473526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94323921203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07222938537598</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.16930484771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494556427002</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">7.3093786239624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657814025879</t>
+    <t xml:space="preserve">7.36097526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657766342163</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898963928223</t>
@@ -347,19 +347,19 @@
     <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214365005493</t>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136377334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941551208496</t>
+    <t xml:space="preserve">6.87941598892212</t>
   </si>
   <si>
     <t xml:space="preserve">6.74182748794556</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260641098022</t>
+    <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501886367798</t>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836832046509</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -60093,9 +60093,11 @@
       <c r="E2195" t="n">
         <v>2.77999997138977</v>
       </c>
-      <c r="F2195"/>
+      <c r="F2195" t="n">
+        <v>2.72000002861023</v>
+      </c>
       <c r="G2195" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60103,27 +60105,51 @@
     </row>
     <row r="2196">
       <c r="A2196" s="1" t="n">
-        <v>46094.6910300926</v>
+        <v>46097.3333333333</v>
       </c>
       <c r="B2196" t="n">
-        <v>13124</v>
+        <v>25019</v>
       </c>
       <c r="C2196" t="n">
-        <v>2.77999997138977</v>
+        <v>2.76999998092651</v>
       </c>
       <c r="D2196" t="n">
-        <v>2.66000008583069</v>
+        <v>2.60999989509583</v>
       </c>
       <c r="E2196" t="n">
-        <v>2.77999997138977</v>
-      </c>
-      <c r="F2196" t="n">
-        <v>2.72000002861023</v>
-      </c>
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2196"/>
       <c r="G2196" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="H2196" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="1" t="n">
+        <v>46097.694224537</v>
+      </c>
+      <c r="B2197" t="n">
+        <v>25019</v>
+      </c>
+      <c r="C2197" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="D2197" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="E2197" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2197" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="G2197" t="s">
+        <v>880</v>
+      </c>
+      <c r="H2197" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40187931060791</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -53,19 +53,19 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5783224105835</t>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
+    <t xml:space="preserve">9.737961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
     <t xml:space="preserve">9.62033367156982</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
@@ -89,82 +89,82 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028308868408</t>
+    <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51951026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636554718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.77997398376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961143493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
+    <t xml:space="preserve">10.0320329666138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961048126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.9984245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488367080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600395202637</t>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.97321796417236</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
+    <t xml:space="preserve">9.78837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">9.0742015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
@@ -221,40 +221,40 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619968414307</t>
+    <t xml:space="preserve">9.41620063781738</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">8.98623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02923393249512</t>
   </si>
   <si>
     <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
@@ -266,10 +266,10 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930484771729</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -305,34 +305,34 @@
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693166732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3093786239624</t>
+    <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32657766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898963928223</t>
+    <t xml:space="preserve">7.32657814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980592727661</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
+    <t xml:space="preserve">7.06860017776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.94820928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381216049194</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -389,19 +389,19 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941598892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74182748794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.8794150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89661455154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">6.89661407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035346984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836832046509</t>
+    <t xml:space="preserve">7.61035394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233861923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315134048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.33315086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
+    <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651096343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77763414382935</t>
+    <t xml:space="preserve">6.26651048660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7776346206665</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
+    <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -60119,9 +60119,11 @@
       <c r="E2196" t="n">
         <v>2.60999989509583</v>
       </c>
-      <c r="F2196"/>
+      <c r="F2196" t="n">
+        <v>2.70000004768372</v>
+      </c>
       <c r="G2196" t="s">
-        <v>894</v>
+        <v>880</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60129,27 +60131,51 @@
     </row>
     <row r="2197">
       <c r="A2197" s="1" t="n">
-        <v>46097.694224537</v>
+        <v>46098.3333333333</v>
       </c>
       <c r="B2197" t="n">
-        <v>25019</v>
+        <v>19666</v>
       </c>
       <c r="C2197" t="n">
-        <v>2.76999998092651</v>
+        <v>2.75</v>
       </c>
       <c r="D2197" t="n">
-        <v>2.60999989509583</v>
+        <v>2.70000004768372</v>
       </c>
       <c r="E2197" t="n">
-        <v>2.60999989509583</v>
-      </c>
-      <c r="F2197" t="n">
         <v>2.70000004768372</v>
       </c>
+      <c r="F2197"/>
       <c r="G2197" t="s">
-        <v>880</v>
+        <v>894</v>
       </c>
       <c r="H2197" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="1" t="n">
+        <v>46098.6911226852</v>
+      </c>
+      <c r="B2198" t="n">
+        <v>19666</v>
+      </c>
+      <c r="C2198" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D2198" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="E2198" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="F2198" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G2198" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2198" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.44389152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229244232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -74,22 +74,22 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028213500977</t>
+    <t xml:space="preserve">9.5363130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997398376465</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919830322266</t>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057240486145</t>
+    <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9984245300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">9.99842548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83038425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
+    <t xml:space="preserve">9.83038520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
+    <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.41619873046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923393249512</t>
+    <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">9.2012186050415</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
+    <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657814025879</t>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657766342163</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
@@ -347,40 +347,40 @@
     <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334892272949</t>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06860017776489</t>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859922409058</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342317581177</t>
+    <t xml:space="preserve">6.79342269897461</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
+    <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89661407470703</t>
+    <t xml:space="preserve">6.69023132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416616439819</t>
@@ -437,37 +437,37 @@
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
+    <t xml:space="preserve">7.61895132064819</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836688995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
     <t xml:space="preserve">7.46648073196411</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,49 +527,49 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
+    <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
     <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7776346206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.77763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -614,52 +614,52 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990081787109</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85768222808838</t>
+    <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -60137,7 +60137,7 @@
         <v>19666</v>
       </c>
       <c r="C2197" t="n">
-        <v>2.75</v>
+        <v>2.79999995231628</v>
       </c>
       <c r="D2197" t="n">
         <v>2.70000004768372</v>
@@ -60145,9 +60145,11 @@
       <c r="E2197" t="n">
         <v>2.70000004768372</v>
       </c>
-      <c r="F2197"/>
+      <c r="F2197" t="n">
+        <v>2.79999995231628</v>
+      </c>
       <c r="G2197" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60155,27 +60157,51 @@
     </row>
     <row r="2198">
       <c r="A2198" s="1" t="n">
-        <v>46098.6911226852</v>
+        <v>46099.3333333333</v>
       </c>
       <c r="B2198" t="n">
-        <v>19666</v>
+        <v>33459</v>
       </c>
       <c r="C2198" t="n">
-        <v>2.75</v>
+        <v>2.88000011444092</v>
       </c>
       <c r="D2198" t="n">
-        <v>2.70000004768372</v>
+        <v>2.73000001907349</v>
       </c>
       <c r="E2198" t="n">
-        <v>2.70000004768372</v>
-      </c>
-      <c r="F2198" t="n">
-        <v>2.79999995231628</v>
-      </c>
+        <v>2.78999996185303</v>
+      </c>
+      <c r="F2198"/>
       <c r="G2198" t="s">
-        <v>888</v>
+        <v>894</v>
       </c>
       <c r="H2198" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="1" t="n">
+        <v>46099.6910185185</v>
+      </c>
+      <c r="B2199" t="n">
+        <v>33459</v>
+      </c>
+      <c r="C2199" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="D2199" t="n">
+        <v>2.73000001907349</v>
+      </c>
+      <c r="E2199" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="F2199" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="G2199" t="s">
+        <v>636</v>
+      </c>
+      <c r="H2199" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
+    <t xml:space="preserve">9.41868591308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73796272277832</t>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796367645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435523986816</t>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791213989258</t>
+    <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193084716797</t>
@@ -86,25 +86,25 @@
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028308868408</t>
+    <t xml:space="preserve">9.53631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636363983154</t>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430274963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440582275391</t>
+    <t xml:space="preserve">9.91440391540527</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,49 +128,49 @@
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.95641613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93960952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656423568726</t>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.9984245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162078857422</t>
+    <t xml:space="preserve">10.0488376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955894470215</t>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,46 +203,46 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9901819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219223022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
+    <t xml:space="preserve">9.07420063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94816970825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522483825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">9.11522579193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024375915527</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07223033905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125453948975</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -266,31 +266,31 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35849094390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.35848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930484771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171825408936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
+    <t xml:space="preserve">7.87693023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
   </si>
   <si>
     <t xml:space="preserve">7.5673565864563</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937957763672</t>
+    <t xml:space="preserve">7.30937814712524</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097526550293</t>
@@ -335,28 +335,28 @@
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136377334595</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41256999969482</t>
+    <t xml:space="preserve">7.41257047653198</t>
   </si>
   <si>
     <t xml:space="preserve">7.53296041488647</t>
@@ -365,34 +365,34 @@
     <t xml:space="preserve">7.29218006134033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739347457886</t>
+    <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06859970092773</t>
+    <t xml:space="preserve">7.06860017776489</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743083953857</t>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381311416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.87941551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98260641098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140066146851</t>
+    <t xml:space="preserve">6.98260688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902557373047</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501886367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">6.84501838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058485031128</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696760177612</t>
+    <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233861923218</t>
+    <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22206783294678</t>
+    <t xml:space="preserve">6.22206735610962</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7776346206665</t>
+    <t xml:space="preserve">6.26651096343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652040481567</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320093154907</t>
+    <t xml:space="preserve">5.33320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990081787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323687553406</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324036598206</t>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.91101360321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212361335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
+    <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
@@ -60223,9 +60223,11 @@
       <c r="E2200" t="n">
         <v>2.79999995231628</v>
       </c>
-      <c r="F2200"/>
+      <c r="F2200" t="n">
+        <v>2.83999991416931</v>
+      </c>
       <c r="G2200" t="s">
-        <v>894</v>
+        <v>667</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60233,27 +60235,51 @@
     </row>
     <row r="2201">
       <c r="A2201" s="1" t="n">
-        <v>46101.6911458333</v>
+        <v>46104.3333333333</v>
       </c>
       <c r="B2201" t="n">
-        <v>6515</v>
+        <v>9367</v>
       </c>
       <c r="C2201" t="n">
-        <v>2.85999989509583</v>
+        <v>2.80999994277954</v>
       </c>
       <c r="D2201" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E2201" t="n">
         <v>2.75999999046326</v>
       </c>
-      <c r="E2201" t="n">
-        <v>2.79999995231628</v>
-      </c>
-      <c r="F2201" t="n">
-        <v>2.83999991416931</v>
-      </c>
+      <c r="F2201"/>
       <c r="G2201" t="s">
-        <v>667</v>
+        <v>894</v>
       </c>
       <c r="H2201" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="1" t="n">
+        <v>46104.6912962963</v>
+      </c>
+      <c r="B2202" t="n">
+        <v>9367</v>
+      </c>
+      <c r="C2202" t="n">
+        <v>2.80999994277954</v>
+      </c>
+      <c r="D2202" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E2202" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="F2202" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="G2202" t="s">
+        <v>640</v>
+      </c>
+      <c r="H2202" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40187931060791</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5783224105835</t>
+    <t xml:space="preserve">9.45229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435428619385</t>
+    <t xml:space="preserve">9.73796367645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435523986816</t>
   </si>
   <si>
     <t xml:space="preserve">9.63713836669922</t>
@@ -80,46 +80,46 @@
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.53631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51951026916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430274963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
+    <t xml:space="preserve">9.56151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157115936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316738128662</t>
+    <t xml:space="preserve">9.82198143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157020568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997207641602</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
+    <t xml:space="preserve">10.0404348373413</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88919925689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239646911621</t>
+    <t xml:space="preserve">9.88920021057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656423568726</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
@@ -170,16 +170,16 @@
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162078857422</t>
+    <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
@@ -188,31 +188,31 @@
     <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425407409668</t>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425121307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07420063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">9.11621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0742015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -236,46 +236,46 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90024566650391</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07222843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
+    <t xml:space="preserve">9.02923202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34129047393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
+    <t xml:space="preserve">8.28969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3412914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -302,82 +302,82 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693119049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533502578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">7.87692975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3093786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657766342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657814025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65335035324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
+    <t xml:space="preserve">7.73934268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218053817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820976257324</t>
+    <t xml:space="preserve">6.96540832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9482102394104</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,19 +389,19 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941598892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260688781738</t>
+    <t xml:space="preserve">6.8794150352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74182748794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260593414307</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140113830566</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,22 +428,22 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416568756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377670288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
+    <t xml:space="preserve">7.24058532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976951599121</t>
   </si>
   <si>
     <t xml:space="preserve">7.69634580612183</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">7.78234004974365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836832046509</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -60298,9 +60298,11 @@
       <c r="E2203" t="n">
         <v>2.75999999046326</v>
       </c>
-      <c r="F2203"/>
+      <c r="F2203" t="n">
+        <v>2.75</v>
+      </c>
       <c r="G2203" t="s">
-        <v>893</v>
+        <v>690</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60308,27 +60310,51 @@
     </row>
     <row r="2204">
       <c r="A2204" s="1" t="n">
-        <v>46106.6782291667</v>
+        <v>46107.3333333333</v>
       </c>
       <c r="B2204" t="n">
-        <v>4347</v>
+        <v>3522</v>
       </c>
       <c r="C2204" t="n">
-        <v>2.79999995231628</v>
+        <v>2.75999999046326</v>
       </c>
       <c r="D2204" t="n">
-        <v>2.69000005722046</v>
+        <v>2.67000007629395</v>
       </c>
       <c r="E2204" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="F2204"/>
+      <c r="G2204" t="s">
+        <v>893</v>
+      </c>
+      <c r="H2204" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="1" t="n">
+        <v>46107.6910185185</v>
+      </c>
+      <c r="B2205" t="n">
+        <v>3522</v>
+      </c>
+      <c r="C2205" t="n">
         <v>2.75999999046326</v>
       </c>
-      <c r="F2204" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="G2204" t="s">
-        <v>690</v>
-      </c>
-      <c r="H2204" t="s">
+      <c r="D2205" t="n">
+        <v>2.67000007629395</v>
+      </c>
+      <c r="E2205" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="F2205" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="G2205" t="s">
+        <v>889</v>
+      </c>
+      <c r="H2205" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -53,49 +53,49 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.737961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791023254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64554023742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5363130569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41028213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950836181641</t>
+    <t xml:space="preserve">9.6371374130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.49430370330811</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
+    <t xml:space="preserve">9.82198333740234</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997398376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8555908203125</t>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
     <t xml:space="preserve">9.95641613006592</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002456665039</t>
+    <t xml:space="preserve">10.0320320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002265930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -161,40 +161,40 @@
     <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600395202637</t>
+    <t xml:space="preserve">9.8976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873649597168</t>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837394714355</t>
+    <t xml:space="preserve">9.78837299346924</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425121307373</t>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
@@ -215,22 +215,22 @@
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923393249512</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.2012186050415</t>
@@ -257,37 +257,37 @@
     <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607849121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969573974609</t>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607753753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969669342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42728328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.42728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.16930675506592</t>
@@ -299,34 +299,34 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490772247314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
@@ -335,52 +335,52 @@
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
   </si>
   <si>
     <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06860017776489</t>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859922409058</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381311416626</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342317581177</t>
+    <t xml:space="preserve">6.79342269897461</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69023180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89661407470703</t>
+    <t xml:space="preserve">6.69023132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416616439819</t>
@@ -437,37 +437,37 @@
     <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
+    <t xml:space="preserve">7.61895179748535</t>
   </si>
   <si>
     <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836688995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -482,13 +482,13 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
     <t xml:space="preserve">7.46648073196411</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,49 +527,49 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
+    <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
     <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7776346206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.77763414382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,19 +578,19 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
+    <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -614,52 +614,52 @@
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990081787109</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85768222808838</t>
+    <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
     <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,19 +680,19 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -60412,6 +60412,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2208">
+      <c r="A2208" s="1" t="n">
+        <v>46113.2916666667</v>
+      </c>
+      <c r="B2208" t="n">
+        <v>9214</v>
+      </c>
+      <c r="C2208" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2208" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E2208" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2208" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G2208" t="s">
+        <v>888</v>
+      </c>
+      <c r="H2208" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868495941162</t>
+    <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229434967041</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
+    <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193084716797</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
+    <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
@@ -101,22 +101,22 @@
     <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636363983154</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832685470581</t>
+    <t xml:space="preserve">9.77157115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
     <t xml:space="preserve">9.91440486907959</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">10.0320320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88920021057129</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961143493652</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.9984245300293</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600299835205</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">9.98162078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.78837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">9.24224281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420063018799</t>
+    <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868591308594</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832336425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.57832431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234397888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -71,25 +71,25 @@
     <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70435428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.70435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64553833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4102840423584</t>
+    <t xml:space="preserve">9.61193180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5363130569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41028213500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
+    <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -137,88 +137,88 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002265930176</t>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842643737793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162174224854</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162269592285</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837299346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.62873649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837394714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
+    <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94816970825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018001556396</t>
+    <t xml:space="preserve">8.94817161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9901819229126</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">8.98623561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.72825908660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.59926986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28969669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090339660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35848903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41008567810059</t>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490867614746</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
@@ -317,10 +317,10 @@
     <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56735706329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
+    <t xml:space="preserve">7.56735754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
+    <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53295993804932</t>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08579778671265</t>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -380,10 +380,10 @@
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381311416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743036270142</t>
+    <t xml:space="preserve">6.9138126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743083953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74182748794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.7418270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
+    <t xml:space="preserve">7.05140113830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3437762260437</t>
+    <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035442352295</t>
+    <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.33315134048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1553783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648120880127</t>
+    <t xml:space="preserve">7.11093473434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15537786483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984035491943</t>
+    <t xml:space="preserve">6.39984083175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428443908691</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
+    <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1776237487793</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986066818237</t>
+    <t xml:space="preserve">5.73319053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986114501953</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -626,34 +626,34 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
+    <t xml:space="preserve">4.24878358840942</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990105628967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324060440063</t>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435362815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.64435386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,22 +680,22 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212488174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323862075806</t>
+    <t xml:space="preserve">3.76879501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
     <t xml:space="preserve">4.06212091445923</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -60516,6 +60516,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2212">
+      <c r="A2212" s="1" t="n">
+        <v>46121.2916666667</v>
+      </c>
+      <c r="B2212" t="n">
+        <v>9724</v>
+      </c>
+      <c r="C2212" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="D2212" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="E2212" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F2212" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="G2212" t="s">
+        <v>693</v>
+      </c>
+      <c r="H2212" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40187931060791</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
+    <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
     <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
+    <t xml:space="preserve">9.51950836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636363983154</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316928863525</t>
+    <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85558986663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95641613006592</t>
+    <t xml:space="preserve">9.8555908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961143493652</t>
+    <t xml:space="preserve">9.93960952758789</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239456176758</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89760112762451</t>
+    <t xml:space="preserve">10.0656423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9984245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.90600204467773</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162269592285</t>
+    <t xml:space="preserve">9.98162078857422</t>
   </si>
   <si>
     <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873649597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.62873554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72955894470215</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224281311035</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817161560059</t>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.9901819229126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
+    <t xml:space="preserve">9.03219223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.33020687103271</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11522579193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98623561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825908660889</t>
+    <t xml:space="preserve">9.11522483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98623752593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825717926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90024471282959</t>
+    <t xml:space="preserve">8.90024375915527</t>
   </si>
   <si>
     <t xml:space="preserve">8.77125453948975</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.28969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">8.51327610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090244293213</t>
+    <t xml:space="preserve">8.22090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">8.25529861450195</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35848999023438</t>
+    <t xml:space="preserve">8.35849094390869</t>
   </si>
   <si>
     <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87692975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5673565864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221742630005</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334939956665</t>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334987640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214365005493</t>
+    <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739442825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.96540880203247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820928573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91381216049194</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743083953857</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87941551208496</t>
+    <t xml:space="preserve">6.8794150352478</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -404,37 +404,37 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
   </si>
   <si>
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">7.01700401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
+    <t xml:space="preserve">7.44696760177612</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233909606934</t>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233861923218</t>
   </si>
   <si>
     <t xml:space="preserve">7.43836784362793</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315134048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.33315086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
+    <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650104522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.66650056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651096343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985074996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77763414382935</t>
+    <t xml:space="preserve">6.26651048660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7776346206665</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652088165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6443042755127</t>
+    <t xml:space="preserve">5.68874788284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64430379867554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544729232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656055450439</t>
+    <t xml:space="preserve">4.35544681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656103134155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990081787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101384162903</t>
+    <t xml:space="preserve">3.91101408004761</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
+    <t xml:space="preserve">3.76879477500916</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434743881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
+    <t xml:space="preserve">3.88434791564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323068618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.06212139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767627716064</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -60542,6 +60542,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2213">
+      <c r="A2213" s="1" t="n">
+        <v>46122.2916666667</v>
+      </c>
+      <c r="B2213" t="n">
+        <v>771</v>
+      </c>
+      <c r="C2213" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D2213" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="E2213" t="n">
+        <v>2.65000009536743</v>
+      </c>
+      <c r="F2213" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G2213" t="s">
+        <v>691</v>
+      </c>
+      <c r="H2213" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796367645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.52791213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5363130569458</t>
+    <t xml:space="preserve">9.53631496429443</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992053985596</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157020568848</t>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77156925201416</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
+    <t xml:space="preserve">9.91440677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404357910156</t>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404367446899</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002265930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.88920021057129</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89760112762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">9.8976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600395202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62873649597168</t>
+    <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.72956085205078</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224090576172</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15822219848633</t>
+    <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
     <t xml:space="preserve">9.11621189117432</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219032287598</t>
+    <t xml:space="preserve">8.94816970825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018001556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619968414307</t>
+    <t xml:space="preserve">9.41619873046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825908660889</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -245,10 +245,10 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923202514648</t>
+    <t xml:space="preserve">8.77125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -257,31 +257,31 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.28969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
+    <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.22090244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">7.82533550262451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3093786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
@@ -344,31 +344,31 @@
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.739342212677</t>
+    <t xml:space="preserve">7.73934316635132</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136377334595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41257047653198</t>
   </si>
   <si>
     <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">6.63863611221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260593414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">6.7762246131897</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023132324219</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416568756104</t>
+    <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895322799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
+    <t xml:space="preserve">7.61895132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61035394668579</t>
+    <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33315134048462</t>
+    <t xml:space="preserve">7.6442551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
     <t xml:space="preserve">7.37759494781494</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
+    <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
@@ -521,31 +521,31 @@
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
+    <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
   </si>
   <si>
     <t xml:space="preserve">3.78657269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
+    <t xml:space="preserve">3.99990057945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80435013771057</t>
+    <t xml:space="preserve">3.80434989929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
+    <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
     <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212512016296</t>
+    <t xml:space="preserve">3.90212535858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434743881226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212091445923</t>
+    <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767532348633</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -60620,6 +60620,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2216">
+      <c r="A2216" s="1" t="n">
+        <v>46127.2916666667</v>
+      </c>
+      <c r="B2216" t="n">
+        <v>39431</v>
+      </c>
+      <c r="C2216" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2216" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E2216" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="F2216" t="n">
+        <v>2.76999998092651</v>
+      </c>
+      <c r="G2216" t="s">
+        <v>890</v>
+      </c>
+      <c r="H2216" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44388961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
+    <t xml:space="preserve">9.44389057159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033462524414</t>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033367156982</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52791213989258</t>
+    <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
     <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53631496429443</t>
+    <t xml:space="preserve">9.64553833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
@@ -101,37 +101,37 @@
     <t xml:space="preserve">9.49430465698242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992053985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636459350586</t>
+    <t xml:space="preserve">9.56992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636554718018</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77156925201416</t>
+    <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440677642822</t>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85558986663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404367446899</t>
+    <t xml:space="preserve">9.8555908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95641613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">9.99002265930176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88920021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93960952758789</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057240486145</t>
+    <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -164,22 +164,22 @@
     <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600395202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038425445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038520812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224090576172</t>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
+    <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
@@ -60646,6 +60646,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2217">
+      <c r="A2217" s="1" t="n">
+        <v>46128.2916666667</v>
+      </c>
+      <c r="B2217" t="n">
+        <v>16668</v>
+      </c>
+      <c r="C2217" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2217" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="E2217" t="n">
+        <v>2.71000003814697</v>
+      </c>
+      <c r="F2217" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G2217" t="s">
+        <v>691</v>
+      </c>
+      <c r="H2217" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188026428223</t>
+    <t xml:space="preserve">9.40188121795654</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41868591308594</t>
+    <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
+    <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
     <t xml:space="preserve">9.57832336425781</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64553833007812</t>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49430465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992149353027</t>
+    <t xml:space="preserve">9.49430370330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992244720459</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636554718018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198238372803</t>
+    <t xml:space="preserve">9.82198143005371</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
@@ -119,46 +119,46 @@
     <t xml:space="preserve">10.1832704544067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997303009033</t>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404357910156</t>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404348373413</t>
   </si>
   <si>
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002265930176</t>
+    <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93960952758789</t>
+    <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656414031982</t>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162269592285</t>
+    <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.973219871521</t>
@@ -182,25 +182,25 @@
     <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837394714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827182769775</t>
+    <t xml:space="preserve">9.78837490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.32626247406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
+    <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">8.94816970825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99018001556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">8.99018096923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41619873046875</t>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94324016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222938537598</t>
+    <t xml:space="preserve">8.94323921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
+    <t xml:space="preserve">9.2012186050415</t>
   </si>
   <si>
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">8.59926986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409381866455</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -299,73 +299,73 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533502578735</t>
   </si>
   <si>
     <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097431182861</t>
+    <t xml:space="preserve">7.36097526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
+    <t xml:space="preserve">7.18898916244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73934316635132</t>
+    <t xml:space="preserve">7.73934364318848</t>
   </si>
   <si>
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41257047653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739442825317</t>
+    <t xml:space="preserve">7.13739347457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.08579778671265</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9138126373291</t>
+    <t xml:space="preserve">6.91381216049194</t>
   </si>
   <si>
     <t xml:space="preserve">6.70743036270142</t>
@@ -398,10 +398,10 @@
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260593414307</t>
+    <t xml:space="preserve">6.79342317581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260688781738</t>
   </si>
   <si>
     <t xml:space="preserve">7.05140066146851</t>
@@ -416,10 +416,10 @@
     <t xml:space="preserve">6.84501886367798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023132324219</t>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023180007935</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,25 +428,25 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
+    <t xml:space="preserve">7.24058485031128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895132064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634628295898</t>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377670288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634580612183</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035346984863</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
+    <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15537786483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06649112701416</t>
+    <t xml:space="preserve">7.1553783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
     <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
+    <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
     <t xml:space="preserve">6.88871812820435</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57761430740356</t>
+    <t xml:space="preserve">6.57761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
+    <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
     <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540761947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">5.95540714263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
@@ -572,13 +572,13 @@
     <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874740600586</t>
+    <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
     <t xml:space="preserve">5.82207727432251</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8221275806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657269477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990057945251</t>
+    <t xml:space="preserve">3.82212734222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657293319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990105628967</t>
   </si>
   <si>
     <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8576819896698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
+    <t xml:space="preserve">3.85768222808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324060440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
     <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879747390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80434989929199</t>
+    <t xml:space="preserve">3.68879723548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212337493896</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434743881226</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
     <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71546292304993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81323838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212139129639</t>
+    <t xml:space="preserve">3.71546316146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81323862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212091445923</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
@@ -60672,6 +60672,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2218">
+      <c r="A2218" s="1" t="n">
+        <v>46129.2916666667</v>
+      </c>
+      <c r="B2218" t="n">
+        <v>28120</v>
+      </c>
+      <c r="C2218" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="D2218" t="n">
+        <v>2.64000010490417</v>
+      </c>
+      <c r="E2218" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="F2218" t="n">
+        <v>2.75999999046326</v>
+      </c>
+      <c r="G2218" t="s">
+        <v>640</v>
+      </c>
+      <c r="H2218" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40188121795654</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -53,37 +53,37 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.737961769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074680328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435428619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6371374130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64554023742676</t>
+    <t xml:space="preserve">9.73796272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.5363130569458</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950836181641</t>
+    <t xml:space="preserve">9.56151866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.49430370330811</t>
@@ -104,7 +104,7 @@
     <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">9.77157020568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76316928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997398376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8555908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.76316833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85558986663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
@@ -146,52 +146,52 @@
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656414031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99842548370361</t>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842643737793</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488376617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600299835205</t>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600204467773</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.98162269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72956085205078</t>
+    <t xml:space="preserve">9.72955989837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
     <t xml:space="preserve">9.28425216674805</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0742015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94816970825195</t>
+    <t xml:space="preserve">9.07420063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94817066192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.99018096923828</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">9.03219127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020782470703</t>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020687103271</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825813293457</t>
+    <t xml:space="preserve">8.98623561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825908660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07223033905029</t>
+    <t xml:space="preserve">9.07222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,49 +248,49 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923202514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607753753662</t>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3412914276123</t>
+    <t xml:space="preserve">8.34129047393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409381866455</t>
+    <t xml:space="preserve">8.51327610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409286499023</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.41008472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490772247314</t>
+    <t xml:space="preserve">8.13490962982178</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693071365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533550262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735706329346</t>
+    <t xml:space="preserve">7.87692975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937814712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097431182861</t>
+    <t xml:space="preserve">7.30937910079956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
+    <t xml:space="preserve">7.18898868560791</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2061882019043</t>
+    <t xml:space="preserve">7.20618772506714</t>
   </si>
   <si>
     <t xml:space="preserve">7.739342212677</t>
@@ -350,40 +350,40 @@
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214317321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256952285767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53295993804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29218006134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08579778671265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859922409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214365005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256999969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53296041488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29217958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739442825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0857982635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91381311416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743036270142</t>
+    <t xml:space="preserve">6.9138126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743083953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342269897461</t>
+    <t xml:space="preserve">6.63863563537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342317581177</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140066146851</t>
+    <t xml:space="preserve">7.05140113830566</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
+    <t xml:space="preserve">6.93101119995117</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023132324219</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3437762260437</t>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34377574920654</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836688995361</t>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6442551612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33315086364746</t>
+    <t xml:space="preserve">7.64425468444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33315134048462</t>
   </si>
   <si>
     <t xml:space="preserve">7.37759494781494</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28870725631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.2887077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02204751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871812820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760391235352</t>
+    <t xml:space="preserve">7.022047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
@@ -521,31 +521,31 @@
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094417572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.71094465255737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095457077026</t>
+    <t xml:space="preserve">6.31095409393311</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318061828613</t>
+    <t xml:space="preserve">6.13318109512329</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985122680664</t>
+    <t xml:space="preserve">5.99985074996948</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319101333618</t>
+    <t xml:space="preserve">5.73319053649902</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207727432251</t>
+    <t xml:space="preserve">5.82207775115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8221275806427</t>
+    <t xml:space="preserve">4.24878358840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
     <t xml:space="preserve">3.78657269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990057945251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
   </si>
   <si>
     <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324036598206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101804733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435362815857</t>
+    <t xml:space="preserve">3.73324012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101757049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80434989929199</t>
+    <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
+    <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
     <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212535858154</t>
+    <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434743881226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546292304993</t>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
+    <t xml:space="preserve">4.06212091445923</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185453414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435390472412</t>
+    <t xml:space="preserve">4.38185501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435342788696</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935564041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268781661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32685232162476</t>
+    <t xml:space="preserve">4.36352109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268733978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3268518447876</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934679031372</t>
+    <t xml:space="preserve">4.23518133163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934631347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767532348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684789657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850860595703</t>
+    <t xml:space="preserve">4.21684741973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850908279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934188842773</t>
+    <t xml:space="preserve">4.07934141159058</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267311096191</t>
+    <t xml:space="preserve">4.04267358779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433477401733</t>
+    <t xml:space="preserve">3.91433453559875</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849927902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683342933655</t>
+    <t xml:space="preserve">3.86849904060364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683319091797</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936006546021</t>
+    <t xml:space="preserve">4.51936054229736</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019382476807</t>
+    <t xml:space="preserve">4.51019334793091</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183611869812</t>
+    <t xml:space="preserve">3.94183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854686737061</t>
+    <t xml:space="preserve">4.96854639053345</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11521911621094</t>
+    <t xml:space="preserve">5.1152195930481</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355398178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15188789367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521469116211</t>
+    <t xml:space="preserve">5.13355350494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1518874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521516799927</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023160934448</t>
+    <t xml:space="preserve">5.39023113250732</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6102409362793</t>
+    <t xml:space="preserve">5.61024045944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359128952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525295257568</t>
+    <t xml:space="preserve">6.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525247573853</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9402551651001</t>
+    <t xml:space="preserve">5.94025468826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025026321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192077636719</t>
+    <t xml:space="preserve">5.83025074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693279266357</t>
+    <t xml:space="preserve">6.19693326950073</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027381896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860330581665</t>
+    <t xml:space="preserve">6.38027429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860378265381</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4719443321228</t>
+    <t xml:space="preserve">6.47194480895996</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194923400879</t>
+    <t xml:space="preserve">6.56361532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194875717163</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861753463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528045654297</t>
+    <t xml:space="preserve">6.61861705780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528093338013</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696125030518</t>
+    <t xml:space="preserve">6.85696077346802</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362417221069</t>
+    <t xml:space="preserve">6.78362464904785</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -60753,6 +60753,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2221">
+      <c r="A2221" s="1" t="n">
+        <v>46134.2916666667</v>
+      </c>
+      <c r="B2221" t="n">
+        <v>4413</v>
+      </c>
+      <c r="C2221" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="D2221" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E2221" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="F2221" t="n">
+        <v>2.72000002861023</v>
+      </c>
+      <c r="G2221" t="s">
+        <v>886</v>
+      </c>
+      <c r="H2221" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">9.44389057159424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4186840057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45229339599609</t>
+    <t xml:space="preserve">9.41868495941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45229434967041</t>
   </si>
   <si>
     <t xml:space="preserve">9.6539421081543</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">9.57832431793213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66234493255615</t>
+    <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
     <t xml:space="preserve">9.73796272277832</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">9.56992244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198238372803</t>
+    <t xml:space="preserve">9.74636459350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198143005371</t>
   </si>
   <si>
     <t xml:space="preserve">9.77157020568848</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.91440582275391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77997398376465</t>
+    <t xml:space="preserve">9.77997207641602</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0404357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320329666138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99002456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88919925689697</t>
+    <t xml:space="preserve">10.0404348373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99002361297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88920021057129</t>
   </si>
   <si>
     <t xml:space="preserve">9.93961048126221</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057240486145</t>
+    <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488386154175</t>
+    <t xml:space="preserve">10.0488367080688</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">9.83038520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97321891784668</t>
+    <t xml:space="preserve">9.98162174224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.973219871521</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -185,22 +185,22 @@
     <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626342773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626247406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224185943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425121307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11621189117432</t>
+    <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
@@ -212,25 +212,25 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219127655029</t>
+    <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
     <t xml:space="preserve">9.28721046447754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33020782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.33020687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41619968414307</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.98623561859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825908660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -245,16 +245,16 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02923393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2012186050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919704437256</t>
+    <t xml:space="preserve">8.77125453948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20121765136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.59926986694336</t>
@@ -263,13 +263,13 @@
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3412914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42728328704834</t>
+    <t xml:space="preserve">8.28969669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34129047393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
     <t xml:space="preserve">8.51327610015869</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">8.41008472442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16930675506592</t>
+    <t xml:space="preserve">8.1693058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -299,103 +299,103 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490867614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87693166732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490962982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87692975997925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533645629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
   </si>
   <si>
     <t xml:space="preserve">7.56735754013062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39537191390991</t>
+    <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097526550293</t>
+    <t xml:space="preserve">7.36097478866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898916244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980592727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2061882019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73934316635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
+    <t xml:space="preserve">7.18898868560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20618772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.739342212677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136472702026</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.72214365005493</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53295993804932</t>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739347457886</t>
+    <t xml:space="preserve">7.13739442825317</t>
   </si>
   <si>
     <t xml:space="preserve">7.0857982635498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06860017776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540880203247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94820928573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91381216049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743036270142</t>
+    <t xml:space="preserve">7.06859970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9138126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743083953857</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
+    <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863611221313</t>
+    <t xml:space="preserve">6.63863563537598</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -416,46 +416,46 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101167678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89661407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01700401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24058485031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416616439819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696760177612</t>
+    <t xml:space="preserve">6.93101119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89661455154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01700353622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24058532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416664123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
     <t xml:space="preserve">7.61895227432251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3437762260437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
+    <t xml:space="preserve">7.34377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
   </si>
   <si>
     <t xml:space="preserve">7.61035394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78233861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836784362793</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -464,10 +464,10 @@
     <t xml:space="preserve">7.64425468444824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33315086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37759447097778</t>
+    <t xml:space="preserve">7.33315134048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37759494781494</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -476,28 +476,28 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093425750732</t>
+    <t xml:space="preserve">7.11093473434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
+    <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.2887077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55536794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648073196411</t>
+    <t xml:space="preserve">7.5553674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648025512695</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981107711792</t>
+    <t xml:space="preserve">7.59981155395508</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">6.97760438919067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53317070007324</t>
+    <t xml:space="preserve">6.5331711769104</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04429388046265</t>
+    <t xml:space="preserve">5.95540761947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0442943572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.17762422561646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26651048660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99985122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7776346206665</t>
+    <t xml:space="preserve">6.26651096343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99985074996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
     <t xml:space="preserve">5.73319053649902</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207775115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541753768921</t>
@@ -602,22 +602,22 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098432540894</t>
+    <t xml:space="preserve">5.11098384857178</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07101011276245</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">3.82212734222412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990081787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8932363986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324036598206</t>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990034103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89323663711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324012756348</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">3.64435386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68879723548889</t>
+    <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101408004761</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878755569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212313652039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434593200684</t>
+    <t xml:space="preserve">4.08878707885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -680,37 +680,37 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879477500916</t>
+    <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
     <t xml:space="preserve">3.90212512016296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546339988708</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10656452178955</t>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10656404495239</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767580032349</t>
+    <t xml:space="preserve">4.09767627716064</t>
   </si>
   <si>
     <t xml:space="preserve">4.13434457778931</t>
@@ -60909,6 +60909,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2227">
+      <c r="A2227" s="1" t="n">
+        <v>46142.2916666667</v>
+      </c>
+      <c r="B2227" t="n">
+        <v>18522</v>
+      </c>
+      <c r="C2227" t="n">
+        <v>2.70000004768372</v>
+      </c>
+      <c r="D2227" t="n">
+        <v>2.59999990463257</v>
+      </c>
+      <c r="E2227" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F2227" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="G2227" t="s">
+        <v>643</v>
+      </c>
+      <c r="H2227" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40187931060791</t>
+    <t xml:space="preserve">9.40188026428223</t>
   </si>
   <si>
     <t xml:space="preserve">SIT.MI</t>
@@ -50,37 +50,37 @@
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70435523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63713836669922</t>
+    <t xml:space="preserve">9.45229339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65394115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57832336425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.737961769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70435428619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6371374130249</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193084716797</t>
+    <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -89,13 +89,13 @@
     <t xml:space="preserve">9.53631401062012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41028213500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950836181641</t>
+    <t xml:space="preserve">9.41028308868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51950931549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.49430370330811</t>
@@ -104,52 +104,52 @@
     <t xml:space="preserve">9.56992244720459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74636459350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82198143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
+    <t xml:space="preserve">9.74636554718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77156925201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832704544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95641613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0404348373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0320339202881</t>
+    <t xml:space="preserve">9.9564151763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88920021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">9.88919925689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488367080688</t>
+    <t xml:space="preserve">10.0488386154175</t>
   </si>
   <si>
     <t xml:space="preserve">9.8976001739502</t>
@@ -173,34 +173,34 @@
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837490081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425121307373</t>
+    <t xml:space="preserve">9.28425216674805</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
+    <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">8.99018096923828</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03219032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28721046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
+    <t xml:space="preserve">9.03219127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623561859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825908660889</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,49 +248,49 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49607849121094</t>
+    <t xml:space="preserve">9.02923202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49607753753662</t>
   </si>
   <si>
     <t xml:space="preserve">8.28969669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1693058013916</t>
+    <t xml:space="preserve">8.41008567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16930675506592</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">8.53047466278076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
+    <t xml:space="preserve">8.13490772247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87692975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
   </si>
   <si>
     <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30937910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36097478866577</t>
+    <t xml:space="preserve">7.30937814712524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36097431182861</t>
   </si>
   <si>
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
+    <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618772506714</t>
+    <t xml:space="preserve">7.2061882019043</t>
   </si>
   <si>
     <t xml:space="preserve">7.739342212677</t>
@@ -350,40 +350,40 @@
     <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48136472702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214365005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739442825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06859970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">7.48136425018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859922409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9138126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70743083953857</t>
+    <t xml:space="preserve">6.91381311416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63863563537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79342317581177</t>
+    <t xml:space="preserve">6.63863611221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79342269897461</t>
   </si>
   <si>
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
+    <t xml:space="preserve">7.05140066146851</t>
   </si>
   <si>
     <t xml:space="preserve">6.75902605056763</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">6.84501838684082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023132324219</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700353622437</t>
+    <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46416664123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
+    <t xml:space="preserve">7.46416616439819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
   </si>
   <si>
     <t xml:space="preserve">7.42976903915405</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">7.78233909606934</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.43836688995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33315134048462</t>
+    <t xml:space="preserve">7.6442551612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
     <t xml:space="preserve">7.37759494781494</t>
@@ -476,7 +476,7 @@
     <t xml:space="preserve">7.24426412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11093473434448</t>
+    <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.15537786483765</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">7.06649112701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5553674697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536699295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
   </si>
   <si>
     <t xml:space="preserve">6.66650104522705</t>
@@ -521,31 +521,31 @@
     <t xml:space="preserve">6.62205743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5331711769104</t>
+    <t xml:space="preserve">6.53317070007324</t>
   </si>
   <si>
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428443908691</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428396224976</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
+    <t xml:space="preserve">6.31095457077026</t>
   </si>
   <si>
     <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">5.68874740600586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
+    <t xml:space="preserve">5.82207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.86652088165283</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55541753768921</t>
+    <t xml:space="preserve">5.55541706085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764406204224</t>
+    <t xml:space="preserve">5.37764453887939</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07101011276245</t>
+    <t xml:space="preserve">4.07100963592529</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
   </si>
   <si>
     <t xml:space="preserve">3.78657269477844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323663711548</t>
+    <t xml:space="preserve">3.99990057945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.8576819896698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80435013771057</t>
+    <t xml:space="preserve">3.80434989929199</t>
   </si>
   <si>
     <t xml:space="preserve">3.91101384162903</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
+    <t xml:space="preserve">4.08878755569458</t>
   </si>
   <si>
     <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">3.96434593200684</t>
   </si>
   <si>
     <t xml:space="preserve">3.99101161956787</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212512016296</t>
+    <t xml:space="preserve">3.90212535858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434743881226</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546339988708</t>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06212091445923</t>
+    <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
     <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10656404495239</t>
+    <t xml:space="preserve">4.10656452178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.00878953933716</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">4.19851350784302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
   </si>
   <si>
     <t xml:space="preserve">4.33601951599121</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">4.30851793289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.29935121536255</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">4.25351572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
   </si>
   <si>
     <t xml:space="preserve">4.24434900283813</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">4.12517690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09767532348633</t>
+    <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
     <t xml:space="preserve">4.15267848968506</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
+    <t xml:space="preserve">9.44388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
@@ -53,34 +53,34 @@
     <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73796272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67074584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62033367156982</t>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5783224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796367645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67074680328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62033271789551</t>
   </si>
   <si>
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63713932037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.63713836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52791118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
@@ -107,25 +107,25 @@
     <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82198143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1832695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85558986663818</t>
+    <t xml:space="preserve">9.82198238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77157115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1832714080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.95641613006592</t>
@@ -137,43 +137,43 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88920021057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239551544189</t>
+    <t xml:space="preserve">9.99002456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88919830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93961238861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656404495239</t>
+    <t xml:space="preserve">10.0656414031982</t>
   </si>
   <si>
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8976001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
+    <t xml:space="preserve">10.0488367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.98162174224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.973219871521</t>
+    <t xml:space="preserve">9.97321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.62873554229736</t>
@@ -182,43 +182,43 @@
     <t xml:space="preserve">9.72956085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78837490081787</t>
+    <t xml:space="preserve">9.78837394714355</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827278137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32626247406006</t>
+    <t xml:space="preserve">9.32626342773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.24224185943604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28425216674805</t>
+    <t xml:space="preserve">9.28425312042236</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
+    <t xml:space="preserve">9.11621189117432</t>
   </si>
   <si>
     <t xml:space="preserve">9.0742015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">8.94816970825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
+    <t xml:space="preserve">9.28721141815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -230,16 +230,16 @@
     <t xml:space="preserve">8.98623561859131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825908660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8572473526001</t>
+    <t xml:space="preserve">8.72825813293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85724830627441</t>
   </si>
   <si>
     <t xml:space="preserve">8.94324016571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">9.07222938537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0292329788208</t>
+    <t xml:space="preserve">9.02923202514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.20121765136719</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">9.45919609069824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28969669342041</t>
+    <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">8.34129047393799</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -299,31 +299,31 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047466278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490962982178</t>
+    <t xml:space="preserve">8.53047561645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87692975997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494508743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30937910079956</t>
+    <t xml:space="preserve">7.87693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3093786239624</t>
   </si>
   <si>
     <t xml:space="preserve">7.36097478866577</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99980545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86221742630005</t>
+    <t xml:space="preserve">7.18898963928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99980592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">7.20618772506714</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">7.739342212677</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65334939956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136472702026</t>
+    <t xml:space="preserve">7.65334892272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
     <t xml:space="preserve">7.72214365005493</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29217958450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13739442825317</t>
+    <t xml:space="preserve">7.29218006134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.0857982635498</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">7.06859970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96540832519531</t>
+    <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
     <t xml:space="preserve">6.94820976257324</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">6.9138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70743083953857</t>
+    <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
     <t xml:space="preserve">7.10299682617188</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
+    <t xml:space="preserve">6.74182748794556</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863563537598</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">6.75902605056763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7762246131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">6.77622413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023132324219</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46416664123535</t>
+    <t xml:space="preserve">7.24058485031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46416568756104</t>
   </si>
   <si>
     <t xml:space="preserve">7.44696712493896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61895227432251</t>
+    <t xml:space="preserve">7.61895275115967</t>
   </si>
   <si>
     <t xml:space="preserve">7.34377574920654</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">7.42976903915405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69634628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
+    <t xml:space="preserve">7.69634580612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
   </si>
   <si>
     <t xml:space="preserve">7.78233909606934</t>
@@ -61039,6 +61039,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2232">
+      <c r="A2232" s="1" t="n">
+        <v>46150.2916666667</v>
+      </c>
+      <c r="B2232" t="n">
+        <v>45238</v>
+      </c>
+      <c r="C2232" t="n">
+        <v>2.78999996185303</v>
+      </c>
+      <c r="D2232" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="E2232" t="n">
+        <v>2.5699999332428</v>
+      </c>
+      <c r="F2232" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="G2232" t="s">
+        <v>889</v>
+      </c>
+      <c r="H2232" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="895">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="896">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,25 +44,25 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41868495941162</t>
+    <t xml:space="preserve">9.44389152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41868591308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.45229244232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65394115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57832336425781</t>
+    <t xml:space="preserve">9.6539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5783224105835</t>
   </si>
   <si>
     <t xml:space="preserve">9.66234397888184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73796272277832</t>
+    <t xml:space="preserve">9.737961769104</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">9.70435428619385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6371374130249</t>
+    <t xml:space="preserve">9.63713836669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.52791118621826</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">9.61193180084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64554023742676</t>
+    <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.53631401062012</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56151962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51950931549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49430370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56992244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74636554718018</t>
+    <t xml:space="preserve">9.56152057647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51951026916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49430465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56992149353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74636459350586</t>
   </si>
   <si>
     <t xml:space="preserve">9.82198238372803</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">9.76316833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1832704544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997398376465</t>
+    <t xml:space="preserve">10.1832695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997303009033</t>
   </si>
   <si>
     <t xml:space="preserve">9.8555908203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9564151763916</t>
+    <t xml:space="preserve">9.95641613006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.0404357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0320339202881</t>
+    <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
     <t xml:space="preserve">9.99002361297607</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">9.93961048126221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87239456176758</t>
+    <t xml:space="preserve">9.87239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">10.0572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656423568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9984245300293</t>
+    <t xml:space="preserve">10.0656404495239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488376617432</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">9.8976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90600204467773</t>
+    <t xml:space="preserve">9.90600299835205</t>
   </si>
   <si>
     <t xml:space="preserve">9.83038520812988</t>
@@ -179,10 +179,10 @@
     <t xml:space="preserve">9.62873554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72955989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78837394714355</t>
+    <t xml:space="preserve">9.72956085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78837299346924</t>
   </si>
   <si>
     <t xml:space="preserve">9.36827182769775</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">9.1162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07420253753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94817066192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99018096923828</t>
+    <t xml:space="preserve">9.0742015838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94816970825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99018001556396</t>
   </si>
   <si>
     <t xml:space="preserve">9.03219127655029</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41620063781738</t>
+    <t xml:space="preserve">9.41619873046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.11522579193115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98623752593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825717926025</t>
+    <t xml:space="preserve">8.98623657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825813293457</t>
   </si>
   <si>
     <t xml:space="preserve">8.8572473526001</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">8.90024471282959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77125453948975</t>
+    <t xml:space="preserve">8.77125549316406</t>
   </si>
   <si>
     <t xml:space="preserve">9.0292329788208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926891326904</t>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926986694336</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607849121094</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51327610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
+    <t xml:space="preserve">8.51327705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.32409286499023</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">8.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41008472442627</t>
+    <t xml:space="preserve">8.41008567810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.1693058013916</t>
@@ -299,67 +299,67 @@
     <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53047561645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13490962982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03171825408936</t>
+    <t xml:space="preserve">8.53047466278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13490867614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
     <t xml:space="preserve">7.87693071365356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70494556427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5673565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537191390991</t>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494604110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537239074707</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937814712524</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36097526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32657814025879</t>
+    <t xml:space="preserve">7.36097431182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32657766342163</t>
   </si>
   <si>
     <t xml:space="preserve">7.18898916244507</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99980592727661</t>
+    <t xml:space="preserve">6.99980545043945</t>
   </si>
   <si>
     <t xml:space="preserve">6.86221694946289</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334892272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48136425018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72214412689209</t>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48136472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72214317321777</t>
   </si>
   <si>
     <t xml:space="preserve">7.41256999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53296089172363</t>
+    <t xml:space="preserve">7.53296041488647</t>
   </si>
   <si>
     <t xml:space="preserve">7.29218006134033</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">7.13739395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0857982635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06860017776489</t>
+    <t xml:space="preserve">7.08579778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06859922409058</t>
   </si>
   <si>
     <t xml:space="preserve">6.96540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94820928573608</t>
+    <t xml:space="preserve">6.94820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.9138126373291</t>
@@ -389,37 +389,37 @@
     <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8794150352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74182748794556</t>
+    <t xml:space="preserve">6.87941551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7418270111084</t>
   </si>
   <si>
     <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79342317581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98260688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501791000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69023180007935</t>
+    <t xml:space="preserve">6.79342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98260641098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902605056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69023132324219</t>
   </si>
   <si>
     <t xml:space="preserve">6.89661455154419</t>
@@ -428,40 +428,40 @@
     <t xml:space="preserve">7.01700401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24058485031128</t>
+    <t xml:space="preserve">7.24058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">7.46416616439819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836736679077</t>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895132064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836688995361</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64425468444824</t>
+    <t xml:space="preserve">7.6442551612854</t>
   </si>
   <si>
     <t xml:space="preserve">7.33315086364746</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.15537786483765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.066490650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2887077331543</t>
+    <t xml:space="preserve">7.06649112701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28870725631714</t>
   </si>
   <si>
     <t xml:space="preserve">7.55536699295044</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.46648073196411</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.022047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57761478424072</t>
+    <t xml:space="preserve">7.02204751968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57761430740356</t>
   </si>
   <si>
     <t xml:space="preserve">6.62205743789673</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">6.84427404403687</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71094465255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39984083175659</t>
+    <t xml:space="preserve">6.71094417572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39984035491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.44428396224976</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13318109512329</t>
+    <t xml:space="preserve">6.31095457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13318061828613</t>
   </si>
   <si>
     <t xml:space="preserve">6.08873748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95540714263916</t>
+    <t xml:space="preserve">5.95540761947632</t>
   </si>
   <si>
     <t xml:space="preserve">6.0442943572998</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
+    <t xml:space="preserve">5.73319101333618</t>
   </si>
   <si>
     <t xml:space="preserve">5.59986114501953</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">5.51097393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68874788284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
+    <t xml:space="preserve">5.68874740600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55541706085205</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07100963592529</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82212734222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78657293319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85768222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73324012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75101757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64435386657715</t>
+    <t xml:space="preserve">4.24878311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8221275806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78657269477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99990057945251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8576819896698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73324036598206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75101804733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64435362815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.68879747390747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80435013771057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.80434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08878707885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">4.08878755569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212337493896</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">3.76879501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90212512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88434791564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83101606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71546316146851</t>
+    <t xml:space="preserve">3.90212535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88434743881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83101558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71546292304993</t>
   </si>
   <si>
     <t xml:space="preserve">3.81323838233948</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">4.06212139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -2697,6 +2697,9 @@
   </si>
   <si>
     <t xml:space="preserve">2.73000001907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60999989509583</t>
   </si>
 </sst>
 </file>
@@ -61169,6 +61172,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2237">
+      <c r="A2237" s="1" t="n">
+        <v>46157.2916666667</v>
+      </c>
+      <c r="B2237" t="n">
+        <v>6406</v>
+      </c>
+      <c r="C2237" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="D2237" t="n">
+        <v>2.53999996185303</v>
+      </c>
+      <c r="E2237" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="F2237" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="G2237" t="s">
+        <v>895</v>
+      </c>
+      <c r="H2237" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">SIT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44389152526855</t>
+    <t xml:space="preserve">9.44388961791992</t>
   </si>
   <si>
     <t xml:space="preserve">9.41868495941162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45229244232178</t>
+    <t xml:space="preserve">9.45229339599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.65394115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57832431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66234397888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.737961769104</t>
+    <t xml:space="preserve">9.5783224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73796272277832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67074584960938</t>
@@ -80,19 +80,19 @@
     <t xml:space="preserve">9.52791213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61193180084229</t>
+    <t xml:space="preserve">9.61193084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.64553928375244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53631401062012</t>
+    <t xml:space="preserve">9.5363130569458</t>
   </si>
   <si>
     <t xml:space="preserve">9.41028308868408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56152057647705</t>
+    <t xml:space="preserve">9.56151962280273</t>
   </si>
   <si>
     <t xml:space="preserve">9.51950931549072</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">9.49430370330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56992340087891</t>
+    <t xml:space="preserve">9.56992149353027</t>
   </si>
   <si>
     <t xml:space="preserve">9.74636459350586</t>
@@ -110,22 +110,22 @@
     <t xml:space="preserve">9.82198238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77157020568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76316833496094</t>
+    <t xml:space="preserve">9.77157115936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76316738128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.1832695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91440486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8555908203125</t>
+    <t xml:space="preserve">9.91440582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77997398376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85558986663818</t>
   </si>
   <si>
     <t xml:space="preserve">9.95641613006592</t>
@@ -137,19 +137,19 @@
     <t xml:space="preserve">10.0320329666138</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99002361297607</t>
+    <t xml:space="preserve">9.99002456665039</t>
   </si>
   <si>
     <t xml:space="preserve">9.88919925689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93961048126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572395324707</t>
+    <t xml:space="preserve">9.93961143493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057240486145</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656414031982</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">9.99842548370361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89759922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90600204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83038520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98162174224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.973219871521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62873458862305</t>
+    <t xml:space="preserve">10.0488386154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89760112762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90600299835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83038425445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98162078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62873649597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.72955989837646</t>
@@ -185,25 +185,25 @@
     <t xml:space="preserve">9.78837490081787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32626247406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28425312042236</t>
+    <t xml:space="preserve">9.36827278137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32626342773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24224281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28425121307373</t>
   </si>
   <si>
     <t xml:space="preserve">9.15822124481201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0742015838623</t>
+    <t xml:space="preserve">9.11621189117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07420063018799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94816970825195</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">9.03219032287598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33020687103271</t>
+    <t xml:space="preserve">9.28721046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33020782470703</t>
   </si>
   <si>
     <t xml:space="preserve">9.41619968414307</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">8.8572473526001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94323921203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07222843170166</t>
+    <t xml:space="preserve">8.94324016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07223033905029</t>
   </si>
   <si>
     <t xml:space="preserve">8.90024471282959</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">8.77125453948975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02923393249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20121765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45919609069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59926986694336</t>
+    <t xml:space="preserve">9.0292329788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2012186050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45919704437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59926891326904</t>
   </si>
   <si>
     <t xml:space="preserve">8.49607753753662</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">8.28969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34129047393799</t>
+    <t xml:space="preserve">8.3412914276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.42728424072266</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">8.51327705383301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22090244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32409286499023</t>
+    <t xml:space="preserve">8.22090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25529956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32409381866455</t>
   </si>
   <si>
     <t xml:space="preserve">8.35848999023438</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2381010055542</t>
+    <t xml:space="preserve">8.23810005187988</t>
   </si>
   <si>
     <t xml:space="preserve">8.53047561645508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13490962982178</t>
+    <t xml:space="preserve">8.13490772247314</t>
   </si>
   <si>
     <t xml:space="preserve">8.03171730041504</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87693023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82533597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56735754013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39537239074707</t>
+    <t xml:space="preserve">7.87693119049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82533550262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70494508743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">7.30937910079956</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">7.32657814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18898868560791</t>
+    <t xml:space="preserve">7.18898963928223</t>
   </si>
   <si>
     <t xml:space="preserve">6.99980545043945</t>
@@ -341,34 +341,34 @@
     <t xml:space="preserve">6.86221742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20618772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.739342212677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65334987640381</t>
+    <t xml:space="preserve">7.2061882019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73934316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65334939956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.48136425018311</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72214412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41256999969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53296041488647</t>
+    <t xml:space="preserve">7.72214317321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41256952285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53295993804932</t>
   </si>
   <si>
     <t xml:space="preserve">7.29217958450317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13739395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0857982635498</t>
+    <t xml:space="preserve">7.13739347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08579778671265</t>
   </si>
   <si>
     <t xml:space="preserve">7.06859970092773</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">6.70743036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10299634933472</t>
+    <t xml:space="preserve">7.10299682617188</t>
   </si>
   <si>
     <t xml:space="preserve">6.87941551208496</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7418270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63863563537598</t>
+    <t xml:space="preserve">6.74182748794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63863611221313</t>
   </si>
   <si>
     <t xml:space="preserve">6.79342317581177</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">6.98260641098022</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05140113830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75902605056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77622413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84501838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93101119995117</t>
+    <t xml:space="preserve">7.05140066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75902557373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7762246131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84501886367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93101167678833</t>
   </si>
   <si>
     <t xml:space="preserve">6.69023180007935</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">6.89661455154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01700401306152</t>
+    <t xml:space="preserve">7.01700353622437</t>
   </si>
   <si>
     <t xml:space="preserve">7.24058532714844</t>
@@ -434,28 +434,28 @@
     <t xml:space="preserve">7.46416664123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44696712493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61895227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34377574920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69634580612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61035442352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78233957290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43836784362793</t>
+    <t xml:space="preserve">7.44696760177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61895275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3437762260437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42976903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69634628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61035394668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78233909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43836736679077</t>
   </si>
   <si>
     <t xml:space="preserve">7.26638269424438</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">7.33315086364746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37759494781494</t>
+    <t xml:space="preserve">7.37759447097778</t>
   </si>
   <si>
     <t xml:space="preserve">7.51092433929443</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">7.11093425750732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15537786483765</t>
+    <t xml:space="preserve">7.1553783416748</t>
   </si>
   <si>
     <t xml:space="preserve">7.066490650177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2887077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55536699295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46648025512695</t>
+    <t xml:space="preserve">7.28870725631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55536794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46648120880127</t>
   </si>
   <si>
     <t xml:space="preserve">7.42203807830811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59981155395508</t>
+    <t xml:space="preserve">7.59981107711792</t>
   </si>
   <si>
     <t xml:space="preserve">7.19982147216797</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">7.022047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88871765136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760438919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66650056838989</t>
+    <t xml:space="preserve">6.88871812820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760391235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66650104522705</t>
   </si>
   <si>
     <t xml:space="preserve">6.57761478424072</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">6.71094465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39984083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44428396224976</t>
+    <t xml:space="preserve">6.39984035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44428443908691</t>
   </si>
   <si>
     <t xml:space="preserve">6.35539770126343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31095409393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22206735610962</t>
+    <t xml:space="preserve">6.31095457077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22206783294678</t>
   </si>
   <si>
     <t xml:space="preserve">6.13318109512329</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">5.95540714263916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0442943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17762422561646</t>
+    <t xml:space="preserve">6.04429388046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1776237487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.26651096343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99985074996948</t>
+    <t xml:space="preserve">5.99985122680664</t>
   </si>
   <si>
     <t xml:space="preserve">5.77763414382935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73319053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59986114501953</t>
+    <t xml:space="preserve">5.73319101333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59986066818237</t>
   </si>
   <si>
     <t xml:space="preserve">5.51097393035889</t>
@@ -581,52 +581,52 @@
     <t xml:space="preserve">5.68874788284302</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82207775115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86652040481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64430379867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55541706085205</t>
+    <t xml:space="preserve">5.82207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86652088165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6443042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55541753768921</t>
   </si>
   <si>
     <t xml:space="preserve">5.91096448898315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33320045471191</t>
+    <t xml:space="preserve">5.33320093154907</t>
   </si>
   <si>
     <t xml:space="preserve">5.46653079986572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37764453887939</t>
+    <t xml:space="preserve">5.37764406204224</t>
   </si>
   <si>
     <t xml:space="preserve">5.28875732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11098384857178</t>
+    <t xml:space="preserve">5.11098432540894</t>
   </si>
   <si>
     <t xml:space="preserve">4.71099424362183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35544681549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26656103134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07100963592529</t>
+    <t xml:space="preserve">4.35544729232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07101011276245</t>
   </si>
   <si>
     <t xml:space="preserve">4.17767381668091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24878358840942</t>
+    <t xml:space="preserve">4.24878311157227</t>
   </si>
   <si>
     <t xml:space="preserve">3.82212734222412</t>
@@ -635,31 +635,31 @@
     <t xml:space="preserve">3.78657293319702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99990034103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89323687553406</t>
+    <t xml:space="preserve">3.99990105628967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8932363986969</t>
   </si>
   <si>
     <t xml:space="preserve">3.85768222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73324012756348</t>
+    <t xml:space="preserve">3.73324060440063</t>
   </si>
   <si>
     <t xml:space="preserve">3.75101757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64435386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68879747390747</t>
+    <t xml:space="preserve">3.64435362815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68879723548889</t>
   </si>
   <si>
     <t xml:space="preserve">3.80435013771057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91101360321045</t>
+    <t xml:space="preserve">3.91101384162903</t>
   </si>
   <si>
     <t xml:space="preserve">4.04434394836426</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.08878707885742</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212361335754</t>
+    <t xml:space="preserve">3.98212313652039</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434593200684</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">3.95545697212219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76879501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90212512016296</t>
+    <t xml:space="preserve">3.76879477500916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90212488174438</t>
   </si>
   <si>
     <t xml:space="preserve">3.88434791564941</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83101606369019</t>
+    <t xml:space="preserve">3.83101558685303</t>
   </si>
   <si>
     <t xml:space="preserve">3.71546316146851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81323838233948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06212139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13323020935059</t>
+    <t xml:space="preserve">3.81323862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06212091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13323068618774</t>
   </si>
   <si>
     <t xml:space="preserve">4.10656452178955</t>
@@ -710,85 +710,85 @@
     <t xml:space="preserve">4.00878953933716</t>
   </si>
   <si>
+    <t xml:space="preserve">4.09767627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13434457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19851350784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38185453414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33601951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30851793289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36352062225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40935564041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268781661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32685232162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29935121536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26268291473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25351572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23518180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24434900283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28101682662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4826922416687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10684299468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17101240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12517690658569</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.09767580032349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13434457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19851350784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38185501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35435342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33601951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30851793289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36352109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40935611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268733978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3268518447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29935121536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26268291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25351572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23518133163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18934631347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24434900283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28101682662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4826922416687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10684299468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17101240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09767532348633</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.15267848968506</t>
   </si>
   <si>
     <t xml:space="preserve">4.18017959594727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21684741973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08850908279419</t>
+    <t xml:space="preserve">4.21684789657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08850860595703</t>
   </si>
   <si>
     <t xml:space="preserve">4.20768070220947</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">4.06100749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07934141159058</t>
+    <t xml:space="preserve">4.07934188842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.9876708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04267358779907</t>
+    <t xml:space="preserve">4.04267311096191</t>
   </si>
   <si>
     <t xml:space="preserve">4.03350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91433453559875</t>
+    <t xml:space="preserve">3.91433477401733</t>
   </si>
   <si>
     <t xml:space="preserve">3.99683833122253</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">3.89600038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86849904060364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88683319091797</t>
+    <t xml:space="preserve">3.86849927902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88683342933655</t>
   </si>
   <si>
     <t xml:space="preserve">4.11600971221924</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">4.49185943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51936054229736</t>
+    <t xml:space="preserve">4.51936006546021</t>
   </si>
   <si>
     <t xml:space="preserve">4.45519161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51019334793091</t>
+    <t xml:space="preserve">4.51019382476807</t>
   </si>
   <si>
     <t xml:space="preserve">3.96933698654175</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.81349682807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94183588027954</t>
+    <t xml:space="preserve">3.94183611869812</t>
   </si>
   <si>
     <t xml:space="preserve">4.34518623352051</t>
@@ -890,25 +890,25 @@
     <t xml:space="preserve">5.04188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96854639053345</t>
+    <t xml:space="preserve">4.96854686737061</t>
   </si>
   <si>
     <t xml:space="preserve">5.07855129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1152195930481</t>
+    <t xml:space="preserve">5.11521911621094</t>
   </si>
   <si>
     <t xml:space="preserve">5.17022180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13355350494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1518874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00521516799927</t>
+    <t xml:space="preserve">5.13355398178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15188789367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00521469116211</t>
   </si>
   <si>
     <t xml:space="preserve">5.02354907989502</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.22522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39023113250732</t>
+    <t xml:space="preserve">5.39023160934448</t>
   </si>
   <si>
     <t xml:space="preserve">5.26189231872559</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">5.51856994628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61024045944214</t>
+    <t xml:space="preserve">5.6102409362793</t>
   </si>
   <si>
     <t xml:space="preserve">5.68357706069946</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">6.03192520141602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88525247573853</t>
+    <t xml:space="preserve">6.01359128952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88525295257568</t>
   </si>
   <si>
     <t xml:space="preserve">5.9769229888916</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">6.05025959014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94025468826294</t>
+    <t xml:space="preserve">5.9402551651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.7752480506897</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">5.79358196258545</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83025074005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92192125320435</t>
+    <t xml:space="preserve">5.83025026321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92192077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.95858907699585</t>
@@ -980,16 +980,16 @@
     <t xml:space="preserve">6.141930103302</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19693326950073</t>
+    <t xml:space="preserve">6.19693279266357</t>
   </si>
   <si>
     <t xml:space="preserve">6.41694211959839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38027429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28860378265381</t>
+    <t xml:space="preserve">6.38027381896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28860330581665</t>
   </si>
   <si>
     <t xml:space="preserve">6.43527603149414</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">6.52694654464722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47194480895996</t>
+    <t xml:space="preserve">6.4719443321228</t>
   </si>
   <si>
     <t xml:space="preserve">6.45361042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56361532211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58194875717163</t>
+    <t xml:space="preserve">6.56361484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58194923400879</t>
   </si>
   <si>
     <t xml:space="preserve">6.60028314590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">6.6369514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54528093338013</t>
+    <t xml:space="preserve">6.61861753463745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54528045654297</t>
   </si>
   <si>
     <t xml:space="preserve">6.69195413589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85696077346802</t>
+    <t xml:space="preserve">6.85696125030518</t>
   </si>
   <si>
     <t xml:space="preserve">6.87529516220093</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">6.8019585609436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78362464904785</t>
+    <t xml:space="preserve">6.78362417221069</t>
   </si>
   <si>
     <t xml:space="preserve">6.966965675354</t>
@@ -61250,6 +61250,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2240">
+      <c r="A2240" s="1" t="n">
+        <v>46162.2916666667</v>
+      </c>
+      <c r="B2240" t="n">
+        <v>18318</v>
+      </c>
+      <c r="C2240" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="D2240" t="n">
+        <v>2.50999999046326</v>
+      </c>
+      <c r="E2240" t="n">
+        <v>2.60999989509583</v>
+      </c>
+      <c r="F2240" t="n">
+        <v>2.61999988555908</v>
+      </c>
+      <c r="G2240" t="s">
+        <v>885</v>
+      </c>
+      <c r="H2240" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394306182861</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394306182861</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>9.73796272277832</v>
+        <v>9.73796367645264</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>9.70435333251953</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G16" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G18" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>9.56152057647705</v>
+        <v>9.56151962280273</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>9.73796272277832</v>
+        <v>9.73796367645264</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G41" t="n">
-        <v>9.73796272277832</v>
+        <v>9.73796367645264</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157115936279</v>
+        <v>9.77157020568848</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157115936279</v>
+        <v>9.77157020568848</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832704544067</v>
+        <v>10.1832695007324</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G54" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>9.99002361297607</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G68" t="n">
-        <v>9.99002361297607</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656404495239</v>
+        <v>10.0656414031982</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G82" t="n">
-        <v>9.99002361297607</v>
+        <v>9.99002456665039</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440391540527</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488386154175</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>9.73796272277832</v>
+        <v>9.73796367645264</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G105" t="n">
-        <v>9.6371374130249</v>
+        <v>9.63713836669922</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873458862305</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873458862305</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394306182861</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72956085205078</v>
+        <v>9.72955989837646</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636459350586</v>
+        <v>9.74636363983154</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.70435333251953</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>9.70435333251953</v>
+        <v>9.70435428619385</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>11</v>
       </c>
       <c r="G159" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11</v>
       </c>
       <c r="G164" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="G165" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11</v>
       </c>
       <c r="G166" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>11</v>
       </c>
       <c r="G168" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>11</v>
       </c>
       <c r="G177" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>11</v>
       </c>
       <c r="G182" t="n">
-        <v>9.24224281311035</v>
+        <v>9.24224185943604</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.99018096923828</v>
+        <v>8.99018001556396</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.99018096923828</v>
+        <v>8.99018001556396</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.15822124481201</v>
+        <v>9.1582202911377</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G224" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G225" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>11</v>
       </c>
       <c r="G245" t="n">
-        <v>9.45919704437256</v>
+        <v>9.45919609069824</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>11</v>
       </c>
       <c r="G246" t="n">
-        <v>9.45919704437256</v>
+        <v>9.45919609069824</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07223033905029</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G267" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G269" t="n">
-        <v>8.77125549316406</v>
+        <v>8.77125453948975</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10</v>
       </c>
       <c r="G285" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.1693058013916</v>
+        <v>8.16930484771729</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.3412914276123</v>
+        <v>8.34129047393799</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490867614746</v>
+        <v>8.13490962982178</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171920776367</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171920776367</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494508743286</v>
+        <v>7.70494604110718</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.2061882019043</v>
+        <v>7.20618772506714</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.2061882019043</v>
+        <v>7.20618772506714</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.73934316635132</v>
+        <v>7.739342212677</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494508743286</v>
+        <v>7.70494604110718</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G340" t="n">
-        <v>7.29217958450317</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G341" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.9138126373291</v>
+        <v>6.91381311416626</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G360" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G361" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G363" t="n">
-        <v>6.7418270111084</v>
+        <v>6.74182748794556</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260641098022</v>
+        <v>6.98260688781738</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G372" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G376" t="n">
-        <v>6.77622509002686</v>
+        <v>6.7762246131897</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.9138126373291</v>
+        <v>6.91381311416626</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G399" t="n">
-        <v>6.89661407470703</v>
+        <v>6.89661455154419</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696807861328</v>
+        <v>7.44696712493896</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377670288086</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377670288086</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G429" t="n">
-        <v>7.29217958450317</v>
+        <v>7.29218006134033</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G430" t="n">
-        <v>7.13739347457886</v>
+        <v>7.13739395141602</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937910079956</v>
+        <v>7.30937814712524</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.73934316635132</v>
+        <v>7.739342212677</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136472702026</v>
+        <v>7.48136377334595</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233814239502</v>
+        <v>7.78233909606934</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735754013062</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759447097778</v>
+        <v>7.37759494781494</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536794662476</v>
+        <v>7.55536699295044</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759447097778</v>
+        <v>7.37759494781494</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648073196411</v>
+        <v>7.46648025512695</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>7.59981107711792</v>
+        <v>7.59981155395508</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7</v>
       </c>
       <c r="G554" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428443908691</v>
+        <v>6.44428396224976</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7</v>
       </c>
       <c r="G579" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7</v>
       </c>
       <c r="G580" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7</v>
       </c>
       <c r="G581" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>7</v>
       </c>
       <c r="G584" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7</v>
       </c>
       <c r="G585" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>7</v>
       </c>
       <c r="G589" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651048660278</v>
+        <v>6.26651096343994</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.75</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99985122680664</v>
+        <v>5.99985074996948</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>5.82207727432251</v>
+        <v>5.82207775115967</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7</v>
       </c>
       <c r="G611" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7</v>
       </c>
       <c r="G612" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7</v>
       </c>
       <c r="G613" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7</v>
       </c>
       <c r="G614" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7</v>
       </c>
       <c r="G615" t="n">
-        <v>6.22206783294678</v>
+        <v>6.22206735610962</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.04429388046265</v>
+        <v>6.0442943572998</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.75</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99985122680664</v>
+        <v>5.99985074996948</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541753768921</v>
+        <v>5.55541706085205</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.7776346206665</v>
+        <v>5.77763414382935</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6</v>
       </c>
       <c r="G655" t="n">
-        <v>5.33320093154907</v>
+        <v>5.33320045471191</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.33320093154907</v>
+        <v>5.33320045471191</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.75</v>
       </c>
       <c r="G664" t="n">
-        <v>5.11098432540894</v>
+        <v>5.11098384857178</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07101011276245</v>
+        <v>4.07100963592529</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323687553406</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324036598206</v>
+        <v>3.73324012756348</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G684" t="n">
-        <v>3.68879723548889</v>
+        <v>3.68879747390747</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101360321045</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>4.5</v>
       </c>
       <c r="G689" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G690" t="n">
-        <v>4.08878755569458</v>
+        <v>4.08878707885742</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212361335754</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101360321045</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101360321045</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>4.5</v>
       </c>
       <c r="G698" t="n">
-        <v>3.99990081787109</v>
+        <v>3.99990034103394</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212361335754</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212313652039</v>
+        <v>3.98212361335754</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101408004761</v>
+        <v>3.91101360321045</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323687553406</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G703" t="n">
-        <v>3.76879477500916</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G711" t="n">
-        <v>3.76879477500916</v>
+        <v>3.76879501342773</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>3.8932363986969</v>
+        <v>3.89323687553406</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G719" t="n">
-        <v>4.08878755569458</v>
+        <v>4.08878707885742</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -58664,6 +58664,32 @@
         <v>2.34999990463257</v>
       </c>
       <c r="H2242" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="1" t="n">
+        <v>46167.2916666667</v>
+      </c>
+      <c r="B2243" t="n">
+        <v>75802</v>
+      </c>
+      <c r="C2243" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D2243" t="n">
+        <v>2.21000003814697</v>
+      </c>
+      <c r="E2243" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="F2243" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="G2243" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="H2243" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868591308594</v>
+        <v>9.41868495941162</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>11.25</v>
       </c>
       <c r="G5" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.65394306182861</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.65394306182861</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>11.25</v>
       </c>
       <c r="G28" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992244720459</v>
+        <v>9.56992149353027</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992244720459</v>
+        <v>9.56992149353027</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G42" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G44" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G48" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997303009033</v>
+        <v>9.77997207641602</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>9.8555908203125</v>
+        <v>9.85558986663818</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961143493652</v>
+        <v>9.93961048126221</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.9984245300293</v>
+        <v>9.99842548370361</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.9984245300293</v>
+        <v>9.99842548370361</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>11.8800001144409</v>
       </c>
       <c r="G98" t="n">
-        <v>9.98162078857422</v>
+        <v>9.98162174224854</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.973219871521</v>
+        <v>9.97321891784668</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>9.8555908203125</v>
+        <v>9.85558986663818</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873458862305</v>
+        <v>9.62873554229736</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873458862305</v>
+        <v>9.62873554229736</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.65394306182861</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553928375244</v>
+        <v>9.64553833007812</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72955989837646</v>
+        <v>9.72956085205078</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G116" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G124" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G125" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>9.74636363983154</v>
+        <v>9.74636459350586</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>11.25</v>
       </c>
       <c r="G157" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425312042236</v>
+        <v>9.28425216674805</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>9.57832336425781</v>
+        <v>9.57832431793213</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>11.25</v>
       </c>
       <c r="G180" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>11.25</v>
       </c>
       <c r="G181" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G183" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94816970825195</v>
+        <v>8.94817161560059</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94816970825195</v>
+        <v>8.94817161560059</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>9.1582202911377</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623561859131</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825908660889</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623561859131</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07223033905029</v>
+        <v>9.07222938537598</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>8.28969573974609</v>
+        <v>8.28969669342041</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>8.28969573974609</v>
+        <v>8.28969669342041</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825908660889</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825908660889</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10</v>
       </c>
       <c r="G285" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G289" t="n">
-        <v>8.25529956817627</v>
+        <v>8.25529861450195</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.16930484771729</v>
+        <v>8.1693058013916</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59926891326904</v>
+        <v>8.59926986694336</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047561645508</v>
+        <v>8.53047466278076</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171730041504</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171825408936</v>
+        <v>8.03171730041504</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693023681641</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693023681641</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533550262451</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533550262451</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G337" t="n">
-        <v>7.41257047653198</v>
+        <v>7.41256999969482</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.08579778671265</v>
+        <v>7.0857982635498</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G343" t="n">
-        <v>7.06860017776489</v>
+        <v>7.06859970092773</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.08579778671265</v>
+        <v>7.0857982635498</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980545043945</v>
+        <v>6.99980592727661</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>6.91381311416626</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63863611221313</v>
+        <v>6.63863563537598</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902557373047</v>
+        <v>6.75902605056763</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>6.91381311416626</v>
+        <v>6.9138126373291</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023180007935</v>
+        <v>6.69023132324219</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902557373047</v>
+        <v>6.75902605056763</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058485031128</v>
+        <v>7.24058532714844</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416664123535</v>
+        <v>7.46416568756104</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895227432251</v>
+        <v>7.61895322799683</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G419" t="n">
-        <v>7.41257047653198</v>
+        <v>7.41256999969482</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377574920654</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377574920654</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976856231689</v>
+        <v>7.42976903915405</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.30937814712524</v>
+        <v>7.3093786239624</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035346984863</v>
+        <v>7.61035394668579</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.25</v>
       </c>
       <c r="G459" t="n">
-        <v>7.33315086364746</v>
+        <v>7.33315134048462</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.25</v>
       </c>
       <c r="G460" t="n">
-        <v>7.33315086364746</v>
+        <v>7.33315134048462</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.25</v>
       </c>
       <c r="G467" t="n">
-        <v>7.33315086364746</v>
+        <v>7.33315134048462</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.55536699295044</v>
+        <v>7.5553674697876</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.25</v>
       </c>
       <c r="G478" t="n">
-        <v>7.33315086364746</v>
+        <v>7.33315134048462</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8</v>
       </c>
       <c r="G498" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8</v>
       </c>
       <c r="G504" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8</v>
       </c>
       <c r="G505" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8</v>
       </c>
       <c r="G506" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8</v>
       </c>
       <c r="G509" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8</v>
       </c>
       <c r="G511" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8</v>
       </c>
       <c r="G512" t="n">
-        <v>7.11093425750732</v>
+        <v>7.11093473434448</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.066490650177</v>
+        <v>7.06649112701416</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650056838989</v>
+        <v>6.66650104522705</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>7.25</v>
       </c>
       <c r="G536" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>7.25</v>
       </c>
       <c r="G537" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>7.25</v>
       </c>
       <c r="G538" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>7.25</v>
       </c>
       <c r="G539" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>7.25</v>
       </c>
       <c r="G541" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761478424072</v>
+        <v>6.57761430740356</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G551" t="n">
-        <v>6.53317070007324</v>
+        <v>6.5331711769104</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>7.25</v>
       </c>
       <c r="G553" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>7</v>
       </c>
       <c r="G554" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>7.25</v>
       </c>
       <c r="G575" t="n">
-        <v>6.44428396224976</v>
+        <v>6.44428443908691</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>7</v>
       </c>
       <c r="G579" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>7</v>
       </c>
       <c r="G580" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>7</v>
       </c>
       <c r="G581" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>7</v>
       </c>
       <c r="G584" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>7</v>
       </c>
       <c r="G585" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>7</v>
       </c>
       <c r="G589" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7</v>
       </c>
       <c r="G611" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7</v>
       </c>
       <c r="G612" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7</v>
       </c>
       <c r="G613" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7</v>
       </c>
       <c r="G614" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7</v>
       </c>
       <c r="G615" t="n">
-        <v>6.22206735610962</v>
+        <v>6.22206783294678</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540714263916</v>
+        <v>5.95540761947632</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652040481567</v>
+        <v>5.86652088165283</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>6.25</v>
       </c>
       <c r="G645" t="n">
-        <v>5.55541706085205</v>
+        <v>5.55541753768921</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.64430379867554</v>
+        <v>5.6443042755127</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874788284302</v>
+        <v>5.68874740600586</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>6</v>
       </c>
       <c r="G655" t="n">
-        <v>5.33320045471191</v>
+        <v>5.33320093154907</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>6</v>
       </c>
       <c r="G661" t="n">
-        <v>5.33320045471191</v>
+        <v>5.33320093154907</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764453887939</v>
+        <v>5.37764406204224</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544681549072</v>
+        <v>4.35544729232788</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656103134155</v>
+        <v>4.26656055450439</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G668" t="n">
-        <v>4.07100963592529</v>
+        <v>4.07101011276245</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.89323687553406</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G686" t="n">
-        <v>3.91101360321045</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G691" t="n">
-        <v>3.98212361335754</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G692" t="n">
-        <v>3.96434593200684</v>
+        <v>3.96434617042542</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>3.85768222808838</v>
+        <v>3.8576819896698</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G695" t="n">
-        <v>3.91101360321045</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>3.91101360321045</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G699" t="n">
-        <v>3.98212361335754</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G700" t="n">
-        <v>3.98212361335754</v>
+        <v>3.98212337493896</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G701" t="n">
-        <v>3.91101360321045</v>
+        <v>3.91101384162903</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G702" t="n">
-        <v>3.89323687553406</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G705" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G706" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G708" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101582527161</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G709" t="n">
-        <v>3.83101606369019</v>
+        <v>3.83101582527161</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G710" t="n">
-        <v>3.71546316146851</v>
+        <v>3.71546339988708</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G713" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G714" t="n">
-        <v>3.78657293319702</v>
+        <v>3.78657269477844</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>3.88434791564941</v>
+        <v>3.88434743881226</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G718" t="n">
-        <v>3.89323687553406</v>
+        <v>3.89323663711548</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G720" t="n">
-        <v>4.06212139129639</v>
+        <v>4.06212091445923</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>4.13323020935059</v>
+        <v>4.13323068618774</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G722" t="n">
-        <v>4.10656452178955</v>
+        <v>4.10656404495239</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G723" t="n">
-        <v>4.10656452178955</v>
+        <v>4.10656404495239</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>4.6100001335144</v>
       </c>
       <c r="G727" t="n">
-        <v>4.09767580032349</v>
+        <v>4.09767627716064</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -58690,6 +58690,32 @@
         <v>2.22000002861023</v>
       </c>
       <c r="H2243" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="1" t="n">
+        <v>46168.2916666667</v>
+      </c>
+      <c r="B2244" t="n">
+        <v>46328</v>
+      </c>
+      <c r="C2244" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="D2244" t="n">
+        <v>2.14000010490417</v>
+      </c>
+      <c r="E2244" t="n">
+        <v>2.16000008583069</v>
+      </c>
+      <c r="F2244" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="G2244" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="H2244" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44389057159424</v>
+        <v>9.44388961791992</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868495941162</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G7" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G11" t="n">
-        <v>9.73796367645264</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074584960938</v>
+        <v>9.67074680328369</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G13" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G22" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188026428223</v>
+        <v>9.40188121795654</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992149353027</v>
+        <v>9.56992244720459</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G40" t="n">
-        <v>9.73796367645264</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G41" t="n">
-        <v>9.73796367645264</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77157115936279</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157020568848</v>
+        <v>9.77157115936279</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832695007324</v>
+        <v>10.1832704544067</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>9.85558986663818</v>
+        <v>9.8555908203125</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961048126221</v>
+        <v>9.93961143493652</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.95641613006592</v>
+        <v>9.9564151763916</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>11.9700002670288</v>
       </c>
       <c r="G73" t="n">
-        <v>10.057240486145</v>
+        <v>10.0572395324707</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656414031982</v>
+        <v>10.0656404495239</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320320129395</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.99842548370361</v>
+        <v>9.9984245300293</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440391540527</v>
+        <v>9.91440486907959</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G99" t="n">
-        <v>9.97321891784668</v>
+        <v>9.973219871521</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>9.85558986663818</v>
+        <v>9.8555908203125</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198238372803</v>
+        <v>9.82198333740234</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G104" t="n">
-        <v>9.73796367645264</v>
+        <v>9.73796272277832</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873458862305</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873458862305</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G109" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G113" t="n">
-        <v>9.64553833007812</v>
+        <v>9.64553928375244</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72956085205078</v>
+        <v>9.72955989837646</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G148" t="n">
-        <v>9.62033462524414</v>
+        <v>9.62033367156982</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G151" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G152" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234397888184</v>
+        <v>9.66234302520752</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425216674805</v>
+        <v>9.28425312042236</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>9.57832431793213</v>
+        <v>9.57832336425781</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430370330811</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>9.41028308868408</v>
+        <v>9.41028213500977</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827278137207</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94817161560059</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94817161560059</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.99018001556396</v>
+        <v>8.99018096923828</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.99018001556396</v>
+        <v>8.99018096923828</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.0742015838623</v>
+        <v>9.07420063018799</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623561859131</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825908660889</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623561859131</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>9.20121765136719</v>
+        <v>9.2012186050415</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94324016571045</v>
+        <v>8.94323921203613</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>8.28969669342041</v>
+        <v>8.28969573974609</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>8.28969669342041</v>
+        <v>8.28969573974609</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G278" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825908660889</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825908660889</v>
+        <v>8.72825813293457</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008472442627</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008472442627</v>
+        <v>8.41008567810059</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.1693058013916</v>
+        <v>8.16930484771729</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047466278076</v>
+        <v>8.53047561645508</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490962982178</v>
+        <v>8.13490867614746</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693119049072</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533550262451</v>
+        <v>7.82533502578735</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494604110718</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G320" t="n">
-        <v>7.32657814025879</v>
+        <v>7.32657766342163</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G321" t="n">
-        <v>7.32657814025879</v>
+        <v>7.32657766342163</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898916244507</v>
+        <v>7.18898963928223</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533550262451</v>
+        <v>7.82533502578735</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494604110718</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023132324219</v>
+        <v>6.69023180007935</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.87941551208496</v>
+        <v>6.87941598892212</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058532714844</v>
+        <v>7.24058485031128</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416568756104</v>
+        <v>7.46416616439819</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696712493896</v>
+        <v>7.44696760177612</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895322799683</v>
+        <v>7.61895227432251</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214317321777</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295993804932</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.34377574920654</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.34377574920654</v>
+        <v>7.3437762260437</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976903915405</v>
+        <v>7.42976856231689</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035394668579</v>
+        <v>7.61035346984863</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735706329346</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836784362793</v>
+        <v>7.43836832046509</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -58716,6 +58716,32 @@
         <v>2.1800000667572</v>
       </c>
       <c r="H2244" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" s="1" t="n">
+        <v>46169.2916666667</v>
+      </c>
+      <c r="B2245" t="n">
+        <v>56910</v>
+      </c>
+      <c r="C2245" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D2245" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="E2245" t="n">
+        <v>2.15000009536743</v>
+      </c>
+      <c r="F2245" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="G2245" t="n">
+        <v>2.20000004768372</v>
+      </c>
+      <c r="H2245" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44388961791992</v>
+        <v>9.44389057159424</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868591308594</v>
+        <v>9.41868495941162</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074680328369</v>
+        <v>9.67074584960938</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193084716797</v>
+        <v>9.61193180084229</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193084716797</v>
+        <v>9.61193180084229</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G26" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G27" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791118621826</v>
+        <v>9.52791213989258</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G46" t="n">
-        <v>9.77157115936279</v>
+        <v>9.77157020568848</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G49" t="n">
-        <v>9.77157115936279</v>
+        <v>9.77157020568848</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832704544067</v>
+        <v>10.1832695007324</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G55" t="n">
-        <v>9.8555908203125</v>
+        <v>9.85558986663818</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G57" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G58" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G65" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G67" t="n">
-        <v>9.93961143493652</v>
+        <v>9.93961048126221</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G69" t="n">
-        <v>9.9564151763916</v>
+        <v>9.95641613006592</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.9984245300293</v>
+        <v>9.99842548370361</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320320129395</v>
+        <v>10.0320329666138</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.9984245300293</v>
+        <v>9.99842548370361</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600395202637</v>
+        <v>9.90600299835205</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600395202637</v>
+        <v>9.90600299835205</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488367080688</v>
+        <v>10.0488376617432</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88919925689697</v>
+        <v>9.88920021057129</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G101" t="n">
-        <v>9.8555908203125</v>
+        <v>9.85558986663818</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G102" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>11.6899995803833</v>
       </c>
       <c r="G103" t="n">
-        <v>9.82198333740234</v>
+        <v>9.82198238372803</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873458862305</v>
+        <v>9.62873554229736</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873458862305</v>
+        <v>9.62873554229736</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.6539421081543</v>
+        <v>9.65394115447998</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72955989837646</v>
+        <v>9.72956085205078</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038425445557</v>
+        <v>9.83038520812988</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837490081787</v>
+        <v>9.78837394714355</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827373504639</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827373504639</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827373504639</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.53631401062012</v>
+        <v>9.5363130569458</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827373504639</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827373504639</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827373504639</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G169" t="n">
-        <v>9.28425312042236</v>
+        <v>9.28425216674805</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827373504639</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G171" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430370330811</v>
+        <v>9.49430274963379</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G175" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G176" t="n">
-        <v>9.41028213500977</v>
+        <v>9.41028308868408</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827182769775</v>
+        <v>9.36827373504639</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G185" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94816970825195</v>
+        <v>8.94817161560059</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94816970825195</v>
+        <v>8.94817161560059</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G189" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.1162109375</v>
+        <v>9.11621189117432</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219032287598</v>
+        <v>9.03219127655029</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G199" t="n">
-        <v>9.07420063018799</v>
+        <v>9.0742015838623</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623561859131</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825908660889</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G219" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G220" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623657226562</v>
+        <v>8.98623561859131</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G235" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G241" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>9.15822124481201</v>
+        <v>9.15822219848633</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G243" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G250" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G251" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G252" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G254" t="n">
-        <v>9.2012186050415</v>
+        <v>9.20121765136719</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G259" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G261" t="n">
-        <v>8.94323921203613</v>
+        <v>8.94324016571045</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.0292329788208</v>
+        <v>9.02923202514648</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>8.28969573974609</v>
+        <v>8.28969669342041</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>8.28969573974609</v>
+        <v>8.28969669342041</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G278" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825908660889</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825813293457</v>
+        <v>8.72825908660889</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G292" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G293" t="n">
-        <v>8.41008567810059</v>
+        <v>8.41008472442627</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.16930484771729</v>
+        <v>8.1693058013916</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047561645508</v>
+        <v>8.53047466278076</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.42728424072266</v>
+        <v>8.42728328704834</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490867614746</v>
+        <v>8.13490962982178</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693119049072</v>
+        <v>7.87693071365356</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533550262451</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494604110718</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G320" t="n">
-        <v>7.32657766342163</v>
+        <v>7.32657814025879</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G321" t="n">
-        <v>7.32657766342163</v>
+        <v>7.32657814025879</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898963928223</v>
+        <v>7.18898916244507</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533502578735</v>
+        <v>7.82533550262451</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494556427002</v>
+        <v>7.70494604110718</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023180007935</v>
+        <v>6.69023132324219</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101167678833</v>
+        <v>6.93101119995117</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.87941598892212</v>
+        <v>6.87941551208496</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540880203247</v>
+        <v>6.96540832519531</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058485031128</v>
+        <v>7.24058532714844</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416616439819</v>
+        <v>7.46416568756104</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G414" t="n">
-        <v>7.44696760177612</v>
+        <v>7.44696712493896</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895227432251</v>
+        <v>7.61895322799683</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214317321777</v>
+        <v>7.72214365005493</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53295993804932</v>
+        <v>7.53296041488647</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G420" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377574920654</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>7.3437762260437</v>
+        <v>7.34377574920654</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G427" t="n">
-        <v>7.42976856231689</v>
+        <v>7.42976903915405</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035346984863</v>
+        <v>7.61035394668579</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634580612183</v>
+        <v>7.69634628295898</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.56735706329346</v>
+        <v>7.5673565864563</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G446" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G447" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G449" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G450" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G451" t="n">
-        <v>7.43836832046509</v>
+        <v>7.43836784362793</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537191390991</v>
+        <v>7.39537143707275</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -58742,6 +58742,32 @@
         <v>2.20000004768372</v>
       </c>
       <c r="H2245" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="1" t="n">
+        <v>46170.2916666667</v>
+      </c>
+      <c r="B2246" t="n">
+        <v>13717</v>
+      </c>
+      <c r="C2246" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D2246" t="n">
+        <v>2.1800000667572</v>
+      </c>
+      <c r="E2246" t="n">
+        <v>2.22000002861023</v>
+      </c>
+      <c r="F2246" t="n">
+        <v>2.21000003814697</v>
+      </c>
+      <c r="G2246" t="n">
+        <v>2.21000003814697</v>
+      </c>
+      <c r="H2246" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/SIT.MI.xlsx
+++ b/data/SIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G2" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G3" t="n">
-        <v>9.44389057159424</v>
+        <v>9.44389152526855</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G4" t="n">
-        <v>9.41868495941162</v>
+        <v>9.41868591308594</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G6" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G8" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>11.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67074584960938</v>
+        <v>9.67074680328369</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G14" t="n">
-        <v>9.70435428619385</v>
+        <v>9.70435333251953</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>11.5</v>
       </c>
       <c r="G15" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G17" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G20" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>9.61193180084229</v>
+        <v>9.61193084716797</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G24" t="n">
-        <v>9.40188121795654</v>
+        <v>9.40188026428223</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G31" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>9.56992244720459</v>
+        <v>9.56992053985596</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G34" t="n">
-        <v>9.52791213989258</v>
+        <v>9.52791118621826</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G35" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G36" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>11.3900003433228</v>
       </c>
       <c r="G37" t="n">
-        <v>9.56992244720459</v>
+        <v>9.56992053985596</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G38" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>11.5</v>
       </c>
       <c r="G47" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G50" t="n">
-        <v>9.76316833496094</v>
+        <v>9.76316928863525</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1832695007324</v>
+        <v>10.1832704544067</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G53" t="n">
-        <v>9.77997207641602</v>
+        <v>9.77997303009033</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G56" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G60" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G61" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G62" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G63" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G64" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G66" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G68" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G71" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G72" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G74" t="n">
-        <v>10.0656404495239</v>
+        <v>10.0656414031982</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>9.99842548370361</v>
+        <v>9.99842643737793</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G76" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G77" t="n">
-        <v>10.0320329666138</v>
+        <v>10.0320339202881</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>9.99842548370361</v>
+        <v>9.99842643737793</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G80" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G82" t="n">
-        <v>9.99002456665039</v>
+        <v>9.99002361297607</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G85" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G86" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>11.789999961853</v>
       </c>
       <c r="G88" t="n">
-        <v>9.90600299835205</v>
+        <v>9.90600395202637</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G89" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G90" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G94" t="n">
-        <v>9.91440486907959</v>
+        <v>9.91440582275391</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G96" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G97" t="n">
-        <v>10.0488376617432</v>
+        <v>10.0488367080688</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>9.88920021057129</v>
+        <v>9.88919925689697</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G106" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873649597168</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>9.62873554229736</v>
+        <v>9.62873649597168</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G108" t="n">
-        <v>9.65394115447998</v>
+        <v>9.6539421081543</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>11.5</v>
       </c>
       <c r="G110" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G112" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>11.5</v>
       </c>
       <c r="G114" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G115" t="n">
-        <v>9.72956085205078</v>
+        <v>9.72955989837646</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G117" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G119" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G121" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G122" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G123" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G127" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G128" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G129" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G131" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G135" t="n">
-        <v>9.83038520812988</v>
+        <v>9.83038425445557</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>11.5</v>
       </c>
       <c r="G136" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.5</v>
       </c>
       <c r="G137" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>9.78837394714355</v>
+        <v>9.78837490081787</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G140" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G141" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>9.36827373504639</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G146" t="n">
-        <v>9.36827373504639</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G147" t="n">
-        <v>9.36827373504639</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G149" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G150" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G153" t="n">
-        <v>9.70435428619385</v>
+        <v>9.70435333251953</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>11.5</v>
       </c>
       <c r="G154" t="n">
-        <v>9.66234302520752</v>
+        <v>9.66234397888184</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>9.5363130569458</v>
+        <v>9.53631401062012</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G156" t="n">
-        <v>9.70435428619385</v>
+        <v>9.70435333251953</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>9.36827373504639</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G162" t="n">
-        <v>9.36827373504639</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G163" t="n">
-        <v>9.36827373504639</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G170" t="n">
-        <v>9.36827373504639</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G172" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G174" t="n">
-        <v>9.49430274963379</v>
+        <v>9.49430465698242</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G179" t="n">
-        <v>9.36827373504639</v>
+        <v>9.36827182769775</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G186" t="n">
-        <v>8.94817161560059</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G187" t="n">
-        <v>8.94817161560059</v>
+        <v>8.94816970825195</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>8.99018096923828</v>
+        <v>8.99018001556396</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.75</v>
       </c>
       <c r="G190" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G192" t="n">
-        <v>9.11621189117432</v>
+        <v>9.1162109375</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.75</v>
       </c>
       <c r="G193" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.75</v>
       </c>
       <c r="G194" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G195" t="n">
-        <v>8.99018096923828</v>
+        <v>8.99018001556396</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>10.75</v>
       </c>
       <c r="G196" t="n">
-        <v>9.03219127655029</v>
+        <v>9.03219032287598</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G202" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G203" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G205" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G206" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G207" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G210" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G211" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G214" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G216" t="n">
-        <v>8.98623561859131</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G217" t="n">
-        <v>8.72825908660889</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G222" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07222843170166</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G223" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024375915527</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>8.90024471282959</v>
+        <v>8.90024375915527</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>8.98623561859131</v>
+        <v>8.98623657226562</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>10.5</v>
       </c>
       <c r="G228" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G230" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G231" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>9.33020782470703</v>
+        <v>9.33020687103271</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G234" t="n">
-        <v>9.11522579193115</v>
+        <v>9.11522483825684</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G236" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G237" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>10.5</v>
       </c>
       <c r="G238" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G240" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>9.15822219848633</v>
+        <v>9.15822124481201</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G244" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G247" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G248" t="n">
-        <v>9.28721046447754</v>
+        <v>9.28721141815186</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>10.5</v>
       </c>
       <c r="G255" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>10.5</v>
       </c>
       <c r="G256" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>10.5</v>
       </c>
       <c r="G257" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>10.5</v>
       </c>
       <c r="G258" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>10.5</v>
       </c>
       <c r="G262" t="n">
-        <v>9.02923202514648</v>
+        <v>9.0292329788208</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G264" t="n">
-        <v>9.07222938537598</v>
+        <v>9.07222843170166</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>10</v>
       </c>
       <c r="G270" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G272" t="n">
-        <v>8.28969669342041</v>
+        <v>8.28969573974609</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>9.64000034332275</v>
       </c>
       <c r="G273" t="n">
-        <v>8.28969669342041</v>
+        <v>8.28969573974609</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G274" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G276" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G277" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G278" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G279" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G280" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G281" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G283" t="n">
-        <v>8.72825908660889</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>8.72825908660889</v>
+        <v>8.72825717926025</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>10</v>
       </c>
       <c r="G285" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G287" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>9.5</v>
       </c>
       <c r="G296" t="n">
-        <v>8.1693058013916</v>
+        <v>8.16930675506592</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>10</v>
       </c>
       <c r="G299" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>10</v>
       </c>
       <c r="G300" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>10</v>
       </c>
       <c r="G301" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>10</v>
       </c>
       <c r="G302" t="n">
-        <v>8.59926986694336</v>
+        <v>8.59926891326904</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G303" t="n">
-        <v>8.53047466278076</v>
+        <v>8.53047561645508</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G304" t="n">
-        <v>8.42728328704834</v>
+        <v>8.42728424072266</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G305" t="n">
-        <v>8.34129047393799</v>
+        <v>8.3412914276123</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G306" t="n">
-        <v>8.13490962982178</v>
+        <v>8.13490867614746</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G307" t="n">
-        <v>8.03171730041504</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>8.03171730041504</v>
+        <v>8.03171825408936</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G310" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>9.15999984741211</v>
       </c>
       <c r="G311" t="n">
-        <v>7.87693071365356</v>
+        <v>7.87693023681641</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G312" t="n">
-        <v>7.82533550262451</v>
+        <v>7.82533597946167</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>7.70494604110718</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G314" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G315" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G316" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G317" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>8.5</v>
       </c>
       <c r="G318" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G322" t="n">
-        <v>7.18898916244507</v>
+        <v>7.18898868560791</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G323" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G324" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G325" t="n">
-        <v>7.20618772506714</v>
+        <v>7.20618724822998</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G326" t="n">
-        <v>7.20618772506714</v>
+        <v>7.20618724822998</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>9</v>
       </c>
       <c r="G327" t="n">
-        <v>7.739342212677</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G328" t="n">
-        <v>7.82533550262451</v>
+        <v>7.82533597946167</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G329" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G330" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G331" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G332" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G333" t="n">
-        <v>7.70494604110718</v>
+        <v>7.70494556427002</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G335" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G336" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G338" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295946121216</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G339" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G342" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G345" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G346" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G347" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G348" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G349" t="n">
-        <v>7.0857982635498</v>
+        <v>7.08579778671265</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G350" t="n">
-        <v>6.99980592727661</v>
+        <v>6.99980545043945</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G351" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G355" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G356" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G357" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G358" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>8</v>
       </c>
       <c r="G359" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>8</v>
       </c>
       <c r="G362" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G364" t="n">
-        <v>6.63863563537598</v>
+        <v>6.63863611221313</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G367" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>8</v>
       </c>
       <c r="G368" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G369" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G371" t="n">
-        <v>6.98260688781738</v>
+        <v>6.98260641098022</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G379" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G380" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>8</v>
       </c>
       <c r="G381" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>8</v>
       </c>
       <c r="G382" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G383" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G384" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G385" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G386" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G387" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G388" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>8</v>
       </c>
       <c r="G390" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G391" t="n">
-        <v>6.86221694946289</v>
+        <v>6.86221742630005</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G393" t="n">
-        <v>6.69023132324219</v>
+        <v>6.69023180007935</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>8</v>
       </c>
       <c r="G394" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G395" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G397" t="n">
-        <v>6.94820976257324</v>
+        <v>6.94820928573608</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G398" t="n">
-        <v>6.93101119995117</v>
+        <v>6.93101167678833</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>8</v>
       </c>
       <c r="G402" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>8</v>
       </c>
       <c r="G403" t="n">
-        <v>6.87941551208496</v>
+        <v>6.8794150352478</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G405" t="n">
-        <v>6.75902605056763</v>
+        <v>6.75902557373047</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G408" t="n">
-        <v>6.96540832519531</v>
+        <v>6.96540880203247</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G409" t="n">
-        <v>7.24058532714844</v>
+        <v>7.24058485031128</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>8.68000030517578</v>
       </c>
       <c r="G410" t="n">
-        <v>7.46416568756104</v>
+        <v>7.46416664123535</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G411" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295946121216</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G412" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G413" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G415" t="n">
-        <v>7.61895322799683</v>
+        <v>7.61895227432251</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G416" t="n">
-        <v>7.72214365005493</v>
+        <v>7.72214412689209</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G417" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G418" t="n">
-        <v>7.53296041488647</v>
+        <v>7.53295946121216</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>8.5</v>
       </c>
       <c r="G423" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G424" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G426" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>8.5</v>
       </c>
       <c r="G428" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>8.5</v>
       </c>
       <c r="G431" t="n">
-        <v>7.3093786239624</v>
+        <v>7.30937910079956</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G432" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>9</v>
       </c>
       <c r="G433" t="n">
-        <v>7.739342212677</v>
+        <v>7.73934316635132</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G434" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G435" t="n">
-        <v>7.65334939956665</v>
+        <v>7.65334987640381</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G436" t="n">
-        <v>7.48136377334595</v>
+        <v>7.48136472702026</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G437" t="n">
-        <v>7.61035394668579</v>
+        <v>7.61035442352295</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G438" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G439" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G440" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>7.78233909606934</v>
+        <v>7.78233861923218</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G443" t="n">
-        <v>7.69634628295898</v>
+        <v>7.69634580612183</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G445" t="n">
-        <v>7.5673565864563</v>
+        <v>7.56735754013062</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G452" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G453" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G454" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G455" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G456" t="n">
-        <v>7.39537143707275</v>
+        <v>7.39537191390991</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>8.25</v>
       </c>
       <c r="G459" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>8.25</v>
       </c>
       <c r="G460" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G461" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>8.25</v>
       </c>
       <c r="G467" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>8</v>
       </c>
       <c r="G468" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G470" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>8.5</v>
       </c>
       <c r="G474" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>8.5</v>
       </c>
       <c r="G475" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>8.5</v>
       </c>
       <c r="G476" t="n">
-        <v>7.5553674697876</v>
+        <v>7.55536794662476</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G477" t="n">
-        <v>7.37759494781494</v>
+        <v>7.37759447097778</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>8.25</v>
       </c>
       <c r="G478" t="n">
-        <v>7.33315134048462</v>
+        <v>7.33315086364746</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G480" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G481" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G482" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G493" t="n">
-        <v>7.46648025512695</v>
+        <v>7.46648073196411</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G494" t="n">
-        <v>7.59981155395508</v>
+        <v>7.59981107711792</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>8</v>
       </c>
       <c r="G498" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G499" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>8</v>
       </c>
       <c r="G500" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G501" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G502" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>8</v>
       </c>
       <c r="G504" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>8</v>
       </c>
       <c r="G505" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>8</v>
       </c>
       <c r="G506" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>8</v>
       </c>
       <c r="G509" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>8</v>
       </c>
       <c r="G511" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>8</v>
       </c>
       <c r="G512" t="n">
-        <v>7.11093473434448</v>
+        <v>7.11093425750732</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G513" t="n">
-        <v>7.06649112701416</v>
+        <v>7.066490650177</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>7.5</v>
       </c>
       <c r="G517" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G518" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>7.5</v>
       </c>
       <c r="G519" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>7.5</v>
       </c>
       <c r="G520" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G521" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>7.5</v>
       </c>
       <c r="G525" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>7.5</v>
       </c>
       <c r="G526" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>7.5</v>
       </c>
       <c r="G527" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>7.5</v>
       </c>
       <c r="G528" t="n">
-        <v>6.66650104522705</v>
+        <v>6.66650056838989</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G530" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G531" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G535" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G545" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G548" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G549" t="n">
-        <v>6.57761430740356</v>
+        <v>6.57761478424072</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G550" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G551" t="n">
-        <v>6.5331711769104</v>
+        <v>6.53317070007324</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G569" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G571" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G573" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G574" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G576" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G578" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G582" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G583" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G593" t="n">
-        <v>6.26651096343994</v>
+        <v>6.26651048660278</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G595" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6.75</v>
       </c>
       <c r="G596" t="n">
-        <v>5.99985074996948</v>
+        <v>5.99985122680664</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6.5</v>
       </c>
       <c r="G597" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G604" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G606" t="n">
-        <v>5.82207775115967</v>
+        <v>5.82207727432251</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G607" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G608" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G609" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G621" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G622" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G623" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G624" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G625" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G626" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G627" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G628" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G629" t="n">
-        <v>5.95540761947632</v>
+        <v>5.95540714263916</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G630" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G631" t="n">
-        <v>6.0442943572998</v>
+        <v>6.04429388046265</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>6.75</v>
       </c>
       <c r="G632" t="n">
-        <v>5.99985074996948</v>
+        <v>5.99985122680664</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G633" t="n">
-        <v>5.86652088165283</v>
+        <v>5.86652040481567</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>6.5</v>
       </c>
       <c r="G635" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>6.5</v>
       </c>
       <c r="G636" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>6.5</v>
       </c>
       <c r="G637" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>6.5</v>
       </c>
       <c r="G638" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>6.5</v>
       </c>
       <c r="G639" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>6.5</v>
       </c>
       <c r="G640" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G641" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G644" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G646" t="n">
-        <v>5.6443042755127</v>
+        <v>5.64430379867554</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G647" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G648" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>6.5</v>
       </c>
       <c r="G649" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>6.5</v>
       </c>
       <c r="G651" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>6.5</v>
       </c>
       <c r="G652" t="n">
-        <v>5.77763414382935</v>
+        <v>5.7776346206665</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G654" t="n">
-        <v>5.68874740600586</v>
+        <v>5.68874788284302</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G662" t="n">
-        <v>5.37764406204224</v>
+        <v>5.37764453887939</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>5.75</v>
       </c>
       <c r="G664" t="n">
-        <v>5.11098384857178</v>
+        <v>5.11098432540894</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>4.35544729232788</v>
+        <v>4.35544681549072</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G667" t="n">
-        <v>4.26656055450439</v>
+        <v>4.26656103134155</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G676" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>4.5</v>
       </c>
       <c r="G677" t="n">
-        <v>3.99990034103394</v>
+        <v>3.99990081787109</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G678" t="n">
-        <v>3.78657269477844</v>
+        <v>3.78657293319702</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>3.89323663711548</v>
+        <v>3.8932363986969</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G680" t="n">
-        <v>3.8576819896698</v>
+        <v>3.85768222808838</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G681" t="n">
-        <v>3.73324012756348</v>
+        <v>3.73324036598206